--- a/Backend/Input/Reports/formato.xlsx
+++ b/Backend/Input/Reports/formato.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C3680F-457D-4DEB-A5FC-35FA2E7B03A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBE6590-F3FC-4A54-AFFF-F42552B0CB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="733" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -432,9 +432,6 @@
     <t>Acum oct - 24</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Representa los Hitos acumulados que han sido ejecutados al año 2024. ​</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Todos los Convenios de Alta Dirección Pública (CADP) expuestos, se encuentran vigentes a la fecha del reporte.​</t>
   </si>
   <si>
@@ -857,6 +854,9 @@
   </si>
   <si>
     <t xml:space="preserve">RESULTADO EX ANTE </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Representa los Hitos acumulados que han sido ejecutados al año 2025. ​</t>
   </si>
 </sst>
 </file>
@@ -5875,15 +5875,42 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="79" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5893,36 +5920,9 @@
     <xf numFmtId="0" fontId="35" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="81" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -6040,21 +6040,27 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6082,23 +6088,266 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -6106,9 +6355,6 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6160,9 +6406,6 @@
     <xf numFmtId="0" fontId="43" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -6187,249 +6430,6 @@
     <xf numFmtId="0" fontId="53" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -6442,6 +6442,105 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6472,116 +6571,17 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -21231,7 +21231,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286377"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286385"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21287,7 +21287,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286378"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286386"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21352,7 +21352,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286379"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286387"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21417,7 +21417,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286380"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286388"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21482,7 +21482,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286381"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286389"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21547,7 +21547,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286382"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286390"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21612,7 +21612,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286383"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286391"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21677,7 +21677,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286384"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286392"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25059,7 +25059,7 @@
       <c r="D11" s="304"/>
       <c r="E11" s="309"/>
       <c r="F11" s="310" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G11" s="458">
         <v>2024</v>
@@ -25089,7 +25089,7 @@
       <c r="D12" s="125"/>
       <c r="E12" s="311"/>
       <c r="F12" s="459" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G12" s="460"/>
       <c r="H12" s="125"/>
@@ -25169,7 +25169,7 @@
       <c r="D15" s="125"/>
       <c r="E15" s="308"/>
       <c r="F15" s="456" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G15" s="456"/>
       <c r="H15" s="125"/>
@@ -25197,7 +25197,7 @@
       <c r="D16" s="125"/>
       <c r="E16" s="308"/>
       <c r="F16" s="456" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G16" s="456"/>
       <c r="H16" s="125"/>
@@ -25251,7 +25251,7 @@
       <c r="D18" s="125"/>
       <c r="E18" s="307"/>
       <c r="F18" s="457" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G18" s="457"/>
       <c r="H18" s="125"/>
@@ -25896,32 +25896,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="233"/>
-      <c r="B1" s="541" t="s">
+      <c r="B1" s="623" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="542"/>
-      <c r="D1" s="542"/>
-      <c r="E1" s="542"/>
-      <c r="F1" s="542"/>
-      <c r="G1" s="542"/>
-      <c r="H1" s="542"/>
-      <c r="I1" s="542"/>
-      <c r="J1" s="542"/>
-      <c r="K1" s="542"/>
-      <c r="L1" s="542"/>
-      <c r="M1" s="542"/>
-      <c r="N1" s="542"/>
-      <c r="O1" s="542"/>
-      <c r="P1" s="542"/>
-      <c r="Q1" s="542"/>
-      <c r="R1" s="542"/>
-      <c r="S1" s="542"/>
-      <c r="T1" s="542"/>
-      <c r="U1" s="542"/>
-      <c r="V1" s="542"/>
-      <c r="W1" s="542"/>
-      <c r="X1" s="542"/>
-      <c r="Y1" s="543"/>
+      <c r="C1" s="624"/>
+      <c r="D1" s="624"/>
+      <c r="E1" s="624"/>
+      <c r="F1" s="624"/>
+      <c r="G1" s="624"/>
+      <c r="H1" s="624"/>
+      <c r="I1" s="624"/>
+      <c r="J1" s="624"/>
+      <c r="K1" s="624"/>
+      <c r="L1" s="624"/>
+      <c r="M1" s="624"/>
+      <c r="N1" s="624"/>
+      <c r="O1" s="624"/>
+      <c r="P1" s="624"/>
+      <c r="Q1" s="624"/>
+      <c r="R1" s="624"/>
+      <c r="S1" s="624"/>
+      <c r="T1" s="624"/>
+      <c r="U1" s="624"/>
+      <c r="V1" s="624"/>
+      <c r="W1" s="624"/>
+      <c r="X1" s="624"/>
+      <c r="Y1" s="625"/>
       <c r="Z1" s="228"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -25955,67 +25955,67 @@
     </row>
     <row r="3" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A3" s="234" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="544" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="545"/>
-      <c r="D3" s="545"/>
-      <c r="E3" s="545"/>
-      <c r="F3" s="545"/>
-      <c r="G3" s="545"/>
-      <c r="H3" s="545"/>
-      <c r="I3" s="545"/>
-      <c r="J3" s="545"/>
-      <c r="K3" s="545"/>
-      <c r="L3" s="545"/>
-      <c r="M3" s="545"/>
-      <c r="N3" s="545"/>
-      <c r="O3" s="545"/>
-      <c r="P3" s="545"/>
-      <c r="Q3" s="545"/>
-      <c r="R3" s="545"/>
-      <c r="S3" s="545"/>
-      <c r="T3" s="545"/>
-      <c r="U3" s="545"/>
-      <c r="V3" s="545"/>
-      <c r="W3" s="545"/>
-      <c r="X3" s="545"/>
-      <c r="Y3" s="546"/>
+        <v>182</v>
+      </c>
+      <c r="B3" s="626" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="627"/>
+      <c r="D3" s="627"/>
+      <c r="E3" s="627"/>
+      <c r="F3" s="627"/>
+      <c r="G3" s="627"/>
+      <c r="H3" s="627"/>
+      <c r="I3" s="627"/>
+      <c r="J3" s="627"/>
+      <c r="K3" s="627"/>
+      <c r="L3" s="627"/>
+      <c r="M3" s="627"/>
+      <c r="N3" s="627"/>
+      <c r="O3" s="627"/>
+      <c r="P3" s="627"/>
+      <c r="Q3" s="627"/>
+      <c r="R3" s="627"/>
+      <c r="S3" s="627"/>
+      <c r="T3" s="627"/>
+      <c r="U3" s="627"/>
+      <c r="V3" s="627"/>
+      <c r="W3" s="627"/>
+      <c r="X3" s="627"/>
+      <c r="Y3" s="628"/>
       <c r="Z3" s="229"/>
       <c r="AA3" s="146"/>
     </row>
     <row r="4" spans="1:28" ht="23.25" customHeight="1" thickBot="1">
       <c r="A4" s="235" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="629" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="547" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="548"/>
-      <c r="D4" s="548"/>
-      <c r="E4" s="548"/>
-      <c r="F4" s="548"/>
-      <c r="G4" s="548"/>
-      <c r="H4" s="548"/>
-      <c r="I4" s="548"/>
-      <c r="J4" s="548"/>
-      <c r="K4" s="548"/>
-      <c r="L4" s="548"/>
-      <c r="M4" s="548"/>
-      <c r="N4" s="548"/>
-      <c r="O4" s="548"/>
-      <c r="P4" s="548"/>
-      <c r="Q4" s="548"/>
-      <c r="R4" s="548"/>
-      <c r="S4" s="548"/>
-      <c r="T4" s="548"/>
-      <c r="U4" s="548"/>
-      <c r="V4" s="548"/>
-      <c r="W4" s="548"/>
-      <c r="X4" s="548"/>
-      <c r="Y4" s="549"/>
+      <c r="C4" s="630"/>
+      <c r="D4" s="630"/>
+      <c r="E4" s="630"/>
+      <c r="F4" s="630"/>
+      <c r="G4" s="630"/>
+      <c r="H4" s="630"/>
+      <c r="I4" s="630"/>
+      <c r="J4" s="630"/>
+      <c r="K4" s="630"/>
+      <c r="L4" s="630"/>
+      <c r="M4" s="630"/>
+      <c r="N4" s="630"/>
+      <c r="O4" s="630"/>
+      <c r="P4" s="630"/>
+      <c r="Q4" s="630"/>
+      <c r="R4" s="630"/>
+      <c r="S4" s="630"/>
+      <c r="T4" s="630"/>
+      <c r="U4" s="630"/>
+      <c r="V4" s="630"/>
+      <c r="W4" s="630"/>
+      <c r="X4" s="630"/>
+      <c r="Y4" s="631"/>
       <c r="Z4" s="230"/>
       <c r="AA4" s="146"/>
     </row>
@@ -26050,89 +26050,89 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="236"/>
-      <c r="B6" s="553" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="554"/>
-      <c r="D6" s="554"/>
-      <c r="E6" s="555"/>
+      <c r="B6" s="635" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="636"/>
+      <c r="D6" s="636"/>
+      <c r="E6" s="637"/>
       <c r="F6" s="132"/>
       <c r="G6" s="195"/>
-      <c r="H6" s="573" t="s">
-        <v>145</v>
-      </c>
-      <c r="I6" s="574"/>
-      <c r="J6" s="574"/>
-      <c r="K6" s="575"/>
+      <c r="H6" s="601" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="602"/>
+      <c r="J6" s="602"/>
+      <c r="K6" s="603"/>
       <c r="L6" s="132"/>
       <c r="M6" s="195"/>
-      <c r="N6" s="581" t="s">
-        <v>164</v>
-      </c>
-      <c r="O6" s="582"/>
-      <c r="P6" s="583"/>
+      <c r="N6" s="613" t="s">
+        <v>163</v>
+      </c>
+      <c r="O6" s="614"/>
+      <c r="P6" s="615"/>
       <c r="Q6" s="202"/>
       <c r="R6" s="204"/>
-      <c r="S6" s="533" t="s">
-        <v>146</v>
-      </c>
-      <c r="T6" s="534"/>
+      <c r="S6" s="608" t="s">
+        <v>145</v>
+      </c>
+      <c r="T6" s="609"/>
       <c r="U6" s="205"/>
       <c r="V6" s="209"/>
       <c r="W6" s="196"/>
-      <c r="X6" s="533" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y6" s="534"/>
+      <c r="X6" s="608" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y6" s="609"/>
       <c r="Z6" s="123"/>
       <c r="AA6" s="146"/>
     </row>
     <row r="7" spans="1:28" ht="30.75" customHeight="1" thickBot="1">
       <c r="A7" s="236"/>
       <c r="B7" s="246" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="238" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="238" t="s">
+      <c r="D7" s="239" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="239" t="s">
+      <c r="E7" s="240" t="s">
         <v>143</v>
-      </c>
-      <c r="E7" s="240" t="s">
-        <v>144</v>
       </c>
       <c r="F7" s="132"/>
       <c r="G7" s="162"/>
-      <c r="H7" s="569">
+      <c r="H7" s="610">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="580"/>
-      <c r="J7" s="580"/>
-      <c r="K7" s="570"/>
+      <c r="I7" s="612"/>
+      <c r="J7" s="612"/>
+      <c r="K7" s="611"/>
       <c r="L7" s="132"/>
       <c r="M7" s="162"/>
-      <c r="N7" s="565">
+      <c r="N7" s="616">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="566"/>
-      <c r="P7" s="567"/>
+      <c r="O7" s="617"/>
+      <c r="P7" s="618"/>
       <c r="Q7" s="203"/>
       <c r="R7" s="205"/>
-      <c r="S7" s="569">
+      <c r="S7" s="610">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="570"/>
+      <c r="T7" s="611"/>
       <c r="U7" s="132"/>
       <c r="V7" s="208"/>
       <c r="W7" s="125"/>
-      <c r="X7" s="569">
+      <c r="X7" s="610">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="570"/>
+      <c r="Y7" s="611"/>
       <c r="Z7" s="194"/>
       <c r="AA7" s="146"/>
     </row>
@@ -26201,27 +26201,27 @@
       <c r="D10" s="187"/>
       <c r="E10" s="258"/>
       <c r="F10" s="132"/>
-      <c r="G10" s="561" t="s">
-        <v>148</v>
-      </c>
-      <c r="H10" s="562"/>
-      <c r="I10" s="562"/>
-      <c r="J10" s="562"/>
-      <c r="K10" s="562"/>
-      <c r="L10" s="562"/>
-      <c r="M10" s="562"/>
-      <c r="N10" s="562"/>
-      <c r="O10" s="562"/>
-      <c r="P10" s="562"/>
-      <c r="Q10" s="562"/>
-      <c r="R10" s="562"/>
-      <c r="S10" s="562"/>
-      <c r="T10" s="562"/>
-      <c r="U10" s="562"/>
-      <c r="V10" s="562"/>
-      <c r="W10" s="562"/>
-      <c r="X10" s="562"/>
-      <c r="Y10" s="563"/>
+      <c r="G10" s="642" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="643"/>
+      <c r="I10" s="643"/>
+      <c r="J10" s="643"/>
+      <c r="K10" s="643"/>
+      <c r="L10" s="643"/>
+      <c r="M10" s="643"/>
+      <c r="N10" s="643"/>
+      <c r="O10" s="643"/>
+      <c r="P10" s="643"/>
+      <c r="Q10" s="643"/>
+      <c r="R10" s="643"/>
+      <c r="S10" s="643"/>
+      <c r="T10" s="643"/>
+      <c r="U10" s="643"/>
+      <c r="V10" s="643"/>
+      <c r="W10" s="643"/>
+      <c r="X10" s="643"/>
+      <c r="Y10" s="644"/>
       <c r="Z10" s="123"/>
       <c r="AA10" s="146"/>
     </row>
@@ -26232,35 +26232,35 @@
       <c r="D11" s="187"/>
       <c r="E11" s="258"/>
       <c r="F11" s="132"/>
-      <c r="G11" s="564" t="s">
+      <c r="G11" s="645" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="640"/>
+      <c r="I11" s="640" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="559"/>
-      <c r="I11" s="559" t="s">
+      <c r="J11" s="640"/>
+      <c r="K11" s="640"/>
+      <c r="L11" s="640" t="s">
         <v>150</v>
       </c>
-      <c r="J11" s="559"/>
-      <c r="K11" s="559"/>
-      <c r="L11" s="559" t="s">
+      <c r="M11" s="640"/>
+      <c r="N11" s="640"/>
+      <c r="O11" s="640" t="s">
         <v>151</v>
       </c>
-      <c r="M11" s="559"/>
-      <c r="N11" s="559"/>
-      <c r="O11" s="559" t="s">
-        <v>152</v>
-      </c>
-      <c r="P11" s="559"/>
-      <c r="Q11" s="559"/>
-      <c r="R11" s="559" t="s">
-        <v>147</v>
-      </c>
-      <c r="S11" s="559"/>
-      <c r="T11" s="559"/>
-      <c r="U11" s="559"/>
-      <c r="V11" s="559"/>
-      <c r="W11" s="559"/>
-      <c r="X11" s="559"/>
-      <c r="Y11" s="560"/>
+      <c r="P11" s="640"/>
+      <c r="Q11" s="640"/>
+      <c r="R11" s="640" t="s">
+        <v>146</v>
+      </c>
+      <c r="S11" s="640"/>
+      <c r="T11" s="640"/>
+      <c r="U11" s="640"/>
+      <c r="V11" s="640"/>
+      <c r="W11" s="640"/>
+      <c r="X11" s="640"/>
+      <c r="Y11" s="641"/>
       <c r="Z11" s="123"/>
       <c r="AA11" s="146"/>
     </row>
@@ -26271,33 +26271,33 @@
       <c r="D12" s="243"/>
       <c r="E12" s="258"/>
       <c r="F12" s="132"/>
-      <c r="G12" s="564"/>
-      <c r="H12" s="559"/>
-      <c r="I12" s="559"/>
-      <c r="J12" s="559"/>
-      <c r="K12" s="559"/>
-      <c r="L12" s="559"/>
-      <c r="M12" s="559"/>
-      <c r="N12" s="559"/>
-      <c r="O12" s="559"/>
-      <c r="P12" s="559"/>
-      <c r="Q12" s="559"/>
-      <c r="R12" s="535" t="s">
+      <c r="G12" s="645"/>
+      <c r="H12" s="640"/>
+      <c r="I12" s="640"/>
+      <c r="J12" s="640"/>
+      <c r="K12" s="640"/>
+      <c r="L12" s="640"/>
+      <c r="M12" s="640"/>
+      <c r="N12" s="640"/>
+      <c r="O12" s="640"/>
+      <c r="P12" s="640"/>
+      <c r="Q12" s="640"/>
+      <c r="R12" s="567" t="s">
+        <v>152</v>
+      </c>
+      <c r="S12" s="567"/>
+      <c r="T12" s="567" t="s">
         <v>153</v>
       </c>
-      <c r="S12" s="535"/>
-      <c r="T12" s="535" t="s">
+      <c r="U12" s="567"/>
+      <c r="V12" s="567" t="s">
         <v>154</v>
       </c>
-      <c r="U12" s="535"/>
-      <c r="V12" s="535" t="s">
+      <c r="W12" s="567"/>
+      <c r="X12" s="567" t="s">
         <v>155</v>
       </c>
-      <c r="W12" s="535"/>
-      <c r="X12" s="535" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y12" s="556"/>
+      <c r="Y12" s="598"/>
       <c r="Z12" s="123"/>
       <c r="AA12" s="122"/>
     </row>
@@ -26308,25 +26308,25 @@
       <c r="D13" s="187"/>
       <c r="E13" s="258"/>
       <c r="F13" s="132"/>
-      <c r="G13" s="564"/>
-      <c r="H13" s="559"/>
-      <c r="I13" s="559"/>
-      <c r="J13" s="559"/>
-      <c r="K13" s="559"/>
-      <c r="L13" s="559"/>
-      <c r="M13" s="559"/>
-      <c r="N13" s="559"/>
-      <c r="O13" s="559"/>
-      <c r="P13" s="559"/>
-      <c r="Q13" s="559"/>
-      <c r="R13" s="535"/>
-      <c r="S13" s="535"/>
-      <c r="T13" s="535"/>
-      <c r="U13" s="535"/>
-      <c r="V13" s="535"/>
-      <c r="W13" s="535"/>
-      <c r="X13" s="557"/>
-      <c r="Y13" s="558"/>
+      <c r="G13" s="645"/>
+      <c r="H13" s="640"/>
+      <c r="I13" s="640"/>
+      <c r="J13" s="640"/>
+      <c r="K13" s="640"/>
+      <c r="L13" s="640"/>
+      <c r="M13" s="640"/>
+      <c r="N13" s="640"/>
+      <c r="O13" s="640"/>
+      <c r="P13" s="640"/>
+      <c r="Q13" s="640"/>
+      <c r="R13" s="567"/>
+      <c r="S13" s="567"/>
+      <c r="T13" s="567"/>
+      <c r="U13" s="567"/>
+      <c r="V13" s="567"/>
+      <c r="W13" s="567"/>
+      <c r="X13" s="638"/>
+      <c r="Y13" s="639"/>
       <c r="Z13" s="123"/>
       <c r="AA13" s="124"/>
     </row>
@@ -26337,25 +26337,25 @@
       <c r="D14" s="187"/>
       <c r="E14" s="258"/>
       <c r="F14" s="132"/>
-      <c r="G14" s="536"/>
-      <c r="H14" s="537"/>
-      <c r="I14" s="538"/>
-      <c r="J14" s="539"/>
-      <c r="K14" s="540"/>
-      <c r="L14" s="532"/>
-      <c r="M14" s="532"/>
-      <c r="N14" s="532"/>
-      <c r="O14" s="532"/>
-      <c r="P14" s="532"/>
-      <c r="Q14" s="532"/>
-      <c r="R14" s="532"/>
-      <c r="S14" s="532"/>
-      <c r="T14" s="532"/>
-      <c r="U14" s="532"/>
-      <c r="V14" s="532"/>
-      <c r="W14" s="538"/>
-      <c r="X14" s="532"/>
-      <c r="Y14" s="568"/>
+      <c r="G14" s="619"/>
+      <c r="H14" s="620"/>
+      <c r="I14" s="597"/>
+      <c r="J14" s="621"/>
+      <c r="K14" s="622"/>
+      <c r="L14" s="595"/>
+      <c r="M14" s="595"/>
+      <c r="N14" s="595"/>
+      <c r="O14" s="595"/>
+      <c r="P14" s="595"/>
+      <c r="Q14" s="595"/>
+      <c r="R14" s="595"/>
+      <c r="S14" s="595"/>
+      <c r="T14" s="595"/>
+      <c r="U14" s="595"/>
+      <c r="V14" s="595"/>
+      <c r="W14" s="597"/>
+      <c r="X14" s="595"/>
+      <c r="Y14" s="596"/>
       <c r="Z14" s="123"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -26365,25 +26365,25 @@
       <c r="D15" s="244"/>
       <c r="E15" s="259"/>
       <c r="F15" s="132"/>
-      <c r="G15" s="536"/>
-      <c r="H15" s="537"/>
-      <c r="I15" s="538"/>
-      <c r="J15" s="539"/>
-      <c r="K15" s="540"/>
-      <c r="L15" s="532"/>
-      <c r="M15" s="532"/>
-      <c r="N15" s="532"/>
-      <c r="O15" s="532"/>
-      <c r="P15" s="532"/>
-      <c r="Q15" s="532"/>
-      <c r="R15" s="532"/>
-      <c r="S15" s="532"/>
-      <c r="T15" s="532"/>
-      <c r="U15" s="532"/>
-      <c r="V15" s="532"/>
-      <c r="W15" s="538"/>
-      <c r="X15" s="532"/>
-      <c r="Y15" s="568"/>
+      <c r="G15" s="619"/>
+      <c r="H15" s="620"/>
+      <c r="I15" s="597"/>
+      <c r="J15" s="621"/>
+      <c r="K15" s="622"/>
+      <c r="L15" s="595"/>
+      <c r="M15" s="595"/>
+      <c r="N15" s="595"/>
+      <c r="O15" s="595"/>
+      <c r="P15" s="595"/>
+      <c r="Q15" s="595"/>
+      <c r="R15" s="595"/>
+      <c r="S15" s="595"/>
+      <c r="T15" s="595"/>
+      <c r="U15" s="595"/>
+      <c r="V15" s="595"/>
+      <c r="W15" s="597"/>
+      <c r="X15" s="595"/>
+      <c r="Y15" s="596"/>
       <c r="Z15" s="123"/>
       <c r="AA15" s="146"/>
     </row>
@@ -26394,94 +26394,94 @@
       <c r="D16" s="152"/>
       <c r="E16" s="152"/>
       <c r="F16" s="122"/>
-      <c r="G16" s="536"/>
-      <c r="H16" s="537"/>
-      <c r="I16" s="538"/>
-      <c r="J16" s="539"/>
-      <c r="K16" s="540"/>
-      <c r="L16" s="532"/>
-      <c r="M16" s="532"/>
-      <c r="N16" s="532"/>
-      <c r="O16" s="532"/>
-      <c r="P16" s="532"/>
-      <c r="Q16" s="532"/>
-      <c r="R16" s="532"/>
-      <c r="S16" s="532"/>
-      <c r="T16" s="532"/>
-      <c r="U16" s="532"/>
-      <c r="V16" s="532"/>
-      <c r="W16" s="538"/>
-      <c r="X16" s="532"/>
-      <c r="Y16" s="568"/>
+      <c r="G16" s="619"/>
+      <c r="H16" s="620"/>
+      <c r="I16" s="597"/>
+      <c r="J16" s="621"/>
+      <c r="K16" s="622"/>
+      <c r="L16" s="595"/>
+      <c r="M16" s="595"/>
+      <c r="N16" s="595"/>
+      <c r="O16" s="595"/>
+      <c r="P16" s="595"/>
+      <c r="Q16" s="595"/>
+      <c r="R16" s="595"/>
+      <c r="S16" s="595"/>
+      <c r="T16" s="595"/>
+      <c r="U16" s="595"/>
+      <c r="V16" s="595"/>
+      <c r="W16" s="597"/>
+      <c r="X16" s="595"/>
+      <c r="Y16" s="596"/>
       <c r="Z16" s="123"/>
       <c r="AA16" s="146"/>
       <c r="AB16" s="253"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="122"/>
-      <c r="B17" s="550" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="551"/>
-      <c r="D17" s="551"/>
-      <c r="E17" s="552"/>
+      <c r="B17" s="632" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="633"/>
+      <c r="D17" s="633"/>
+      <c r="E17" s="634"/>
       <c r="F17" s="132"/>
-      <c r="G17" s="536"/>
-      <c r="H17" s="537"/>
-      <c r="I17" s="538"/>
-      <c r="J17" s="539"/>
-      <c r="K17" s="540"/>
-      <c r="L17" s="532"/>
-      <c r="M17" s="532"/>
-      <c r="N17" s="532"/>
-      <c r="O17" s="532"/>
-      <c r="P17" s="532"/>
-      <c r="Q17" s="532"/>
-      <c r="R17" s="532"/>
-      <c r="S17" s="532"/>
-      <c r="T17" s="532"/>
-      <c r="U17" s="532"/>
-      <c r="V17" s="532"/>
-      <c r="W17" s="538"/>
-      <c r="X17" s="532"/>
-      <c r="Y17" s="568"/>
+      <c r="G17" s="619"/>
+      <c r="H17" s="620"/>
+      <c r="I17" s="597"/>
+      <c r="J17" s="621"/>
+      <c r="K17" s="622"/>
+      <c r="L17" s="595"/>
+      <c r="M17" s="595"/>
+      <c r="N17" s="595"/>
+      <c r="O17" s="595"/>
+      <c r="P17" s="595"/>
+      <c r="Q17" s="595"/>
+      <c r="R17" s="595"/>
+      <c r="S17" s="595"/>
+      <c r="T17" s="595"/>
+      <c r="U17" s="595"/>
+      <c r="V17" s="595"/>
+      <c r="W17" s="597"/>
+      <c r="X17" s="595"/>
+      <c r="Y17" s="596"/>
       <c r="Z17" s="123"/>
       <c r="AA17" s="146"/>
     </row>
     <row r="18" spans="1:27" ht="34.5" customHeight="1">
       <c r="A18" s="122"/>
       <c r="B18" s="210" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="186" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="185" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="211" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="186" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="185" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="211" t="s">
-        <v>160</v>
-      </c>
       <c r="F18" s="132"/>
-      <c r="G18" s="536"/>
-      <c r="H18" s="537"/>
-      <c r="I18" s="538"/>
-      <c r="J18" s="539"/>
-      <c r="K18" s="540"/>
-      <c r="L18" s="532"/>
-      <c r="M18" s="532"/>
-      <c r="N18" s="532"/>
-      <c r="O18" s="532"/>
-      <c r="P18" s="532"/>
-      <c r="Q18" s="532"/>
-      <c r="R18" s="532"/>
-      <c r="S18" s="532"/>
-      <c r="T18" s="532"/>
-      <c r="U18" s="532"/>
-      <c r="V18" s="532"/>
-      <c r="W18" s="538"/>
-      <c r="X18" s="532"/>
-      <c r="Y18" s="568"/>
+      <c r="G18" s="619"/>
+      <c r="H18" s="620"/>
+      <c r="I18" s="597"/>
+      <c r="J18" s="621"/>
+      <c r="K18" s="622"/>
+      <c r="L18" s="595"/>
+      <c r="M18" s="595"/>
+      <c r="N18" s="595"/>
+      <c r="O18" s="595"/>
+      <c r="P18" s="595"/>
+      <c r="Q18" s="595"/>
+      <c r="R18" s="595"/>
+      <c r="S18" s="595"/>
+      <c r="T18" s="595"/>
+      <c r="U18" s="595"/>
+      <c r="V18" s="595"/>
+      <c r="W18" s="597"/>
+      <c r="X18" s="595"/>
+      <c r="Y18" s="596"/>
       <c r="Z18" s="123"/>
       <c r="AA18" s="146"/>
     </row>
@@ -26492,25 +26492,25 @@
       <c r="D19" s="192"/>
       <c r="E19" s="260"/>
       <c r="F19" s="132"/>
-      <c r="G19" s="536"/>
-      <c r="H19" s="537"/>
-      <c r="I19" s="538"/>
-      <c r="J19" s="539"/>
-      <c r="K19" s="540"/>
-      <c r="L19" s="532"/>
-      <c r="M19" s="532"/>
-      <c r="N19" s="532"/>
-      <c r="O19" s="532"/>
-      <c r="P19" s="532"/>
-      <c r="Q19" s="532"/>
-      <c r="R19" s="532"/>
-      <c r="S19" s="532"/>
-      <c r="T19" s="532"/>
-      <c r="U19" s="532"/>
-      <c r="V19" s="532"/>
-      <c r="W19" s="538"/>
-      <c r="X19" s="532"/>
-      <c r="Y19" s="568"/>
+      <c r="G19" s="619"/>
+      <c r="H19" s="620"/>
+      <c r="I19" s="597"/>
+      <c r="J19" s="621"/>
+      <c r="K19" s="622"/>
+      <c r="L19" s="595"/>
+      <c r="M19" s="595"/>
+      <c r="N19" s="595"/>
+      <c r="O19" s="595"/>
+      <c r="P19" s="595"/>
+      <c r="Q19" s="595"/>
+      <c r="R19" s="595"/>
+      <c r="S19" s="595"/>
+      <c r="T19" s="595"/>
+      <c r="U19" s="595"/>
+      <c r="V19" s="595"/>
+      <c r="W19" s="597"/>
+      <c r="X19" s="595"/>
+      <c r="Y19" s="596"/>
       <c r="Z19" s="123"/>
       <c r="AA19" s="146"/>
     </row>
@@ -26521,25 +26521,25 @@
       <c r="D20" s="192"/>
       <c r="E20" s="260"/>
       <c r="F20" s="132"/>
-      <c r="G20" s="536"/>
-      <c r="H20" s="537"/>
-      <c r="I20" s="538"/>
-      <c r="J20" s="539"/>
-      <c r="K20" s="540"/>
-      <c r="L20" s="532"/>
-      <c r="M20" s="532"/>
-      <c r="N20" s="532"/>
-      <c r="O20" s="532"/>
-      <c r="P20" s="532"/>
-      <c r="Q20" s="532"/>
-      <c r="R20" s="532"/>
-      <c r="S20" s="532"/>
-      <c r="T20" s="532"/>
-      <c r="U20" s="532"/>
-      <c r="V20" s="532"/>
-      <c r="W20" s="538"/>
-      <c r="X20" s="532"/>
-      <c r="Y20" s="568"/>
+      <c r="G20" s="619"/>
+      <c r="H20" s="620"/>
+      <c r="I20" s="597"/>
+      <c r="J20" s="621"/>
+      <c r="K20" s="622"/>
+      <c r="L20" s="595"/>
+      <c r="M20" s="595"/>
+      <c r="N20" s="595"/>
+      <c r="O20" s="595"/>
+      <c r="P20" s="595"/>
+      <c r="Q20" s="595"/>
+      <c r="R20" s="595"/>
+      <c r="S20" s="595"/>
+      <c r="T20" s="595"/>
+      <c r="U20" s="595"/>
+      <c r="V20" s="595"/>
+      <c r="W20" s="597"/>
+      <c r="X20" s="595"/>
+      <c r="Y20" s="596"/>
       <c r="Z20" s="123"/>
       <c r="AA20" s="146"/>
     </row>
@@ -26550,25 +26550,25 @@
       <c r="D21" s="192"/>
       <c r="E21" s="260"/>
       <c r="F21" s="132"/>
-      <c r="G21" s="536"/>
-      <c r="H21" s="537"/>
-      <c r="I21" s="538"/>
-      <c r="J21" s="539"/>
-      <c r="K21" s="540"/>
-      <c r="L21" s="532"/>
-      <c r="M21" s="532"/>
-      <c r="N21" s="532"/>
-      <c r="O21" s="532"/>
-      <c r="P21" s="532"/>
-      <c r="Q21" s="532"/>
-      <c r="R21" s="532"/>
-      <c r="S21" s="532"/>
-      <c r="T21" s="532"/>
-      <c r="U21" s="532"/>
-      <c r="V21" s="532"/>
-      <c r="W21" s="538"/>
-      <c r="X21" s="532"/>
-      <c r="Y21" s="568"/>
+      <c r="G21" s="619"/>
+      <c r="H21" s="620"/>
+      <c r="I21" s="597"/>
+      <c r="J21" s="621"/>
+      <c r="K21" s="622"/>
+      <c r="L21" s="595"/>
+      <c r="M21" s="595"/>
+      <c r="N21" s="595"/>
+      <c r="O21" s="595"/>
+      <c r="P21" s="595"/>
+      <c r="Q21" s="595"/>
+      <c r="R21" s="595"/>
+      <c r="S21" s="595"/>
+      <c r="T21" s="595"/>
+      <c r="U21" s="595"/>
+      <c r="V21" s="595"/>
+      <c r="W21" s="597"/>
+      <c r="X21" s="595"/>
+      <c r="Y21" s="596"/>
       <c r="Z21" s="123"/>
       <c r="AA21" s="146"/>
     </row>
@@ -26579,25 +26579,25 @@
       <c r="D22" s="192"/>
       <c r="E22" s="260"/>
       <c r="F22" s="132"/>
-      <c r="G22" s="536"/>
-      <c r="H22" s="537"/>
-      <c r="I22" s="538"/>
-      <c r="J22" s="539"/>
-      <c r="K22" s="540"/>
-      <c r="L22" s="532"/>
-      <c r="M22" s="532"/>
-      <c r="N22" s="532"/>
-      <c r="O22" s="532"/>
-      <c r="P22" s="532"/>
-      <c r="Q22" s="532"/>
-      <c r="R22" s="532"/>
-      <c r="S22" s="532"/>
-      <c r="T22" s="532"/>
-      <c r="U22" s="532"/>
-      <c r="V22" s="532"/>
-      <c r="W22" s="538"/>
-      <c r="X22" s="532"/>
-      <c r="Y22" s="568"/>
+      <c r="G22" s="619"/>
+      <c r="H22" s="620"/>
+      <c r="I22" s="597"/>
+      <c r="J22" s="621"/>
+      <c r="K22" s="622"/>
+      <c r="L22" s="595"/>
+      <c r="M22" s="595"/>
+      <c r="N22" s="595"/>
+      <c r="O22" s="595"/>
+      <c r="P22" s="595"/>
+      <c r="Q22" s="595"/>
+      <c r="R22" s="595"/>
+      <c r="S22" s="595"/>
+      <c r="T22" s="595"/>
+      <c r="U22" s="595"/>
+      <c r="V22" s="595"/>
+      <c r="W22" s="597"/>
+      <c r="X22" s="595"/>
+      <c r="Y22" s="596"/>
       <c r="Z22" s="123"/>
       <c r="AA22" s="146"/>
     </row>
@@ -26608,48 +26608,48 @@
       <c r="D23" s="214"/>
       <c r="E23" s="261"/>
       <c r="F23" s="132"/>
-      <c r="G23" s="579" t="s">
-        <v>157</v>
-      </c>
-      <c r="H23" s="571"/>
-      <c r="I23" s="571">
+      <c r="G23" s="607" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="599"/>
+      <c r="I23" s="599">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="571"/>
-      <c r="K23" s="571"/>
-      <c r="L23" s="571">
+      <c r="J23" s="599"/>
+      <c r="K23" s="599"/>
+      <c r="L23" s="599">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="571"/>
-      <c r="N23" s="571"/>
-      <c r="O23" s="576">
+      <c r="M23" s="599"/>
+      <c r="N23" s="599"/>
+      <c r="O23" s="604">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="577"/>
-      <c r="Q23" s="578"/>
-      <c r="R23" s="576">
+      <c r="P23" s="605"/>
+      <c r="Q23" s="606"/>
+      <c r="R23" s="604">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="578"/>
-      <c r="T23" s="576">
+      <c r="S23" s="606"/>
+      <c r="T23" s="604">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="578"/>
-      <c r="V23" s="576">
+      <c r="U23" s="606"/>
+      <c r="V23" s="604">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="577"/>
-      <c r="X23" s="571">
+      <c r="W23" s="605"/>
+      <c r="X23" s="599">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="572"/>
+      <c r="Y23" s="600"/>
       <c r="Z23" s="123"/>
       <c r="AA23" s="146"/>
     </row>
@@ -26719,28 +26719,28 @@
       <c r="E26" s="125"/>
       <c r="F26" s="122"/>
       <c r="G26" s="188"/>
-      <c r="H26" s="616" t="s">
-        <v>172</v>
-      </c>
-      <c r="I26" s="617"/>
-      <c r="J26" s="618"/>
+      <c r="H26" s="562" t="s">
+        <v>171</v>
+      </c>
+      <c r="I26" s="563"/>
+      <c r="J26" s="564"/>
       <c r="K26" s="132"/>
-      <c r="L26" s="622" t="s">
-        <v>165</v>
-      </c>
-      <c r="M26" s="623"/>
-      <c r="N26" s="623"/>
-      <c r="O26" s="623"/>
-      <c r="P26" s="623"/>
-      <c r="Q26" s="623"/>
-      <c r="R26" s="623"/>
-      <c r="S26" s="623"/>
-      <c r="T26" s="623"/>
-      <c r="U26" s="623"/>
-      <c r="V26" s="623"/>
-      <c r="W26" s="623"/>
-      <c r="X26" s="623"/>
-      <c r="Y26" s="624"/>
+      <c r="L26" s="571" t="s">
+        <v>164</v>
+      </c>
+      <c r="M26" s="572"/>
+      <c r="N26" s="572"/>
+      <c r="O26" s="572"/>
+      <c r="P26" s="572"/>
+      <c r="Q26" s="572"/>
+      <c r="R26" s="572"/>
+      <c r="S26" s="572"/>
+      <c r="T26" s="572"/>
+      <c r="U26" s="572"/>
+      <c r="V26" s="572"/>
+      <c r="W26" s="572"/>
+      <c r="X26" s="572"/>
+      <c r="Y26" s="573"/>
       <c r="Z26" s="123"/>
       <c r="AA26" s="146"/>
     </row>
@@ -26752,42 +26752,42 @@
       <c r="E27" s="125"/>
       <c r="F27" s="122"/>
       <c r="G27" s="189"/>
-      <c r="H27" s="613">
+      <c r="H27" s="544">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="614"/>
-      <c r="J27" s="615"/>
+      <c r="I27" s="545"/>
+      <c r="J27" s="546"/>
       <c r="K27" s="132"/>
-      <c r="L27" s="587" t="s">
-        <v>149</v>
-      </c>
-      <c r="M27" s="535"/>
-      <c r="N27" s="535"/>
-      <c r="O27" s="535" t="s">
+      <c r="L27" s="593" t="s">
+        <v>148</v>
+      </c>
+      <c r="M27" s="567"/>
+      <c r="N27" s="567"/>
+      <c r="O27" s="567" t="s">
+        <v>165</v>
+      </c>
+      <c r="P27" s="567"/>
+      <c r="Q27" s="567" t="s">
         <v>166</v>
       </c>
-      <c r="P27" s="535"/>
-      <c r="Q27" s="535" t="s">
+      <c r="R27" s="567"/>
+      <c r="S27" s="567" t="s">
         <v>167</v>
       </c>
-      <c r="R27" s="535"/>
-      <c r="S27" s="535" t="s">
+      <c r="T27" s="567" t="s">
         <v>168</v>
       </c>
-      <c r="T27" s="535" t="s">
+      <c r="U27" s="567"/>
+      <c r="V27" s="567" t="s">
         <v>169</v>
       </c>
-      <c r="U27" s="535"/>
-      <c r="V27" s="535" t="s">
+      <c r="W27" s="567" t="s">
         <v>170</v>
       </c>
-      <c r="W27" s="535" t="s">
-        <v>171</v>
-      </c>
-      <c r="X27" s="535"/>
-      <c r="Y27" s="556" t="s">
-        <v>157</v>
+      <c r="X27" s="567"/>
+      <c r="Y27" s="598" t="s">
+        <v>156</v>
       </c>
       <c r="Z27" s="123"/>
       <c r="AA27" s="122"/>
@@ -26804,20 +26804,20 @@
       <c r="I28" s="125"/>
       <c r="J28" s="220"/>
       <c r="K28" s="132"/>
-      <c r="L28" s="587"/>
-      <c r="M28" s="535"/>
-      <c r="N28" s="535"/>
-      <c r="O28" s="535"/>
-      <c r="P28" s="535"/>
-      <c r="Q28" s="535"/>
-      <c r="R28" s="535"/>
-      <c r="S28" s="535"/>
-      <c r="T28" s="535"/>
-      <c r="U28" s="535"/>
-      <c r="V28" s="535"/>
-      <c r="W28" s="535"/>
-      <c r="X28" s="535"/>
-      <c r="Y28" s="556"/>
+      <c r="L28" s="593"/>
+      <c r="M28" s="567"/>
+      <c r="N28" s="567"/>
+      <c r="O28" s="567"/>
+      <c r="P28" s="567"/>
+      <c r="Q28" s="567"/>
+      <c r="R28" s="567"/>
+      <c r="S28" s="567"/>
+      <c r="T28" s="567"/>
+      <c r="U28" s="567"/>
+      <c r="V28" s="567"/>
+      <c r="W28" s="567"/>
+      <c r="X28" s="567"/>
+      <c r="Y28" s="598"/>
       <c r="Z28" s="123"/>
       <c r="AA28" s="146"/>
     </row>
@@ -26833,19 +26833,19 @@
       <c r="I29" s="221"/>
       <c r="J29" s="191"/>
       <c r="K29" s="132"/>
-      <c r="L29" s="584"/>
-      <c r="M29" s="585"/>
-      <c r="N29" s="585"/>
-      <c r="O29" s="585"/>
-      <c r="P29" s="585"/>
-      <c r="Q29" s="585"/>
-      <c r="R29" s="585"/>
+      <c r="L29" s="579"/>
+      <c r="M29" s="547"/>
+      <c r="N29" s="547"/>
+      <c r="O29" s="547"/>
+      <c r="P29" s="547"/>
+      <c r="Q29" s="547"/>
+      <c r="R29" s="547"/>
       <c r="S29" s="113"/>
-      <c r="T29" s="585"/>
-      <c r="U29" s="585"/>
+      <c r="T29" s="547"/>
+      <c r="U29" s="547"/>
       <c r="V29" s="113"/>
-      <c r="W29" s="585"/>
-      <c r="X29" s="586"/>
+      <c r="W29" s="547"/>
+      <c r="X29" s="548"/>
       <c r="Y29" s="254"/>
       <c r="Z29" s="123"/>
       <c r="AA29" s="146"/>
@@ -26862,19 +26862,19 @@
       <c r="I30" s="152"/>
       <c r="J30" s="152"/>
       <c r="K30" s="122"/>
-      <c r="L30" s="584"/>
-      <c r="M30" s="585"/>
-      <c r="N30" s="585"/>
-      <c r="O30" s="585"/>
-      <c r="P30" s="585"/>
-      <c r="Q30" s="585"/>
-      <c r="R30" s="585"/>
+      <c r="L30" s="579"/>
+      <c r="M30" s="547"/>
+      <c r="N30" s="547"/>
+      <c r="O30" s="547"/>
+      <c r="P30" s="547"/>
+      <c r="Q30" s="547"/>
+      <c r="R30" s="547"/>
       <c r="S30" s="113"/>
-      <c r="T30" s="585"/>
-      <c r="U30" s="585"/>
+      <c r="T30" s="547"/>
+      <c r="U30" s="547"/>
       <c r="V30" s="113"/>
-      <c r="W30" s="585"/>
-      <c r="X30" s="586"/>
+      <c r="W30" s="547"/>
+      <c r="X30" s="548"/>
       <c r="Y30" s="254"/>
       <c r="Z30" s="123"/>
       <c r="AA30" s="122"/>
@@ -26887,25 +26887,25 @@
       <c r="E31" s="125"/>
       <c r="F31" s="122"/>
       <c r="G31" s="188"/>
-      <c r="H31" s="619" t="s">
-        <v>162</v>
-      </c>
-      <c r="I31" s="620"/>
-      <c r="J31" s="621"/>
+      <c r="H31" s="568" t="s">
+        <v>161</v>
+      </c>
+      <c r="I31" s="569"/>
+      <c r="J31" s="570"/>
       <c r="K31" s="132"/>
-      <c r="L31" s="584"/>
-      <c r="M31" s="585"/>
-      <c r="N31" s="585"/>
-      <c r="O31" s="585"/>
-      <c r="P31" s="585"/>
-      <c r="Q31" s="585"/>
-      <c r="R31" s="585"/>
+      <c r="L31" s="579"/>
+      <c r="M31" s="547"/>
+      <c r="N31" s="547"/>
+      <c r="O31" s="547"/>
+      <c r="P31" s="547"/>
+      <c r="Q31" s="547"/>
+      <c r="R31" s="547"/>
       <c r="S31" s="113"/>
-      <c r="T31" s="585"/>
-      <c r="U31" s="585"/>
+      <c r="T31" s="547"/>
+      <c r="U31" s="547"/>
       <c r="V31" s="113"/>
-      <c r="W31" s="585"/>
-      <c r="X31" s="586"/>
+      <c r="W31" s="547"/>
+      <c r="X31" s="548"/>
       <c r="Y31" s="254"/>
       <c r="Z31" s="123"/>
       <c r="AA31" s="122"/>
@@ -26922,19 +26922,19 @@
       <c r="I32" s="125"/>
       <c r="J32" s="220"/>
       <c r="K32" s="132"/>
-      <c r="L32" s="584"/>
-      <c r="M32" s="585"/>
-      <c r="N32" s="585"/>
-      <c r="O32" s="585"/>
-      <c r="P32" s="585"/>
-      <c r="Q32" s="585"/>
-      <c r="R32" s="585"/>
+      <c r="L32" s="579"/>
+      <c r="M32" s="547"/>
+      <c r="N32" s="547"/>
+      <c r="O32" s="547"/>
+      <c r="P32" s="547"/>
+      <c r="Q32" s="547"/>
+      <c r="R32" s="547"/>
       <c r="S32" s="113"/>
-      <c r="T32" s="585"/>
-      <c r="U32" s="585"/>
+      <c r="T32" s="547"/>
+      <c r="U32" s="547"/>
       <c r="V32" s="113"/>
-      <c r="W32" s="585"/>
-      <c r="X32" s="586"/>
+      <c r="W32" s="547"/>
+      <c r="X32" s="548"/>
       <c r="Y32" s="254"/>
       <c r="Z32" s="123"/>
       <c r="AA32" s="122"/>
@@ -26947,26 +26947,26 @@
       <c r="E33" s="125"/>
       <c r="F33" s="122"/>
       <c r="G33" s="189"/>
-      <c r="H33" s="613">
+      <c r="H33" s="544">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="614"/>
-      <c r="J33" s="615"/>
+      <c r="I33" s="545"/>
+      <c r="J33" s="546"/>
       <c r="K33" s="132"/>
-      <c r="L33" s="584"/>
-      <c r="M33" s="585"/>
-      <c r="N33" s="585"/>
-      <c r="O33" s="585"/>
-      <c r="P33" s="585"/>
-      <c r="Q33" s="585"/>
-      <c r="R33" s="585"/>
+      <c r="L33" s="579"/>
+      <c r="M33" s="547"/>
+      <c r="N33" s="547"/>
+      <c r="O33" s="547"/>
+      <c r="P33" s="547"/>
+      <c r="Q33" s="547"/>
+      <c r="R33" s="547"/>
       <c r="S33" s="113"/>
-      <c r="T33" s="585"/>
-      <c r="U33" s="585"/>
+      <c r="T33" s="547"/>
+      <c r="U33" s="547"/>
       <c r="V33" s="113"/>
-      <c r="W33" s="585"/>
-      <c r="X33" s="586"/>
+      <c r="W33" s="547"/>
+      <c r="X33" s="548"/>
       <c r="Y33" s="254"/>
       <c r="Z33" s="123"/>
       <c r="AA33" s="252"/>
@@ -26983,19 +26983,19 @@
       <c r="I34" s="125"/>
       <c r="J34" s="220"/>
       <c r="K34" s="132"/>
-      <c r="L34" s="584"/>
-      <c r="M34" s="585"/>
-      <c r="N34" s="585"/>
-      <c r="O34" s="585"/>
-      <c r="P34" s="585"/>
-      <c r="Q34" s="585"/>
-      <c r="R34" s="585"/>
+      <c r="L34" s="579"/>
+      <c r="M34" s="547"/>
+      <c r="N34" s="547"/>
+      <c r="O34" s="547"/>
+      <c r="P34" s="547"/>
+      <c r="Q34" s="547"/>
+      <c r="R34" s="547"/>
       <c r="S34" s="113"/>
-      <c r="T34" s="585"/>
-      <c r="U34" s="585"/>
+      <c r="T34" s="547"/>
+      <c r="U34" s="547"/>
       <c r="V34" s="113"/>
-      <c r="W34" s="585"/>
-      <c r="X34" s="586"/>
+      <c r="W34" s="547"/>
+      <c r="X34" s="548"/>
       <c r="Y34" s="254"/>
       <c r="Z34" s="123"/>
       <c r="AA34" s="122"/>
@@ -27012,19 +27012,19 @@
       <c r="I35" s="221"/>
       <c r="J35" s="191"/>
       <c r="K35" s="132"/>
-      <c r="L35" s="584"/>
-      <c r="M35" s="585"/>
-      <c r="N35" s="585"/>
-      <c r="O35" s="588"/>
-      <c r="P35" s="588"/>
-      <c r="Q35" s="588"/>
-      <c r="R35" s="588"/>
+      <c r="L35" s="579"/>
+      <c r="M35" s="547"/>
+      <c r="N35" s="547"/>
+      <c r="O35" s="574"/>
+      <c r="P35" s="574"/>
+      <c r="Q35" s="574"/>
+      <c r="R35" s="574"/>
       <c r="S35" s="217"/>
-      <c r="T35" s="588"/>
-      <c r="U35" s="588"/>
+      <c r="T35" s="574"/>
+      <c r="U35" s="574"/>
       <c r="V35" s="217"/>
-      <c r="W35" s="588"/>
-      <c r="X35" s="589"/>
+      <c r="W35" s="574"/>
+      <c r="X35" s="594"/>
       <c r="Y35" s="254"/>
       <c r="Z35" s="123"/>
       <c r="AA35" s="146"/>
@@ -27041,19 +27041,19 @@
       <c r="I36" s="152"/>
       <c r="J36" s="152"/>
       <c r="K36" s="122"/>
-      <c r="L36" s="584"/>
-      <c r="M36" s="585"/>
-      <c r="N36" s="586"/>
-      <c r="O36" s="590"/>
-      <c r="P36" s="590"/>
-      <c r="Q36" s="590"/>
-      <c r="R36" s="590"/>
+      <c r="L36" s="579"/>
+      <c r="M36" s="547"/>
+      <c r="N36" s="548"/>
+      <c r="O36" s="551"/>
+      <c r="P36" s="551"/>
+      <c r="Q36" s="551"/>
+      <c r="R36" s="551"/>
       <c r="S36" s="218"/>
-      <c r="T36" s="590"/>
-      <c r="U36" s="590"/>
+      <c r="T36" s="551"/>
+      <c r="U36" s="551"/>
       <c r="V36" s="218"/>
-      <c r="W36" s="590"/>
-      <c r="X36" s="591"/>
+      <c r="W36" s="551"/>
+      <c r="X36" s="575"/>
       <c r="Y36" s="254"/>
       <c r="Z36" s="123"/>
       <c r="AA36" s="122"/>
@@ -27066,25 +27066,25 @@
       <c r="E37" s="125"/>
       <c r="F37" s="122"/>
       <c r="G37" s="188"/>
-      <c r="H37" s="619" t="s">
-        <v>161</v>
-      </c>
-      <c r="I37" s="620"/>
-      <c r="J37" s="621"/>
+      <c r="H37" s="568" t="s">
+        <v>160</v>
+      </c>
+      <c r="I37" s="569"/>
+      <c r="J37" s="570"/>
       <c r="K37" s="132"/>
-      <c r="L37" s="584"/>
-      <c r="M37" s="585"/>
-      <c r="N37" s="586"/>
-      <c r="O37" s="590"/>
-      <c r="P37" s="590"/>
-      <c r="Q37" s="590"/>
-      <c r="R37" s="590"/>
+      <c r="L37" s="579"/>
+      <c r="M37" s="547"/>
+      <c r="N37" s="548"/>
+      <c r="O37" s="551"/>
+      <c r="P37" s="551"/>
+      <c r="Q37" s="551"/>
+      <c r="R37" s="551"/>
       <c r="S37" s="218"/>
-      <c r="T37" s="590"/>
-      <c r="U37" s="590"/>
+      <c r="T37" s="551"/>
+      <c r="U37" s="551"/>
       <c r="V37" s="218"/>
-      <c r="W37" s="590"/>
-      <c r="X37" s="591"/>
+      <c r="W37" s="551"/>
+      <c r="X37" s="575"/>
       <c r="Y37" s="254"/>
       <c r="Z37" s="123"/>
     </row>
@@ -27100,39 +27100,39 @@
       <c r="I38" s="125"/>
       <c r="J38" s="220"/>
       <c r="K38" s="132"/>
-      <c r="L38" s="603" t="s">
-        <v>157</v>
-      </c>
-      <c r="M38" s="604"/>
-      <c r="N38" s="605"/>
-      <c r="O38" s="592">
+      <c r="L38" s="587" t="s">
+        <v>156</v>
+      </c>
+      <c r="M38" s="588"/>
+      <c r="N38" s="589"/>
+      <c r="O38" s="552">
         <f>SUM(O29:P37)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="592"/>
-      <c r="Q38" s="592">
+      <c r="P38" s="552"/>
+      <c r="Q38" s="552">
         <f>SUM(Q29:R37)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="592"/>
+      <c r="R38" s="552"/>
       <c r="S38" s="255">
         <f>SUM(S29:S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="592">
+      <c r="T38" s="552">
         <f>SUM(T29:U37)</f>
         <v>0</v>
       </c>
-      <c r="U38" s="592"/>
+      <c r="U38" s="552"/>
       <c r="V38" s="255">
         <f>SUM(V29:V37)</f>
         <v>0</v>
       </c>
-      <c r="W38" s="592">
+      <c r="W38" s="552">
         <f>SUM(W29:X37)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="592"/>
+      <c r="X38" s="552"/>
       <c r="Y38" s="256">
         <f>SUM(Y29:Y37)</f>
         <v>0</v>
@@ -27148,26 +27148,26 @@
       <c r="E39" s="125"/>
       <c r="F39" s="122"/>
       <c r="G39" s="189"/>
-      <c r="H39" s="613">
+      <c r="H39" s="544">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="614"/>
-      <c r="J39" s="615"/>
+      <c r="I39" s="545"/>
+      <c r="J39" s="546"/>
       <c r="K39" s="132"/>
-      <c r="L39" s="598"/>
-      <c r="M39" s="606"/>
-      <c r="N39" s="607"/>
-      <c r="O39" s="598"/>
-      <c r="P39" s="599"/>
-      <c r="Q39" s="611"/>
-      <c r="R39" s="612"/>
+      <c r="L39" s="582"/>
+      <c r="M39" s="590"/>
+      <c r="N39" s="591"/>
+      <c r="O39" s="582"/>
+      <c r="P39" s="583"/>
+      <c r="Q39" s="565"/>
+      <c r="R39" s="566"/>
       <c r="S39" s="150"/>
-      <c r="T39" s="639"/>
-      <c r="U39" s="639"/>
+      <c r="T39" s="553"/>
+      <c r="U39" s="553"/>
       <c r="V39" s="150"/>
-      <c r="W39" s="639"/>
-      <c r="X39" s="639"/>
+      <c r="W39" s="553"/>
+      <c r="X39" s="553"/>
       <c r="Y39" s="181"/>
       <c r="Z39" s="125"/>
       <c r="AA39" s="122"/>
@@ -27184,19 +27184,19 @@
       <c r="I40" s="125"/>
       <c r="J40" s="220"/>
       <c r="K40" s="132"/>
-      <c r="L40" s="608"/>
-      <c r="M40" s="609"/>
-      <c r="N40" s="610"/>
-      <c r="O40" s="600"/>
-      <c r="P40" s="597"/>
-      <c r="Q40" s="596"/>
-      <c r="R40" s="597"/>
+      <c r="L40" s="555"/>
+      <c r="M40" s="592"/>
+      <c r="N40" s="556"/>
+      <c r="O40" s="584"/>
+      <c r="P40" s="581"/>
+      <c r="Q40" s="580"/>
+      <c r="R40" s="581"/>
       <c r="S40" s="125"/>
-      <c r="T40" s="640"/>
-      <c r="U40" s="640"/>
+      <c r="T40" s="554"/>
+      <c r="U40" s="554"/>
       <c r="V40" s="125"/>
-      <c r="W40" s="640"/>
-      <c r="X40" s="640"/>
+      <c r="W40" s="554"/>
+      <c r="X40" s="554"/>
       <c r="Y40" s="193"/>
       <c r="Z40" s="125"/>
     </row>
@@ -27212,19 +27212,19 @@
       <c r="I41" s="221"/>
       <c r="J41" s="191"/>
       <c r="K41" s="132"/>
-      <c r="L41" s="608"/>
-      <c r="M41" s="609"/>
-      <c r="N41" s="610"/>
-      <c r="O41" s="601"/>
-      <c r="P41" s="602"/>
-      <c r="Q41" s="608"/>
-      <c r="R41" s="610"/>
+      <c r="L41" s="555"/>
+      <c r="M41" s="592"/>
+      <c r="N41" s="556"/>
+      <c r="O41" s="585"/>
+      <c r="P41" s="586"/>
+      <c r="Q41" s="555"/>
+      <c r="R41" s="556"/>
       <c r="S41" s="125"/>
-      <c r="T41" s="608"/>
-      <c r="U41" s="610"/>
+      <c r="T41" s="555"/>
+      <c r="U41" s="556"/>
       <c r="V41" s="125"/>
-      <c r="W41" s="608"/>
-      <c r="X41" s="610"/>
+      <c r="W41" s="555"/>
+      <c r="X41" s="556"/>
       <c r="Y41" s="193"/>
       <c r="Z41" s="125"/>
       <c r="AA41" s="146"/>
@@ -27241,21 +27241,21 @@
       <c r="I42" s="152"/>
       <c r="J42" s="152"/>
       <c r="K42" s="122"/>
-      <c r="L42" s="593"/>
-      <c r="M42" s="594"/>
-      <c r="N42" s="595"/>
-      <c r="O42" s="611"/>
-      <c r="P42" s="612"/>
+      <c r="L42" s="576"/>
+      <c r="M42" s="577"/>
+      <c r="N42" s="578"/>
+      <c r="O42" s="565"/>
+      <c r="P42" s="566"/>
       <c r="Q42" s="125"/>
-      <c r="R42" s="637" t="s">
-        <v>219</v>
-      </c>
-      <c r="S42" s="638"/>
+      <c r="R42" s="549" t="s">
+        <v>218</v>
+      </c>
+      <c r="S42" s="550"/>
       <c r="T42" s="151"/>
-      <c r="U42" s="641"/>
-      <c r="V42" s="642"/>
-      <c r="W42" s="641"/>
-      <c r="X42" s="642"/>
+      <c r="U42" s="557"/>
+      <c r="V42" s="558"/>
+      <c r="W42" s="557"/>
+      <c r="X42" s="558"/>
       <c r="Y42" s="193"/>
       <c r="Z42" s="125"/>
       <c r="AA42" s="122"/>
@@ -27268,26 +27268,26 @@
       <c r="E43" s="125"/>
       <c r="F43" s="122"/>
       <c r="G43" s="188"/>
-      <c r="H43" s="644" t="s">
-        <v>173</v>
-      </c>
-      <c r="I43" s="644"/>
-      <c r="J43" s="645"/>
+      <c r="H43" s="560" t="s">
+        <v>172</v>
+      </c>
+      <c r="I43" s="560"/>
+      <c r="J43" s="561"/>
       <c r="K43" s="132"/>
       <c r="L43" s="188"/>
       <c r="M43" s="219"/>
-      <c r="N43" s="628" t="s">
-        <v>163</v>
-      </c>
-      <c r="O43" s="629"/>
-      <c r="P43" s="630"/>
+      <c r="N43" s="535" t="s">
+        <v>162</v>
+      </c>
+      <c r="O43" s="536"/>
+      <c r="P43" s="537"/>
       <c r="Q43" s="189"/>
       <c r="R43" s="393" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S43" s="406"/>
       <c r="T43" s="403" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U43" s="394"/>
       <c r="V43" s="394"/>
@@ -27334,28 +27334,28 @@
       <c r="E45" s="125"/>
       <c r="F45" s="122"/>
       <c r="G45" s="189"/>
-      <c r="H45" s="613">
+      <c r="H45" s="544">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="614"/>
-      <c r="J45" s="615"/>
+      <c r="I45" s="545"/>
+      <c r="J45" s="546"/>
       <c r="K45" s="132"/>
       <c r="L45" s="189"/>
       <c r="M45" s="125"/>
       <c r="N45" s="125"/>
-      <c r="O45" s="631">
+      <c r="O45" s="538">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="632"/>
+      <c r="P45" s="539"/>
       <c r="Q45" s="189"/>
       <c r="R45" s="394" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S45" s="404"/>
       <c r="T45" s="402" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U45" s="403"/>
       <c r="V45" s="396"/>
@@ -27380,8 +27380,8 @@
       <c r="L46" s="189"/>
       <c r="M46" s="125"/>
       <c r="N46" s="125"/>
-      <c r="O46" s="633"/>
-      <c r="P46" s="634"/>
+      <c r="O46" s="540"/>
+      <c r="P46" s="541"/>
       <c r="Q46" s="189"/>
       <c r="R46" s="395"/>
       <c r="S46" s="410"/>
@@ -27412,11 +27412,11 @@
       <c r="O47" s="221"/>
       <c r="P47" s="191"/>
       <c r="R47" s="402" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S47" s="401"/>
       <c r="T47" s="402" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U47" s="403"/>
       <c r="V47" s="396"/>
@@ -27492,9 +27492,9 @@
       <c r="E50" s="125"/>
       <c r="F50" s="122"/>
       <c r="G50" s="222"/>
-      <c r="H50" s="635"/>
-      <c r="I50" s="635"/>
-      <c r="J50" s="636"/>
+      <c r="H50" s="542"/>
+      <c r="I50" s="542"/>
+      <c r="J50" s="543"/>
       <c r="K50" s="123"/>
       <c r="L50" s="150"/>
       <c r="M50" s="150"/>
@@ -27549,9 +27549,9 @@
       <c r="E52" s="125"/>
       <c r="F52" s="125"/>
       <c r="G52" s="125"/>
-      <c r="H52" s="643"/>
-      <c r="I52" s="643"/>
-      <c r="J52" s="643"/>
+      <c r="H52" s="559"/>
+      <c r="I52" s="559"/>
+      <c r="J52" s="559"/>
       <c r="K52" s="125"/>
       <c r="L52" s="125"/>
       <c r="M52" s="125"/>
@@ -27652,11 +27652,11 @@
       <c r="U55" s="122"/>
       <c r="V55" s="125"/>
       <c r="W55" s="125"/>
-      <c r="X55" s="625"/>
-      <c r="Y55" s="626"/>
-      <c r="Z55" s="626"/>
-      <c r="AA55" s="626"/>
-      <c r="AB55" s="627"/>
+      <c r="X55" s="532"/>
+      <c r="Y55" s="533"/>
+      <c r="Z55" s="533"/>
+      <c r="AA55" s="533"/>
+      <c r="AB55" s="534"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="125"/>
@@ -27872,11 +27872,11 @@
       <c r="P63" s="125"/>
       <c r="Q63" s="122"/>
       <c r="R63" s="122"/>
-      <c r="U63" s="625"/>
-      <c r="V63" s="626"/>
-      <c r="W63" s="626"/>
-      <c r="X63" s="626"/>
-      <c r="Y63" s="627"/>
+      <c r="U63" s="532"/>
+      <c r="V63" s="533"/>
+      <c r="W63" s="533"/>
+      <c r="X63" s="533"/>
+      <c r="Y63" s="534"/>
       <c r="Z63" s="125"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -28312,6 +28312,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -28336,178 +28508,6 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="5" priority="10">
@@ -28548,7 +28548,7 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="B2" s="648" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C2" s="648"/>
       <c r="D2" s="648"/>
@@ -28557,7 +28557,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="B3" s="649" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C3" s="649"/>
       <c r="D3" s="649"/>
@@ -28566,19 +28566,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="115" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="115" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="D4" s="115" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="E4" s="115" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="115" t="s">
+      <c r="F4" s="115" t="s">
         <v>179</v>
-      </c>
-      <c r="F4" s="115" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -28701,13 +28701,13 @@
     </row>
     <row r="14" spans="1:6" ht="15.75">
       <c r="C14" s="293" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D14" s="293" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E14" s="294" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -28770,7 +28770,7 @@
       <c r="D26" s="115"/>
       <c r="E26" s="3"/>
       <c r="G26" s="646" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H26" s="647">
         <v>5</v>
@@ -28999,7 +28999,7 @@
       <c r="I70" s="647"/>
       <c r="J70" s="646"/>
       <c r="K70" s="646" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="8:11">
@@ -29152,23 +29152,23 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="125"/>
-      <c r="B1" s="650" t="s">
-        <v>190</v>
-      </c>
-      <c r="C1" s="651"/>
-      <c r="D1" s="651"/>
-      <c r="E1" s="651"/>
-      <c r="F1" s="651"/>
-      <c r="G1" s="651"/>
-      <c r="H1" s="651"/>
-      <c r="I1" s="651"/>
-      <c r="J1" s="651"/>
-      <c r="K1" s="651"/>
-      <c r="L1" s="651"/>
-      <c r="M1" s="651"/>
-      <c r="N1" s="651"/>
-      <c r="O1" s="651"/>
-      <c r="P1" s="652"/>
+      <c r="B1" s="683" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" s="684"/>
+      <c r="D1" s="684"/>
+      <c r="E1" s="684"/>
+      <c r="F1" s="684"/>
+      <c r="G1" s="684"/>
+      <c r="H1" s="684"/>
+      <c r="I1" s="684"/>
+      <c r="J1" s="684"/>
+      <c r="K1" s="684"/>
+      <c r="L1" s="684"/>
+      <c r="M1" s="684"/>
+      <c r="N1" s="684"/>
+      <c r="O1" s="684"/>
+      <c r="P1" s="685"/>
       <c r="Q1" s="125"/>
       <c r="R1" s="125"/>
       <c r="S1" s="125"/>
@@ -29177,23 +29177,23 @@
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="125"/>
-      <c r="B2" s="653" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="654"/>
-      <c r="D2" s="654"/>
-      <c r="E2" s="654"/>
-      <c r="F2" s="654"/>
-      <c r="G2" s="654"/>
-      <c r="H2" s="654"/>
-      <c r="I2" s="654"/>
-      <c r="J2" s="654"/>
-      <c r="K2" s="654"/>
-      <c r="L2" s="654"/>
-      <c r="M2" s="654"/>
-      <c r="N2" s="654"/>
-      <c r="O2" s="654"/>
-      <c r="P2" s="655"/>
+      <c r="B2" s="686" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="687"/>
+      <c r="D2" s="687"/>
+      <c r="E2" s="687"/>
+      <c r="F2" s="687"/>
+      <c r="G2" s="687"/>
+      <c r="H2" s="687"/>
+      <c r="I2" s="687"/>
+      <c r="J2" s="687"/>
+      <c r="K2" s="687"/>
+      <c r="L2" s="687"/>
+      <c r="M2" s="687"/>
+      <c r="N2" s="687"/>
+      <c r="O2" s="687"/>
+      <c r="P2" s="688"/>
       <c r="Q2" s="125"/>
       <c r="R2" s="125"/>
       <c r="S2" s="125"/>
@@ -29234,14 +29234,14 @@
       <c r="H4" s="123"/>
       <c r="I4" s="131"/>
       <c r="J4" s="278"/>
-      <c r="K4" s="668" t="s">
-        <v>232</v>
-      </c>
-      <c r="L4" s="668"/>
-      <c r="M4" s="668"/>
-      <c r="N4" s="668"/>
-      <c r="O4" s="668"/>
-      <c r="P4" s="668"/>
+      <c r="K4" s="676" t="s">
+        <v>231</v>
+      </c>
+      <c r="L4" s="676"/>
+      <c r="M4" s="676"/>
+      <c r="N4" s="676"/>
+      <c r="O4" s="676"/>
+      <c r="P4" s="676"/>
       <c r="Q4" s="125"/>
       <c r="R4" s="125"/>
       <c r="S4" s="125"/>
@@ -29254,18 +29254,18 @@
       <c r="H5" s="122"/>
       <c r="I5" s="125"/>
       <c r="J5" s="279"/>
-      <c r="K5" s="664" t="s">
-        <v>193</v>
-      </c>
-      <c r="L5" s="664"/>
-      <c r="M5" s="664" t="s">
+      <c r="K5" s="693" t="s">
+        <v>192</v>
+      </c>
+      <c r="L5" s="693"/>
+      <c r="M5" s="693" t="s">
+        <v>195</v>
+      </c>
+      <c r="N5" s="693"/>
+      <c r="O5" s="693" t="s">
         <v>196</v>
       </c>
-      <c r="N5" s="664"/>
-      <c r="O5" s="664" t="s">
-        <v>197</v>
-      </c>
-      <c r="P5" s="664"/>
+      <c r="P5" s="693"/>
       <c r="Q5" s="123"/>
       <c r="R5" s="125"/>
       <c r="S5" s="125"/>
@@ -29278,12 +29278,12 @@
       <c r="H6" s="122"/>
       <c r="I6" s="125"/>
       <c r="J6" s="122"/>
-      <c r="K6" s="679"/>
-      <c r="L6" s="660"/>
-      <c r="M6" s="659"/>
-      <c r="N6" s="660"/>
-      <c r="O6" s="659"/>
-      <c r="P6" s="665"/>
+      <c r="K6" s="672"/>
+      <c r="L6" s="673"/>
+      <c r="M6" s="692"/>
+      <c r="N6" s="673"/>
+      <c r="O6" s="692"/>
+      <c r="P6" s="694"/>
       <c r="Q6" s="123"/>
       <c r="R6" s="125"/>
       <c r="S6" s="125"/>
@@ -29294,18 +29294,18 @@
       <c r="A7" s="125"/>
       <c r="C7" s="125"/>
       <c r="D7" s="125"/>
-      <c r="E7" s="666"/>
-      <c r="F7" s="667"/>
-      <c r="G7" s="667"/>
-      <c r="H7" s="667"/>
+      <c r="E7" s="674"/>
+      <c r="F7" s="675"/>
+      <c r="G7" s="675"/>
+      <c r="H7" s="675"/>
       <c r="I7" s="125"/>
       <c r="J7" s="146"/>
-      <c r="K7" s="669"/>
-      <c r="L7" s="662"/>
-      <c r="M7" s="661"/>
-      <c r="N7" s="662"/>
-      <c r="O7" s="661"/>
-      <c r="P7" s="663"/>
+      <c r="K7" s="668"/>
+      <c r="L7" s="665"/>
+      <c r="M7" s="664"/>
+      <c r="N7" s="665"/>
+      <c r="O7" s="664"/>
+      <c r="P7" s="671"/>
       <c r="Q7" s="123"/>
       <c r="R7" s="125"/>
       <c r="S7" s="125"/>
@@ -29319,12 +29319,12 @@
       <c r="D8" s="125"/>
       <c r="I8" s="125"/>
       <c r="J8" s="122"/>
-      <c r="K8" s="669"/>
-      <c r="L8" s="662"/>
-      <c r="M8" s="661"/>
-      <c r="N8" s="662"/>
-      <c r="O8" s="661"/>
-      <c r="P8" s="663"/>
+      <c r="K8" s="668"/>
+      <c r="L8" s="665"/>
+      <c r="M8" s="664"/>
+      <c r="N8" s="665"/>
+      <c r="O8" s="664"/>
+      <c r="P8" s="671"/>
       <c r="Q8" s="123"/>
       <c r="R8" s="125"/>
       <c r="S8" s="125"/>
@@ -29338,12 +29338,12 @@
       <c r="D9" s="125"/>
       <c r="I9" s="125"/>
       <c r="J9" s="146"/>
-      <c r="K9" s="669"/>
-      <c r="L9" s="662"/>
-      <c r="M9" s="661"/>
-      <c r="N9" s="662"/>
-      <c r="O9" s="661"/>
-      <c r="P9" s="663"/>
+      <c r="K9" s="668"/>
+      <c r="L9" s="665"/>
+      <c r="M9" s="664"/>
+      <c r="N9" s="665"/>
+      <c r="O9" s="664"/>
+      <c r="P9" s="671"/>
       <c r="Q9" s="123"/>
       <c r="R9" s="125"/>
       <c r="S9" s="125"/>
@@ -29357,12 +29357,12 @@
       <c r="D10" s="125"/>
       <c r="I10" s="125"/>
       <c r="J10" s="122"/>
-      <c r="K10" s="669"/>
-      <c r="L10" s="662"/>
-      <c r="M10" s="661"/>
-      <c r="N10" s="662"/>
-      <c r="O10" s="661"/>
-      <c r="P10" s="663"/>
+      <c r="K10" s="668"/>
+      <c r="L10" s="665"/>
+      <c r="M10" s="664"/>
+      <c r="N10" s="665"/>
+      <c r="O10" s="664"/>
+      <c r="P10" s="671"/>
       <c r="Q10" s="123"/>
       <c r="R10" s="125"/>
       <c r="S10" s="125"/>
@@ -29374,20 +29374,20 @@
       <c r="B11" s="125"/>
       <c r="C11" s="125"/>
       <c r="D11" s="122"/>
-      <c r="E11" s="656" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="657"/>
-      <c r="G11" s="657"/>
-      <c r="H11" s="658"/>
+      <c r="E11" s="689" t="s">
+        <v>194</v>
+      </c>
+      <c r="F11" s="690"/>
+      <c r="G11" s="690"/>
+      <c r="H11" s="691"/>
       <c r="I11" s="123"/>
       <c r="J11" s="146"/>
-      <c r="K11" s="669"/>
-      <c r="L11" s="662"/>
-      <c r="M11" s="661"/>
-      <c r="N11" s="662"/>
-      <c r="O11" s="661"/>
-      <c r="P11" s="663"/>
+      <c r="K11" s="668"/>
+      <c r="L11" s="665"/>
+      <c r="M11" s="664"/>
+      <c r="N11" s="665"/>
+      <c r="O11" s="664"/>
+      <c r="P11" s="671"/>
       <c r="Q11" s="123"/>
       <c r="R11" s="125"/>
       <c r="S11" s="125"/>
@@ -29399,22 +29399,22 @@
       <c r="B12" s="125"/>
       <c r="C12" s="125"/>
       <c r="D12" s="122"/>
-      <c r="E12" s="670" t="s">
+      <c r="E12" s="677" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12" s="678"/>
+      <c r="G12" s="679"/>
+      <c r="H12" s="288" t="s">
         <v>193</v>
-      </c>
-      <c r="F12" s="671"/>
-      <c r="G12" s="672"/>
-      <c r="H12" s="288" t="s">
-        <v>194</v>
       </c>
       <c r="I12" s="123"/>
       <c r="J12" s="146"/>
-      <c r="K12" s="669"/>
-      <c r="L12" s="662"/>
-      <c r="M12" s="661"/>
-      <c r="N12" s="662"/>
-      <c r="O12" s="661"/>
-      <c r="P12" s="663"/>
+      <c r="K12" s="668"/>
+      <c r="L12" s="665"/>
+      <c r="M12" s="664"/>
+      <c r="N12" s="665"/>
+      <c r="O12" s="664"/>
+      <c r="P12" s="671"/>
       <c r="Q12" s="123"/>
       <c r="R12" s="125"/>
       <c r="S12" s="125"/>
@@ -29426,22 +29426,22 @@
       <c r="B13" s="125"/>
       <c r="C13" s="125"/>
       <c r="D13" s="122"/>
-      <c r="E13" s="673" t="s">
-        <v>211</v>
-      </c>
-      <c r="F13" s="674"/>
-      <c r="G13" s="675"/>
+      <c r="E13" s="680" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="681"/>
+      <c r="G13" s="682"/>
       <c r="H13" s="349">
         <v>2</v>
       </c>
       <c r="I13" s="123"/>
       <c r="J13" s="122"/>
-      <c r="K13" s="669"/>
-      <c r="L13" s="662"/>
-      <c r="M13" s="661"/>
-      <c r="N13" s="662"/>
-      <c r="O13" s="661"/>
-      <c r="P13" s="663"/>
+      <c r="K13" s="668"/>
+      <c r="L13" s="665"/>
+      <c r="M13" s="664"/>
+      <c r="N13" s="665"/>
+      <c r="O13" s="664"/>
+      <c r="P13" s="671"/>
       <c r="Q13" s="123"/>
       <c r="R13" s="125"/>
       <c r="S13" s="125"/>
@@ -29453,22 +29453,22 @@
       <c r="B14" s="125"/>
       <c r="C14" s="125"/>
       <c r="D14" s="122"/>
-      <c r="E14" s="676" t="s">
-        <v>209</v>
-      </c>
-      <c r="F14" s="677"/>
-      <c r="G14" s="678"/>
+      <c r="E14" s="656" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="657"/>
+      <c r="G14" s="658"/>
       <c r="H14" s="350">
         <v>26</v>
       </c>
       <c r="I14" s="123"/>
       <c r="J14" s="130"/>
-      <c r="K14" s="669"/>
-      <c r="L14" s="662"/>
-      <c r="M14" s="661"/>
-      <c r="N14" s="662"/>
-      <c r="O14" s="661"/>
-      <c r="P14" s="663"/>
+      <c r="K14" s="668"/>
+      <c r="L14" s="665"/>
+      <c r="M14" s="664"/>
+      <c r="N14" s="665"/>
+      <c r="O14" s="664"/>
+      <c r="P14" s="671"/>
       <c r="Q14" s="123"/>
       <c r="R14" s="125"/>
       <c r="S14" s="125"/>
@@ -29480,22 +29480,22 @@
       <c r="B15" s="125"/>
       <c r="C15" s="125"/>
       <c r="D15" s="122"/>
-      <c r="E15" s="676" t="s">
-        <v>210</v>
-      </c>
-      <c r="F15" s="677"/>
-      <c r="G15" s="678"/>
+      <c r="E15" s="656" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="657"/>
+      <c r="G15" s="658"/>
       <c r="H15" s="350">
         <v>5</v>
       </c>
       <c r="I15" s="123"/>
       <c r="J15" s="122"/>
-      <c r="K15" s="669"/>
-      <c r="L15" s="662"/>
-      <c r="M15" s="661"/>
-      <c r="N15" s="662"/>
-      <c r="O15" s="661"/>
-      <c r="P15" s="663"/>
+      <c r="K15" s="668"/>
+      <c r="L15" s="665"/>
+      <c r="M15" s="664"/>
+      <c r="N15" s="665"/>
+      <c r="O15" s="664"/>
+      <c r="P15" s="671"/>
       <c r="Q15" s="123"/>
       <c r="R15" s="125"/>
       <c r="S15" s="125"/>
@@ -29507,22 +29507,22 @@
       <c r="B16" s="125"/>
       <c r="C16" s="125"/>
       <c r="D16" s="122"/>
-      <c r="E16" s="676" t="s">
-        <v>212</v>
-      </c>
-      <c r="F16" s="677"/>
-      <c r="G16" s="678"/>
+      <c r="E16" s="656" t="s">
+        <v>211</v>
+      </c>
+      <c r="F16" s="657"/>
+      <c r="G16" s="658"/>
       <c r="H16" s="350">
         <v>29</v>
       </c>
       <c r="I16" s="123"/>
       <c r="J16" s="146"/>
-      <c r="K16" s="669"/>
-      <c r="L16" s="662"/>
-      <c r="M16" s="661"/>
-      <c r="N16" s="662"/>
-      <c r="O16" s="661"/>
-      <c r="P16" s="663"/>
+      <c r="K16" s="668"/>
+      <c r="L16" s="665"/>
+      <c r="M16" s="664"/>
+      <c r="N16" s="665"/>
+      <c r="O16" s="664"/>
+      <c r="P16" s="671"/>
       <c r="Q16" s="123"/>
       <c r="R16" s="125"/>
       <c r="S16" s="125"/>
@@ -29532,22 +29532,22 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="122"/>
       <c r="D17" s="141"/>
-      <c r="E17" s="676" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" s="677"/>
-      <c r="G17" s="678"/>
+      <c r="E17" s="656" t="s">
+        <v>212</v>
+      </c>
+      <c r="F17" s="657"/>
+      <c r="G17" s="658"/>
       <c r="H17" s="350">
         <v>6</v>
       </c>
       <c r="I17" s="123"/>
       <c r="J17" s="146"/>
-      <c r="K17" s="669"/>
-      <c r="L17" s="662"/>
-      <c r="M17" s="661"/>
-      <c r="N17" s="662"/>
-      <c r="O17" s="661"/>
-      <c r="P17" s="663"/>
+      <c r="K17" s="668"/>
+      <c r="L17" s="665"/>
+      <c r="M17" s="664"/>
+      <c r="N17" s="665"/>
+      <c r="O17" s="664"/>
+      <c r="P17" s="671"/>
       <c r="Q17" s="123"/>
       <c r="R17" s="125"/>
       <c r="S17" s="125"/>
@@ -29558,22 +29558,22 @@
       <c r="A18" s="122"/>
       <c r="C18" s="150"/>
       <c r="D18" s="122"/>
-      <c r="E18" s="688" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" s="689"/>
-      <c r="G18" s="690"/>
+      <c r="E18" s="659" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" s="660"/>
+      <c r="G18" s="661"/>
       <c r="H18" s="351">
         <v>25</v>
       </c>
       <c r="I18" s="123"/>
       <c r="J18" s="122"/>
-      <c r="K18" s="696"/>
-      <c r="L18" s="695"/>
-      <c r="M18" s="680"/>
-      <c r="N18" s="695"/>
-      <c r="O18" s="680"/>
-      <c r="P18" s="681"/>
+      <c r="K18" s="669"/>
+      <c r="L18" s="667"/>
+      <c r="M18" s="666"/>
+      <c r="N18" s="667"/>
+      <c r="O18" s="666"/>
+      <c r="P18" s="670"/>
       <c r="Q18" s="123"/>
       <c r="R18" s="125"/>
       <c r="S18" s="122"/>
@@ -29605,10 +29605,10 @@
     <row r="20" spans="1:21" ht="56.25" customHeight="1" thickBot="1">
       <c r="A20" s="122"/>
       <c r="B20" s="338" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" s="282" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D20" s="281"/>
       <c r="E20" s="133"/>
@@ -29657,13 +29657,13 @@
       <c r="D22" s="317"/>
       <c r="E22" s="326"/>
       <c r="F22" s="348" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G22" s="325"/>
-      <c r="H22" s="691" t="s">
-        <v>198</v>
-      </c>
-      <c r="I22" s="692"/>
+      <c r="H22" s="662" t="s">
+        <v>197</v>
+      </c>
+      <c r="I22" s="663"/>
       <c r="J22" s="334"/>
       <c r="K22" s="344"/>
       <c r="L22" s="322"/>
@@ -29737,7 +29737,7 @@
       <c r="I25" s="201"/>
       <c r="J25" s="122"/>
       <c r="K25" s="435" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L25" s="219"/>
       <c r="M25" s="434"/>
@@ -29756,19 +29756,19 @@
       <c r="D26" s="317"/>
       <c r="E26" s="331"/>
       <c r="F26" s="347" t="s">
-        <v>199</v>
-      </c>
-      <c r="H26" s="693" t="s">
-        <v>228</v>
-      </c>
-      <c r="I26" s="694"/>
+        <v>198</v>
+      </c>
+      <c r="H26" s="695" t="s">
+        <v>227</v>
+      </c>
+      <c r="I26" s="696"/>
       <c r="J26" s="433"/>
-      <c r="K26" s="682" t="s">
-        <v>231</v>
-      </c>
-      <c r="L26" s="683"/>
-      <c r="M26" s="683"/>
-      <c r="N26" s="684"/>
+      <c r="K26" s="650" t="s">
+        <v>230</v>
+      </c>
+      <c r="L26" s="651"/>
+      <c r="M26" s="651"/>
+      <c r="N26" s="652"/>
       <c r="O26" s="123"/>
       <c r="P26" s="220"/>
       <c r="Q26" s="123"/>
@@ -29792,12 +29792,12 @@
       </c>
       <c r="I27" s="283"/>
       <c r="J27" s="280"/>
-      <c r="K27" s="685" t="s">
-        <v>230</v>
-      </c>
-      <c r="L27" s="686"/>
-      <c r="M27" s="686"/>
-      <c r="N27" s="687"/>
+      <c r="K27" s="653" t="s">
+        <v>229</v>
+      </c>
+      <c r="L27" s="654"/>
+      <c r="M27" s="654"/>
+      <c r="N27" s="655"/>
       <c r="O27" s="221"/>
       <c r="P27" s="191"/>
       <c r="Q27" s="123"/>
@@ -30244,32 +30244,22 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
     <mergeCell ref="M15:N15"/>
@@ -30286,22 +30276,32 @@
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -30325,16 +30325,16 @@
   <sheetData>
     <row r="2" spans="1:4" ht="18.75">
       <c r="A2" s="352" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="352" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="352" t="s">
+      <c r="C2" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="352" t="s">
+      <c r="D2" s="352" t="s">
         <v>202</v>
-      </c>
-      <c r="D2" s="352" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.75" customHeight="1">
@@ -30478,14 +30478,14 @@
       <c r="G2" s="357"/>
       <c r="H2" s="357"/>
       <c r="I2" s="357"/>
-      <c r="J2" s="462" t="s">
-        <v>218</v>
-      </c>
-      <c r="K2" s="462"/>
-      <c r="L2" s="462"/>
-      <c r="M2" s="462"/>
-      <c r="N2" s="462"/>
-      <c r="O2" s="462"/>
+      <c r="J2" s="472" t="s">
+        <v>217</v>
+      </c>
+      <c r="K2" s="472"/>
+      <c r="L2" s="472"/>
+      <c r="M2" s="472"/>
+      <c r="N2" s="472"/>
+      <c r="O2" s="472"/>
       <c r="P2" s="357"/>
       <c r="Q2" s="357"/>
       <c r="R2" s="357"/>
@@ -30515,7 +30515,7 @@
     <row r="4" spans="1:19" ht="33" customHeight="1">
       <c r="A4" s="44"/>
       <c r="B4" s="358" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C4" s="358"/>
       <c r="D4" s="358"/>
@@ -30524,16 +30524,16 @@
       <c r="G4" s="358"/>
       <c r="H4" s="358"/>
       <c r="I4" s="358" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="471" t="s">
         <v>216</v>
       </c>
-      <c r="J4" s="461" t="s">
-        <v>217</v>
-      </c>
-      <c r="K4" s="461"/>
-      <c r="L4" s="461"/>
-      <c r="M4" s="461"/>
-      <c r="N4" s="461"/>
-      <c r="O4" s="461"/>
+      <c r="K4" s="471"/>
+      <c r="L4" s="471"/>
+      <c r="M4" s="471"/>
+      <c r="N4" s="471"/>
+      <c r="O4" s="471"/>
       <c r="P4" s="262"/>
       <c r="Q4" s="262"/>
       <c r="R4" s="263"/>
@@ -30549,17 +30549,17 @@
       <c r="G5" s="359"/>
       <c r="H5" s="359"/>
       <c r="I5" s="361"/>
-      <c r="J5" s="472" t="s">
+      <c r="J5" s="464" t="s">
+        <v>186</v>
+      </c>
+      <c r="K5" s="464"/>
+      <c r="L5" s="464"/>
+      <c r="M5" s="464"/>
+      <c r="N5" s="476" t="s">
         <v>187</v>
       </c>
-      <c r="K5" s="472"/>
-      <c r="L5" s="472"/>
-      <c r="M5" s="472"/>
-      <c r="N5" s="469" t="s">
-        <v>188</v>
-      </c>
-      <c r="O5" s="469"/>
-      <c r="P5" s="469"/>
+      <c r="O5" s="476"/>
+      <c r="P5" s="476"/>
       <c r="Q5" s="360"/>
       <c r="R5" s="360"/>
       <c r="S5" s="43"/>
@@ -30590,12 +30590,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="44"/>
-      <c r="C8" s="473" t="str">
+      <c r="C8" s="467" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO OCTUBRE - 2024</v>
       </c>
-      <c r="D8" s="474"/>
-      <c r="E8" s="475"/>
+      <c r="D8" s="468"/>
+      <c r="E8" s="469"/>
       <c r="G8" s="92" t="s">
         <v>1</v>
       </c>
@@ -30638,11 +30638,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="44"/>
-      <c r="C10" s="476" t="s">
+      <c r="C10" s="470" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="476"/>
-      <c r="E10" s="476"/>
+      <c r="D10" s="470"/>
+      <c r="E10" s="470"/>
       <c r="G10" s="119" t="s">
         <v>8</v>
       </c>
@@ -30792,11 +30792,11 @@
       <c r="C15" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="471">
+      <c r="D15" s="462">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="471"/>
+      <c r="E15" s="462"/>
       <c r="H15" s="71"/>
       <c r="M15" s="71"/>
       <c r="N15" s="71"/>
@@ -30839,11 +30839,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="44"/>
-      <c r="C24" s="464" t="s">
+      <c r="C24" s="473" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="465"/>
-      <c r="E24" s="466"/>
+      <c r="D24" s="474"/>
+      <c r="E24" s="475"/>
       <c r="S24" s="43"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -30851,11 +30851,11 @@
       <c r="C25" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="467">
+      <c r="D25" s="465">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="468"/>
+      <c r="E25" s="466"/>
       <c r="S25" s="43"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -30863,11 +30863,11 @@
       <c r="C26" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="467">
+      <c r="D26" s="465">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="468"/>
+      <c r="E26" s="466"/>
       <c r="S26" s="43"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -30899,11 +30899,11 @@
       <c r="C29" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="470">
+      <c r="D29" s="461">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="470"/>
+      <c r="E29" s="461"/>
       <c r="S29" s="43"/>
     </row>
     <row r="30" spans="1:19">
@@ -31017,6 +31017,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -31028,12 +31034,6 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -31384,7 +31384,7 @@
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
       <c r="A2" s="477" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" s="478"/>
       <c r="C2" s="478"/>
@@ -34869,10 +34869,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="114" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="114" t="s">
         <v>138</v>
-      </c>
-      <c r="E3" s="114" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -35889,9 +35889,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="141"/>
-      <c r="B1" s="521"/>
-      <c r="C1" s="522"/>
-      <c r="D1" s="523"/>
+      <c r="B1" s="523"/>
+      <c r="C1" s="524"/>
+      <c r="D1" s="525"/>
       <c r="E1" s="122"/>
       <c r="F1" s="125"/>
       <c r="G1" s="123"/>
@@ -35913,10 +35913,10 @@
       <c r="E2" s="131"/>
       <c r="G2" s="133"/>
       <c r="H2" s="125"/>
-      <c r="I2" s="530" t="s">
+      <c r="I2" s="519" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="531"/>
+      <c r="J2" s="520"/>
       <c r="K2" s="136"/>
       <c r="L2" s="125"/>
       <c r="M2" s="133"/>
@@ -35969,10 +35969,10 @@
       <c r="B5" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="524" t="s">
+      <c r="C5" s="526" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="525"/>
+      <c r="D5" s="527"/>
       <c r="E5" s="266" t="s">
         <v>111</v>
       </c>
@@ -35983,7 +35983,7 @@
         <v>112</v>
       </c>
       <c r="H5" s="267" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I5" s="267" t="s">
         <v>113</v>
@@ -36002,8 +36002,8 @@
       <c r="B6" s="295" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="526"/>
-      <c r="D6" s="527"/>
+      <c r="C6" s="528"/>
+      <c r="D6" s="529"/>
       <c r="E6" s="298"/>
       <c r="F6" s="298"/>
       <c r="G6" s="298"/>
@@ -36023,8 +36023,8 @@
       <c r="B7" s="296" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="528"/>
-      <c r="D7" s="529"/>
+      <c r="C7" s="530"/>
+      <c r="D7" s="531"/>
       <c r="E7" s="300"/>
       <c r="F7" s="300"/>
       <c r="G7" s="300"/>
@@ -36042,8 +36042,8 @@
       <c r="B8" s="296" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="528"/>
-      <c r="D8" s="529"/>
+      <c r="C8" s="530"/>
+      <c r="D8" s="531"/>
       <c r="E8" s="300"/>
       <c r="F8" s="300"/>
       <c r="G8" s="300"/>
@@ -36062,8 +36062,8 @@
       <c r="B9" s="296" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="528"/>
-      <c r="D9" s="529"/>
+      <c r="C9" s="530"/>
+      <c r="D9" s="531"/>
       <c r="E9" s="300"/>
       <c r="F9" s="300"/>
       <c r="G9" s="300"/>
@@ -36083,8 +36083,8 @@
       <c r="B10" s="296" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="528"/>
-      <c r="D10" s="529"/>
+      <c r="C10" s="530"/>
+      <c r="D10" s="531"/>
       <c r="E10" s="300"/>
       <c r="F10" s="300"/>
       <c r="G10" s="300"/>
@@ -36103,8 +36103,8 @@
       <c r="B11" s="296" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="528"/>
-      <c r="D11" s="529"/>
+      <c r="C11" s="530"/>
+      <c r="D11" s="531"/>
       <c r="E11" s="300"/>
       <c r="F11" s="300"/>
       <c r="G11" s="300"/>
@@ -36123,8 +36123,8 @@
       <c r="B12" s="297" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="516"/>
-      <c r="D12" s="517"/>
+      <c r="C12" s="521"/>
+      <c r="D12" s="522"/>
       <c r="E12" s="302"/>
       <c r="F12" s="302"/>
       <c r="G12" s="302"/>
@@ -36158,11 +36158,11 @@
     <row r="14" spans="1:17" ht="30.75" customHeight="1">
       <c r="A14" s="147"/>
       <c r="B14" s="419" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="439"/>
       <c r="D14" s="418" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14" s="175"/>
       <c r="F14" s="176"/>
@@ -36197,18 +36197,18 @@
     <row r="16" spans="1:17" ht="74.25" customHeight="1" thickBot="1">
       <c r="A16" s="147"/>
       <c r="B16" s="421" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="C16" s="441"/>
       <c r="D16" s="427" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="518"/>
-      <c r="F16" s="519"/>
-      <c r="G16" s="519"/>
-      <c r="H16" s="519"/>
-      <c r="I16" s="519"/>
-      <c r="J16" s="520"/>
+        <v>131</v>
+      </c>
+      <c r="E16" s="516"/>
+      <c r="F16" s="517"/>
+      <c r="G16" s="517"/>
+      <c r="H16" s="517"/>
+      <c r="I16" s="517"/>
+      <c r="J16" s="518"/>
       <c r="K16" s="444"/>
       <c r="L16" s="161"/>
       <c r="M16" s="159"/>
@@ -36218,18 +36218,18 @@
     <row r="17" spans="1:16" ht="108.75" customHeight="1" thickBot="1">
       <c r="A17" s="130"/>
       <c r="B17" s="422" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C17" s="442"/>
       <c r="D17" s="427" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" s="518"/>
-      <c r="F17" s="519"/>
-      <c r="G17" s="519"/>
-      <c r="H17" s="519"/>
-      <c r="I17" s="519"/>
-      <c r="J17" s="520"/>
+        <v>130</v>
+      </c>
+      <c r="E17" s="516"/>
+      <c r="F17" s="517"/>
+      <c r="G17" s="517"/>
+      <c r="H17" s="517"/>
+      <c r="I17" s="517"/>
+      <c r="J17" s="518"/>
       <c r="K17" s="189"/>
       <c r="L17" s="172"/>
       <c r="M17" s="161"/>
@@ -36240,18 +36240,18 @@
     <row r="18" spans="1:16" ht="87" customHeight="1" thickBot="1">
       <c r="A18" s="148"/>
       <c r="B18" s="422" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" s="442"/>
       <c r="D18" s="428" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" s="518"/>
-      <c r="F18" s="519"/>
-      <c r="G18" s="519"/>
-      <c r="H18" s="519"/>
-      <c r="I18" s="519"/>
-      <c r="J18" s="520"/>
+        <v>132</v>
+      </c>
+      <c r="E18" s="516"/>
+      <c r="F18" s="517"/>
+      <c r="G18" s="517"/>
+      <c r="H18" s="517"/>
+      <c r="I18" s="517"/>
+      <c r="J18" s="518"/>
       <c r="L18" s="161"/>
       <c r="M18" s="157"/>
       <c r="N18" s="156"/>
@@ -36263,14 +36263,14 @@
       <c r="B19" s="149"/>
       <c r="C19" s="130"/>
       <c r="D19" s="429" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" s="518"/>
-      <c r="F19" s="519"/>
-      <c r="G19" s="519"/>
-      <c r="H19" s="519"/>
-      <c r="I19" s="519"/>
-      <c r="J19" s="520"/>
+        <v>133</v>
+      </c>
+      <c r="E19" s="516"/>
+      <c r="F19" s="517"/>
+      <c r="G19" s="517"/>
+      <c r="H19" s="517"/>
+      <c r="I19" s="517"/>
+      <c r="J19" s="518"/>
       <c r="K19" s="189"/>
       <c r="L19" s="172"/>
       <c r="M19" s="157"/>
@@ -36282,14 +36282,14 @@
       <c r="A20" s="122"/>
       <c r="B20" s="133"/>
       <c r="D20" s="428" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="518"/>
-      <c r="F20" s="519"/>
-      <c r="G20" s="519"/>
-      <c r="H20" s="519"/>
-      <c r="I20" s="519"/>
-      <c r="J20" s="520"/>
+        <v>134</v>
+      </c>
+      <c r="E20" s="516"/>
+      <c r="F20" s="517"/>
+      <c r="G20" s="517"/>
+      <c r="H20" s="517"/>
+      <c r="I20" s="517"/>
+      <c r="J20" s="518"/>
       <c r="K20" s="445"/>
       <c r="L20" s="430"/>
       <c r="M20" s="160"/>
@@ -36300,14 +36300,14 @@
       <c r="B21" s="313"/>
       <c r="C21" s="314"/>
       <c r="D21" s="431" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="518"/>
-      <c r="F21" s="519"/>
-      <c r="G21" s="519"/>
-      <c r="H21" s="519"/>
-      <c r="I21" s="519"/>
-      <c r="J21" s="520"/>
+        <v>135</v>
+      </c>
+      <c r="E21" s="516"/>
+      <c r="F21" s="517"/>
+      <c r="G21" s="517"/>
+      <c r="H21" s="517"/>
+      <c r="I21" s="517"/>
+      <c r="J21" s="518"/>
       <c r="K21" s="446"/>
       <c r="L21" s="94"/>
       <c r="M21" s="158"/>
@@ -36319,14 +36319,14 @@
       <c r="B22" s="152"/>
       <c r="C22" s="130"/>
       <c r="D22" s="447" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" s="518"/>
-      <c r="F22" s="519"/>
-      <c r="G22" s="519"/>
-      <c r="H22" s="519"/>
-      <c r="I22" s="519"/>
-      <c r="J22" s="520"/>
+        <v>136</v>
+      </c>
+      <c r="E22" s="516"/>
+      <c r="F22" s="517"/>
+      <c r="G22" s="517"/>
+      <c r="H22" s="517"/>
+      <c r="I22" s="517"/>
+      <c r="J22" s="518"/>
       <c r="L22" s="158"/>
       <c r="M22" s="161"/>
       <c r="N22" s="161"/>
@@ -36744,11 +36744,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E19:J19"/>
@@ -36761,6 +36756,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -36778,17 +36778,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -37043,6 +37032,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
@@ -37052,23 +37052,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37085,4 +37068,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Backend/Input/Reports/formato.xlsx
+++ b/Backend/Input/Reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24310C58-9371-4EF2-BF1E-ABC6B48D7BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C46B26-2F6F-4447-BC9F-DD010C9F3768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5235" yWindow="0" windowWidth="15375" windowHeight="7785" tabRatio="733" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="02-ESTADO NC" sheetId="20" r:id="rId4"/>
     <sheet name="03-  ESTADO REGIONES" sheetId="32" r:id="rId5"/>
     <sheet name="data_status_NC" sheetId="33" state="hidden" r:id="rId6"/>
-    <sheet name="data_status_reg" sheetId="46" r:id="rId7"/>
+    <sheet name="data_status_reg" sheetId="46" state="hidden" r:id="rId7"/>
     <sheet name="Ev Proveedores" sheetId="43" r:id="rId8"/>
     <sheet name="Convenios ADP" sheetId="45" r:id="rId9"/>
     <sheet name="Gestión de riesgos" sheetId="48" r:id="rId10"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="234">
   <si>
     <t>SUBSECRETARÍA DE EDUCACIÓN</t>
   </si>
@@ -861,12 +861,6 @@
   <si>
     <t>CDC: Estudiantes OAP que postulan a 
 través del SAE</t>
-  </si>
-  <si>
-    <t>bajo</t>
-  </si>
-  <si>
-    <t>medio</t>
   </si>
 </sst>
 </file>
@@ -4926,7 +4920,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="703">
+  <cellXfs count="701">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5862,751 +5856,32 @@
     <xf numFmtId="49" fontId="20" fillId="24" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="72" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="80" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="228" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="230" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="231" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="232" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="170" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="172" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="198" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="4" borderId="253" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="193" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="252" xfId="0" applyFill="1" applyBorder="1"/>
@@ -6650,35 +5925,752 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="252" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="256" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="257" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="231" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="72" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="80" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="252" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="256" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="59" fillId="4" borderId="253" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="59" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="228" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="230" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="231" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="232" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="257" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="231" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="170" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="172" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="19" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="21" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="21" borderId="198" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="21" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -21328,7 +21320,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286401"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286409"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21384,7 +21376,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286402"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286410"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21449,7 +21441,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286403"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286411"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21514,7 +21506,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286404"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286412"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21579,7 +21571,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286405"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286413"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21644,7 +21636,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286406"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286414"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21709,7 +21701,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286407"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286415"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21774,7 +21766,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286408"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286416"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25158,10 +25150,10 @@
       <c r="F11" s="283" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="427">
+      <c r="G11" s="462">
         <v>2024</v>
       </c>
-      <c r="H11" s="427"/>
+      <c r="H11" s="462"/>
       <c r="I11" s="98"/>
       <c r="J11" s="98"/>
       <c r="K11" s="98"/>
@@ -25185,10 +25177,10 @@
       <c r="C12" s="98"/>
       <c r="D12" s="98"/>
       <c r="E12" s="284"/>
-      <c r="F12" s="428" t="s">
+      <c r="F12" s="463" t="s">
         <v>203</v>
       </c>
-      <c r="G12" s="429"/>
+      <c r="G12" s="464"/>
       <c r="H12" s="98"/>
       <c r="I12" s="98"/>
       <c r="J12" s="98"/>
@@ -25265,10 +25257,10 @@
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
       <c r="E15" s="281"/>
-      <c r="F15" s="425" t="s">
+      <c r="F15" s="460" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="425"/>
+      <c r="G15" s="460"/>
       <c r="H15" s="98"/>
       <c r="I15" s="98"/>
       <c r="J15" s="98"/>
@@ -25293,10 +25285,10 @@
       <c r="C16" s="98"/>
       <c r="D16" s="98"/>
       <c r="E16" s="281"/>
-      <c r="F16" s="425" t="s">
+      <c r="F16" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="G16" s="425"/>
+      <c r="G16" s="460"/>
       <c r="H16" s="98"/>
       <c r="I16" s="98"/>
       <c r="J16" s="98"/>
@@ -25347,10 +25339,10 @@
       <c r="C18" s="98"/>
       <c r="D18" s="98"/>
       <c r="E18" s="280"/>
-      <c r="F18" s="426" t="s">
+      <c r="F18" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="G18" s="426"/>
+      <c r="G18" s="461"/>
       <c r="H18" s="98"/>
       <c r="I18" s="98"/>
       <c r="J18" s="98"/>
@@ -25993,32 +25985,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="206"/>
-      <c r="B1" s="505" t="s">
+      <c r="B1" s="627" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="506"/>
-      <c r="D1" s="506"/>
-      <c r="E1" s="506"/>
-      <c r="F1" s="506"/>
-      <c r="G1" s="506"/>
-      <c r="H1" s="506"/>
-      <c r="I1" s="506"/>
-      <c r="J1" s="506"/>
-      <c r="K1" s="506"/>
-      <c r="L1" s="506"/>
-      <c r="M1" s="506"/>
-      <c r="N1" s="506"/>
-      <c r="O1" s="506"/>
-      <c r="P1" s="506"/>
-      <c r="Q1" s="506"/>
-      <c r="R1" s="506"/>
-      <c r="S1" s="506"/>
-      <c r="T1" s="506"/>
-      <c r="U1" s="506"/>
-      <c r="V1" s="506"/>
-      <c r="W1" s="506"/>
-      <c r="X1" s="506"/>
-      <c r="Y1" s="507"/>
+      <c r="C1" s="628"/>
+      <c r="D1" s="628"/>
+      <c r="E1" s="628"/>
+      <c r="F1" s="628"/>
+      <c r="G1" s="628"/>
+      <c r="H1" s="628"/>
+      <c r="I1" s="628"/>
+      <c r="J1" s="628"/>
+      <c r="K1" s="628"/>
+      <c r="L1" s="628"/>
+      <c r="M1" s="628"/>
+      <c r="N1" s="628"/>
+      <c r="O1" s="628"/>
+      <c r="P1" s="628"/>
+      <c r="Q1" s="628"/>
+      <c r="R1" s="628"/>
+      <c r="S1" s="628"/>
+      <c r="T1" s="628"/>
+      <c r="U1" s="628"/>
+      <c r="V1" s="628"/>
+      <c r="W1" s="628"/>
+      <c r="X1" s="628"/>
+      <c r="Y1" s="629"/>
       <c r="Z1" s="201"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -26054,32 +26046,32 @@
       <c r="A3" s="207" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="508" t="s">
+      <c r="B3" s="630" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="509"/>
-      <c r="D3" s="509"/>
-      <c r="E3" s="509"/>
-      <c r="F3" s="509"/>
-      <c r="G3" s="509"/>
-      <c r="H3" s="509"/>
-      <c r="I3" s="509"/>
-      <c r="J3" s="509"/>
-      <c r="K3" s="509"/>
-      <c r="L3" s="509"/>
-      <c r="M3" s="509"/>
-      <c r="N3" s="509"/>
-      <c r="O3" s="509"/>
-      <c r="P3" s="509"/>
-      <c r="Q3" s="509"/>
-      <c r="R3" s="509"/>
-      <c r="S3" s="509"/>
-      <c r="T3" s="509"/>
-      <c r="U3" s="509"/>
-      <c r="V3" s="509"/>
-      <c r="W3" s="509"/>
-      <c r="X3" s="509"/>
-      <c r="Y3" s="510"/>
+      <c r="C3" s="631"/>
+      <c r="D3" s="631"/>
+      <c r="E3" s="631"/>
+      <c r="F3" s="631"/>
+      <c r="G3" s="631"/>
+      <c r="H3" s="631"/>
+      <c r="I3" s="631"/>
+      <c r="J3" s="631"/>
+      <c r="K3" s="631"/>
+      <c r="L3" s="631"/>
+      <c r="M3" s="631"/>
+      <c r="N3" s="631"/>
+      <c r="O3" s="631"/>
+      <c r="P3" s="631"/>
+      <c r="Q3" s="631"/>
+      <c r="R3" s="631"/>
+      <c r="S3" s="631"/>
+      <c r="T3" s="631"/>
+      <c r="U3" s="631"/>
+      <c r="V3" s="631"/>
+      <c r="W3" s="631"/>
+      <c r="X3" s="631"/>
+      <c r="Y3" s="632"/>
       <c r="Z3" s="202"/>
       <c r="AA3" s="119"/>
     </row>
@@ -26087,32 +26079,32 @@
       <c r="A4" s="208" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="511" t="s">
+      <c r="B4" s="633" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="512"/>
-      <c r="D4" s="512"/>
-      <c r="E4" s="512"/>
-      <c r="F4" s="512"/>
-      <c r="G4" s="512"/>
-      <c r="H4" s="512"/>
-      <c r="I4" s="512"/>
-      <c r="J4" s="512"/>
-      <c r="K4" s="512"/>
-      <c r="L4" s="512"/>
-      <c r="M4" s="512"/>
-      <c r="N4" s="512"/>
-      <c r="O4" s="512"/>
-      <c r="P4" s="512"/>
-      <c r="Q4" s="512"/>
-      <c r="R4" s="512"/>
-      <c r="S4" s="512"/>
-      <c r="T4" s="512"/>
-      <c r="U4" s="512"/>
-      <c r="V4" s="512"/>
-      <c r="W4" s="512"/>
-      <c r="X4" s="512"/>
-      <c r="Y4" s="513"/>
+      <c r="C4" s="634"/>
+      <c r="D4" s="634"/>
+      <c r="E4" s="634"/>
+      <c r="F4" s="634"/>
+      <c r="G4" s="634"/>
+      <c r="H4" s="634"/>
+      <c r="I4" s="634"/>
+      <c r="J4" s="634"/>
+      <c r="K4" s="634"/>
+      <c r="L4" s="634"/>
+      <c r="M4" s="634"/>
+      <c r="N4" s="634"/>
+      <c r="O4" s="634"/>
+      <c r="P4" s="634"/>
+      <c r="Q4" s="634"/>
+      <c r="R4" s="634"/>
+      <c r="S4" s="634"/>
+      <c r="T4" s="634"/>
+      <c r="U4" s="634"/>
+      <c r="V4" s="634"/>
+      <c r="W4" s="634"/>
+      <c r="X4" s="634"/>
+      <c r="Y4" s="635"/>
       <c r="Z4" s="203"/>
       <c r="AA4" s="119"/>
     </row>
@@ -26147,40 +26139,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="209"/>
-      <c r="B6" s="517" t="s">
+      <c r="B6" s="639" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="518"/>
-      <c r="D6" s="518"/>
-      <c r="E6" s="519"/>
+      <c r="C6" s="640"/>
+      <c r="D6" s="640"/>
+      <c r="E6" s="641"/>
       <c r="F6" s="105"/>
       <c r="G6" s="168"/>
-      <c r="H6" s="537" t="s">
+      <c r="H6" s="605" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="538"/>
-      <c r="J6" s="538"/>
-      <c r="K6" s="539"/>
+      <c r="I6" s="606"/>
+      <c r="J6" s="606"/>
+      <c r="K6" s="607"/>
       <c r="L6" s="105"/>
       <c r="M6" s="168"/>
-      <c r="N6" s="545" t="s">
+      <c r="N6" s="617" t="s">
         <v>162</v>
       </c>
-      <c r="O6" s="546"/>
-      <c r="P6" s="547"/>
+      <c r="O6" s="618"/>
+      <c r="P6" s="619"/>
       <c r="Q6" s="175"/>
       <c r="R6" s="177"/>
-      <c r="S6" s="497" t="s">
+      <c r="S6" s="612" t="s">
         <v>144</v>
       </c>
-      <c r="T6" s="498"/>
+      <c r="T6" s="613"/>
       <c r="U6" s="178"/>
       <c r="V6" s="182"/>
       <c r="W6" s="169"/>
-      <c r="X6" s="497" t="s">
+      <c r="X6" s="612" t="s">
         <v>145</v>
       </c>
-      <c r="Y6" s="498"/>
+      <c r="Y6" s="613"/>
       <c r="Z6" s="96"/>
       <c r="AA6" s="119"/>
     </row>
@@ -26200,36 +26192,36 @@
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="135"/>
-      <c r="H7" s="533">
+      <c r="H7" s="614">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="544"/>
-      <c r="J7" s="544"/>
-      <c r="K7" s="534"/>
+      <c r="I7" s="616"/>
+      <c r="J7" s="616"/>
+      <c r="K7" s="615"/>
       <c r="L7" s="105"/>
       <c r="M7" s="135"/>
-      <c r="N7" s="529">
+      <c r="N7" s="620">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="530"/>
-      <c r="P7" s="531"/>
+      <c r="O7" s="621"/>
+      <c r="P7" s="622"/>
       <c r="Q7" s="176"/>
       <c r="R7" s="178"/>
-      <c r="S7" s="533">
+      <c r="S7" s="614">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="534"/>
+      <c r="T7" s="615"/>
       <c r="U7" s="105"/>
       <c r="V7" s="181"/>
       <c r="W7" s="98"/>
-      <c r="X7" s="533">
+      <c r="X7" s="614">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="534"/>
+      <c r="Y7" s="615"/>
       <c r="Z7" s="167"/>
       <c r="AA7" s="119"/>
     </row>
@@ -26298,27 +26290,27 @@
       <c r="D10" s="160"/>
       <c r="E10" s="231"/>
       <c r="F10" s="105"/>
-      <c r="G10" s="525" t="s">
+      <c r="G10" s="646" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="526"/>
-      <c r="I10" s="526"/>
-      <c r="J10" s="526"/>
-      <c r="K10" s="526"/>
-      <c r="L10" s="526"/>
-      <c r="M10" s="526"/>
-      <c r="N10" s="526"/>
-      <c r="O10" s="526"/>
-      <c r="P10" s="526"/>
-      <c r="Q10" s="526"/>
-      <c r="R10" s="526"/>
-      <c r="S10" s="526"/>
-      <c r="T10" s="526"/>
-      <c r="U10" s="526"/>
-      <c r="V10" s="526"/>
-      <c r="W10" s="526"/>
-      <c r="X10" s="526"/>
-      <c r="Y10" s="527"/>
+      <c r="H10" s="647"/>
+      <c r="I10" s="647"/>
+      <c r="J10" s="647"/>
+      <c r="K10" s="647"/>
+      <c r="L10" s="647"/>
+      <c r="M10" s="647"/>
+      <c r="N10" s="647"/>
+      <c r="O10" s="647"/>
+      <c r="P10" s="647"/>
+      <c r="Q10" s="647"/>
+      <c r="R10" s="647"/>
+      <c r="S10" s="647"/>
+      <c r="T10" s="647"/>
+      <c r="U10" s="647"/>
+      <c r="V10" s="647"/>
+      <c r="W10" s="647"/>
+      <c r="X10" s="647"/>
+      <c r="Y10" s="648"/>
       <c r="Z10" s="96"/>
       <c r="AA10" s="119"/>
     </row>
@@ -26329,35 +26321,35 @@
       <c r="D11" s="160"/>
       <c r="E11" s="231"/>
       <c r="F11" s="105"/>
-      <c r="G11" s="528" t="s">
+      <c r="G11" s="649" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="523"/>
-      <c r="I11" s="523" t="s">
+      <c r="H11" s="644"/>
+      <c r="I11" s="644" t="s">
         <v>148</v>
       </c>
-      <c r="J11" s="523"/>
-      <c r="K11" s="523"/>
-      <c r="L11" s="523" t="s">
+      <c r="J11" s="644"/>
+      <c r="K11" s="644"/>
+      <c r="L11" s="644" t="s">
         <v>149</v>
       </c>
-      <c r="M11" s="523"/>
-      <c r="N11" s="523"/>
-      <c r="O11" s="523" t="s">
+      <c r="M11" s="644"/>
+      <c r="N11" s="644"/>
+      <c r="O11" s="644" t="s">
         <v>150</v>
       </c>
-      <c r="P11" s="523"/>
-      <c r="Q11" s="523"/>
-      <c r="R11" s="523" t="s">
+      <c r="P11" s="644"/>
+      <c r="Q11" s="644"/>
+      <c r="R11" s="644" t="s">
         <v>145</v>
       </c>
-      <c r="S11" s="523"/>
-      <c r="T11" s="523"/>
-      <c r="U11" s="523"/>
-      <c r="V11" s="523"/>
-      <c r="W11" s="523"/>
-      <c r="X11" s="523"/>
-      <c r="Y11" s="524"/>
+      <c r="S11" s="644"/>
+      <c r="T11" s="644"/>
+      <c r="U11" s="644"/>
+      <c r="V11" s="644"/>
+      <c r="W11" s="644"/>
+      <c r="X11" s="644"/>
+      <c r="Y11" s="645"/>
       <c r="Z11" s="96"/>
       <c r="AA11" s="119"/>
     </row>
@@ -26368,33 +26360,33 @@
       <c r="D12" s="216"/>
       <c r="E12" s="231"/>
       <c r="F12" s="105"/>
-      <c r="G12" s="528"/>
-      <c r="H12" s="523"/>
-      <c r="I12" s="523"/>
-      <c r="J12" s="523"/>
-      <c r="K12" s="523"/>
-      <c r="L12" s="523"/>
-      <c r="M12" s="523"/>
-      <c r="N12" s="523"/>
-      <c r="O12" s="523"/>
-      <c r="P12" s="523"/>
-      <c r="Q12" s="523"/>
-      <c r="R12" s="499" t="s">
+      <c r="G12" s="649"/>
+      <c r="H12" s="644"/>
+      <c r="I12" s="644"/>
+      <c r="J12" s="644"/>
+      <c r="K12" s="644"/>
+      <c r="L12" s="644"/>
+      <c r="M12" s="644"/>
+      <c r="N12" s="644"/>
+      <c r="O12" s="644"/>
+      <c r="P12" s="644"/>
+      <c r="Q12" s="644"/>
+      <c r="R12" s="571" t="s">
         <v>151</v>
       </c>
-      <c r="S12" s="499"/>
-      <c r="T12" s="499" t="s">
+      <c r="S12" s="571"/>
+      <c r="T12" s="571" t="s">
         <v>152</v>
       </c>
-      <c r="U12" s="499"/>
-      <c r="V12" s="499" t="s">
+      <c r="U12" s="571"/>
+      <c r="V12" s="571" t="s">
         <v>153</v>
       </c>
-      <c r="W12" s="499"/>
-      <c r="X12" s="499" t="s">
+      <c r="W12" s="571"/>
+      <c r="X12" s="571" t="s">
         <v>154</v>
       </c>
-      <c r="Y12" s="520"/>
+      <c r="Y12" s="602"/>
       <c r="Z12" s="96"/>
       <c r="AA12" s="95"/>
     </row>
@@ -26405,25 +26397,25 @@
       <c r="D13" s="160"/>
       <c r="E13" s="231"/>
       <c r="F13" s="105"/>
-      <c r="G13" s="528"/>
-      <c r="H13" s="523"/>
-      <c r="I13" s="523"/>
-      <c r="J13" s="523"/>
-      <c r="K13" s="523"/>
-      <c r="L13" s="523"/>
-      <c r="M13" s="523"/>
-      <c r="N13" s="523"/>
-      <c r="O13" s="523"/>
-      <c r="P13" s="523"/>
-      <c r="Q13" s="523"/>
-      <c r="R13" s="499"/>
-      <c r="S13" s="499"/>
-      <c r="T13" s="499"/>
-      <c r="U13" s="499"/>
-      <c r="V13" s="499"/>
-      <c r="W13" s="499"/>
-      <c r="X13" s="521"/>
-      <c r="Y13" s="522"/>
+      <c r="G13" s="649"/>
+      <c r="H13" s="644"/>
+      <c r="I13" s="644"/>
+      <c r="J13" s="644"/>
+      <c r="K13" s="644"/>
+      <c r="L13" s="644"/>
+      <c r="M13" s="644"/>
+      <c r="N13" s="644"/>
+      <c r="O13" s="644"/>
+      <c r="P13" s="644"/>
+      <c r="Q13" s="644"/>
+      <c r="R13" s="571"/>
+      <c r="S13" s="571"/>
+      <c r="T13" s="571"/>
+      <c r="U13" s="571"/>
+      <c r="V13" s="571"/>
+      <c r="W13" s="571"/>
+      <c r="X13" s="642"/>
+      <c r="Y13" s="643"/>
       <c r="Z13" s="96"/>
       <c r="AA13" s="97"/>
     </row>
@@ -26434,25 +26426,25 @@
       <c r="D14" s="160"/>
       <c r="E14" s="231"/>
       <c r="F14" s="105"/>
-      <c r="G14" s="500"/>
-      <c r="H14" s="501"/>
-      <c r="I14" s="502"/>
-      <c r="J14" s="503"/>
-      <c r="K14" s="504"/>
-      <c r="L14" s="496"/>
-      <c r="M14" s="496"/>
-      <c r="N14" s="496"/>
-      <c r="O14" s="496"/>
-      <c r="P14" s="496"/>
-      <c r="Q14" s="496"/>
-      <c r="R14" s="496"/>
-      <c r="S14" s="496"/>
-      <c r="T14" s="496"/>
-      <c r="U14" s="496"/>
-      <c r="V14" s="496"/>
-      <c r="W14" s="502"/>
-      <c r="X14" s="496"/>
-      <c r="Y14" s="532"/>
+      <c r="G14" s="623"/>
+      <c r="H14" s="624"/>
+      <c r="I14" s="601"/>
+      <c r="J14" s="625"/>
+      <c r="K14" s="626"/>
+      <c r="L14" s="599"/>
+      <c r="M14" s="599"/>
+      <c r="N14" s="599"/>
+      <c r="O14" s="599"/>
+      <c r="P14" s="599"/>
+      <c r="Q14" s="599"/>
+      <c r="R14" s="599"/>
+      <c r="S14" s="599"/>
+      <c r="T14" s="599"/>
+      <c r="U14" s="599"/>
+      <c r="V14" s="599"/>
+      <c r="W14" s="601"/>
+      <c r="X14" s="599"/>
+      <c r="Y14" s="600"/>
       <c r="Z14" s="96"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -26462,25 +26454,25 @@
       <c r="D15" s="217"/>
       <c r="E15" s="232"/>
       <c r="F15" s="105"/>
-      <c r="G15" s="500"/>
-      <c r="H15" s="501"/>
-      <c r="I15" s="502"/>
-      <c r="J15" s="503"/>
-      <c r="K15" s="504"/>
-      <c r="L15" s="496"/>
-      <c r="M15" s="496"/>
-      <c r="N15" s="496"/>
-      <c r="O15" s="496"/>
-      <c r="P15" s="496"/>
-      <c r="Q15" s="496"/>
-      <c r="R15" s="496"/>
-      <c r="S15" s="496"/>
-      <c r="T15" s="496"/>
-      <c r="U15" s="496"/>
-      <c r="V15" s="496"/>
-      <c r="W15" s="502"/>
-      <c r="X15" s="496"/>
-      <c r="Y15" s="532"/>
+      <c r="G15" s="623"/>
+      <c r="H15" s="624"/>
+      <c r="I15" s="601"/>
+      <c r="J15" s="625"/>
+      <c r="K15" s="626"/>
+      <c r="L15" s="599"/>
+      <c r="M15" s="599"/>
+      <c r="N15" s="599"/>
+      <c r="O15" s="599"/>
+      <c r="P15" s="599"/>
+      <c r="Q15" s="599"/>
+      <c r="R15" s="599"/>
+      <c r="S15" s="599"/>
+      <c r="T15" s="599"/>
+      <c r="U15" s="599"/>
+      <c r="V15" s="599"/>
+      <c r="W15" s="601"/>
+      <c r="X15" s="599"/>
+      <c r="Y15" s="600"/>
       <c r="Z15" s="96"/>
       <c r="AA15" s="119"/>
     </row>
@@ -26491,57 +26483,57 @@
       <c r="D16" s="125"/>
       <c r="E16" s="125"/>
       <c r="F16" s="95"/>
-      <c r="G16" s="500"/>
-      <c r="H16" s="501"/>
-      <c r="I16" s="502"/>
-      <c r="J16" s="503"/>
-      <c r="K16" s="504"/>
-      <c r="L16" s="496"/>
-      <c r="M16" s="496"/>
-      <c r="N16" s="496"/>
-      <c r="O16" s="496"/>
-      <c r="P16" s="496"/>
-      <c r="Q16" s="496"/>
-      <c r="R16" s="496"/>
-      <c r="S16" s="496"/>
-      <c r="T16" s="496"/>
-      <c r="U16" s="496"/>
-      <c r="V16" s="496"/>
-      <c r="W16" s="502"/>
-      <c r="X16" s="496"/>
-      <c r="Y16" s="532"/>
+      <c r="G16" s="623"/>
+      <c r="H16" s="624"/>
+      <c r="I16" s="601"/>
+      <c r="J16" s="625"/>
+      <c r="K16" s="626"/>
+      <c r="L16" s="599"/>
+      <c r="M16" s="599"/>
+      <c r="N16" s="599"/>
+      <c r="O16" s="599"/>
+      <c r="P16" s="599"/>
+      <c r="Q16" s="599"/>
+      <c r="R16" s="599"/>
+      <c r="S16" s="599"/>
+      <c r="T16" s="599"/>
+      <c r="U16" s="599"/>
+      <c r="V16" s="599"/>
+      <c r="W16" s="601"/>
+      <c r="X16" s="599"/>
+      <c r="Y16" s="600"/>
       <c r="Z16" s="96"/>
       <c r="AA16" s="119"/>
       <c r="AB16" s="226"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="95"/>
-      <c r="B17" s="514" t="s">
+      <c r="B17" s="636" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="515"/>
-      <c r="D17" s="515"/>
-      <c r="E17" s="516"/>
+      <c r="C17" s="637"/>
+      <c r="D17" s="637"/>
+      <c r="E17" s="638"/>
       <c r="F17" s="105"/>
-      <c r="G17" s="500"/>
-      <c r="H17" s="501"/>
-      <c r="I17" s="502"/>
-      <c r="J17" s="503"/>
-      <c r="K17" s="504"/>
-      <c r="L17" s="496"/>
-      <c r="M17" s="496"/>
-      <c r="N17" s="496"/>
-      <c r="O17" s="496"/>
-      <c r="P17" s="496"/>
-      <c r="Q17" s="496"/>
-      <c r="R17" s="496"/>
-      <c r="S17" s="496"/>
-      <c r="T17" s="496"/>
-      <c r="U17" s="496"/>
-      <c r="V17" s="496"/>
-      <c r="W17" s="502"/>
-      <c r="X17" s="496"/>
-      <c r="Y17" s="532"/>
+      <c r="G17" s="623"/>
+      <c r="H17" s="624"/>
+      <c r="I17" s="601"/>
+      <c r="J17" s="625"/>
+      <c r="K17" s="626"/>
+      <c r="L17" s="599"/>
+      <c r="M17" s="599"/>
+      <c r="N17" s="599"/>
+      <c r="O17" s="599"/>
+      <c r="P17" s="599"/>
+      <c r="Q17" s="599"/>
+      <c r="R17" s="599"/>
+      <c r="S17" s="599"/>
+      <c r="T17" s="599"/>
+      <c r="U17" s="599"/>
+      <c r="V17" s="599"/>
+      <c r="W17" s="601"/>
+      <c r="X17" s="599"/>
+      <c r="Y17" s="600"/>
       <c r="Z17" s="96"/>
       <c r="AA17" s="119"/>
     </row>
@@ -26560,25 +26552,25 @@
         <v>158</v>
       </c>
       <c r="F18" s="105"/>
-      <c r="G18" s="500"/>
-      <c r="H18" s="501"/>
-      <c r="I18" s="502"/>
-      <c r="J18" s="503"/>
-      <c r="K18" s="504"/>
-      <c r="L18" s="496"/>
-      <c r="M18" s="496"/>
-      <c r="N18" s="496"/>
-      <c r="O18" s="496"/>
-      <c r="P18" s="496"/>
-      <c r="Q18" s="496"/>
-      <c r="R18" s="496"/>
-      <c r="S18" s="496"/>
-      <c r="T18" s="496"/>
-      <c r="U18" s="496"/>
-      <c r="V18" s="496"/>
-      <c r="W18" s="502"/>
-      <c r="X18" s="496"/>
-      <c r="Y18" s="532"/>
+      <c r="G18" s="623"/>
+      <c r="H18" s="624"/>
+      <c r="I18" s="601"/>
+      <c r="J18" s="625"/>
+      <c r="K18" s="626"/>
+      <c r="L18" s="599"/>
+      <c r="M18" s="599"/>
+      <c r="N18" s="599"/>
+      <c r="O18" s="599"/>
+      <c r="P18" s="599"/>
+      <c r="Q18" s="599"/>
+      <c r="R18" s="599"/>
+      <c r="S18" s="599"/>
+      <c r="T18" s="599"/>
+      <c r="U18" s="599"/>
+      <c r="V18" s="599"/>
+      <c r="W18" s="601"/>
+      <c r="X18" s="599"/>
+      <c r="Y18" s="600"/>
       <c r="Z18" s="96"/>
       <c r="AA18" s="119"/>
     </row>
@@ -26589,25 +26581,25 @@
       <c r="D19" s="165"/>
       <c r="E19" s="233"/>
       <c r="F19" s="105"/>
-      <c r="G19" s="500"/>
-      <c r="H19" s="501"/>
-      <c r="I19" s="502"/>
-      <c r="J19" s="503"/>
-      <c r="K19" s="504"/>
-      <c r="L19" s="496"/>
-      <c r="M19" s="496"/>
-      <c r="N19" s="496"/>
-      <c r="O19" s="496"/>
-      <c r="P19" s="496"/>
-      <c r="Q19" s="496"/>
-      <c r="R19" s="496"/>
-      <c r="S19" s="496"/>
-      <c r="T19" s="496"/>
-      <c r="U19" s="496"/>
-      <c r="V19" s="496"/>
-      <c r="W19" s="502"/>
-      <c r="X19" s="496"/>
-      <c r="Y19" s="532"/>
+      <c r="G19" s="623"/>
+      <c r="H19" s="624"/>
+      <c r="I19" s="601"/>
+      <c r="J19" s="625"/>
+      <c r="K19" s="626"/>
+      <c r="L19" s="599"/>
+      <c r="M19" s="599"/>
+      <c r="N19" s="599"/>
+      <c r="O19" s="599"/>
+      <c r="P19" s="599"/>
+      <c r="Q19" s="599"/>
+      <c r="R19" s="599"/>
+      <c r="S19" s="599"/>
+      <c r="T19" s="599"/>
+      <c r="U19" s="599"/>
+      <c r="V19" s="599"/>
+      <c r="W19" s="601"/>
+      <c r="X19" s="599"/>
+      <c r="Y19" s="600"/>
       <c r="Z19" s="96"/>
       <c r="AA19" s="119"/>
     </row>
@@ -26618,25 +26610,25 @@
       <c r="D20" s="165"/>
       <c r="E20" s="233"/>
       <c r="F20" s="105"/>
-      <c r="G20" s="500"/>
-      <c r="H20" s="501"/>
-      <c r="I20" s="502"/>
-      <c r="J20" s="503"/>
-      <c r="K20" s="504"/>
-      <c r="L20" s="496"/>
-      <c r="M20" s="496"/>
-      <c r="N20" s="496"/>
-      <c r="O20" s="496"/>
-      <c r="P20" s="496"/>
-      <c r="Q20" s="496"/>
-      <c r="R20" s="496"/>
-      <c r="S20" s="496"/>
-      <c r="T20" s="496"/>
-      <c r="U20" s="496"/>
-      <c r="V20" s="496"/>
-      <c r="W20" s="502"/>
-      <c r="X20" s="496"/>
-      <c r="Y20" s="532"/>
+      <c r="G20" s="623"/>
+      <c r="H20" s="624"/>
+      <c r="I20" s="601"/>
+      <c r="J20" s="625"/>
+      <c r="K20" s="626"/>
+      <c r="L20" s="599"/>
+      <c r="M20" s="599"/>
+      <c r="N20" s="599"/>
+      <c r="O20" s="599"/>
+      <c r="P20" s="599"/>
+      <c r="Q20" s="599"/>
+      <c r="R20" s="599"/>
+      <c r="S20" s="599"/>
+      <c r="T20" s="599"/>
+      <c r="U20" s="599"/>
+      <c r="V20" s="599"/>
+      <c r="W20" s="601"/>
+      <c r="X20" s="599"/>
+      <c r="Y20" s="600"/>
       <c r="Z20" s="96"/>
       <c r="AA20" s="119"/>
     </row>
@@ -26647,25 +26639,25 @@
       <c r="D21" s="165"/>
       <c r="E21" s="233"/>
       <c r="F21" s="105"/>
-      <c r="G21" s="500"/>
-      <c r="H21" s="501"/>
-      <c r="I21" s="502"/>
-      <c r="J21" s="503"/>
-      <c r="K21" s="504"/>
-      <c r="L21" s="496"/>
-      <c r="M21" s="496"/>
-      <c r="N21" s="496"/>
-      <c r="O21" s="496"/>
-      <c r="P21" s="496"/>
-      <c r="Q21" s="496"/>
-      <c r="R21" s="496"/>
-      <c r="S21" s="496"/>
-      <c r="T21" s="496"/>
-      <c r="U21" s="496"/>
-      <c r="V21" s="496"/>
-      <c r="W21" s="502"/>
-      <c r="X21" s="496"/>
-      <c r="Y21" s="532"/>
+      <c r="G21" s="623"/>
+      <c r="H21" s="624"/>
+      <c r="I21" s="601"/>
+      <c r="J21" s="625"/>
+      <c r="K21" s="626"/>
+      <c r="L21" s="599"/>
+      <c r="M21" s="599"/>
+      <c r="N21" s="599"/>
+      <c r="O21" s="599"/>
+      <c r="P21" s="599"/>
+      <c r="Q21" s="599"/>
+      <c r="R21" s="599"/>
+      <c r="S21" s="599"/>
+      <c r="T21" s="599"/>
+      <c r="U21" s="599"/>
+      <c r="V21" s="599"/>
+      <c r="W21" s="601"/>
+      <c r="X21" s="599"/>
+      <c r="Y21" s="600"/>
       <c r="Z21" s="96"/>
       <c r="AA21" s="119"/>
     </row>
@@ -26676,25 +26668,25 @@
       <c r="D22" s="165"/>
       <c r="E22" s="233"/>
       <c r="F22" s="105"/>
-      <c r="G22" s="500"/>
-      <c r="H22" s="501"/>
-      <c r="I22" s="502"/>
-      <c r="J22" s="503"/>
-      <c r="K22" s="504"/>
-      <c r="L22" s="496"/>
-      <c r="M22" s="496"/>
-      <c r="N22" s="496"/>
-      <c r="O22" s="496"/>
-      <c r="P22" s="496"/>
-      <c r="Q22" s="496"/>
-      <c r="R22" s="496"/>
-      <c r="S22" s="496"/>
-      <c r="T22" s="496"/>
-      <c r="U22" s="496"/>
-      <c r="V22" s="496"/>
-      <c r="W22" s="502"/>
-      <c r="X22" s="496"/>
-      <c r="Y22" s="532"/>
+      <c r="G22" s="623"/>
+      <c r="H22" s="624"/>
+      <c r="I22" s="601"/>
+      <c r="J22" s="625"/>
+      <c r="K22" s="626"/>
+      <c r="L22" s="599"/>
+      <c r="M22" s="599"/>
+      <c r="N22" s="599"/>
+      <c r="O22" s="599"/>
+      <c r="P22" s="599"/>
+      <c r="Q22" s="599"/>
+      <c r="R22" s="599"/>
+      <c r="S22" s="599"/>
+      <c r="T22" s="599"/>
+      <c r="U22" s="599"/>
+      <c r="V22" s="599"/>
+      <c r="W22" s="601"/>
+      <c r="X22" s="599"/>
+      <c r="Y22" s="600"/>
       <c r="Z22" s="96"/>
       <c r="AA22" s="119"/>
     </row>
@@ -26705,48 +26697,48 @@
       <c r="D23" s="187"/>
       <c r="E23" s="234"/>
       <c r="F23" s="105"/>
-      <c r="G23" s="543" t="s">
+      <c r="G23" s="611" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="535"/>
-      <c r="I23" s="535">
+      <c r="H23" s="603"/>
+      <c r="I23" s="603">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="535"/>
-      <c r="K23" s="535"/>
-      <c r="L23" s="535">
+      <c r="J23" s="603"/>
+      <c r="K23" s="603"/>
+      <c r="L23" s="603">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="535"/>
-      <c r="N23" s="535"/>
-      <c r="O23" s="540">
+      <c r="M23" s="603"/>
+      <c r="N23" s="603"/>
+      <c r="O23" s="608">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="541"/>
-      <c r="Q23" s="542"/>
-      <c r="R23" s="540">
+      <c r="P23" s="609"/>
+      <c r="Q23" s="610"/>
+      <c r="R23" s="608">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="542"/>
-      <c r="T23" s="540">
+      <c r="S23" s="610"/>
+      <c r="T23" s="608">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="542"/>
-      <c r="V23" s="540">
+      <c r="U23" s="610"/>
+      <c r="V23" s="608">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="541"/>
-      <c r="X23" s="535">
+      <c r="W23" s="609"/>
+      <c r="X23" s="603">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="536"/>
+      <c r="Y23" s="604"/>
       <c r="Z23" s="96"/>
       <c r="AA23" s="119"/>
     </row>
@@ -26816,28 +26808,28 @@
       <c r="E26" s="98"/>
       <c r="F26" s="95"/>
       <c r="G26" s="161"/>
-      <c r="H26" s="580" t="s">
+      <c r="H26" s="566" t="s">
         <v>170</v>
       </c>
-      <c r="I26" s="581"/>
-      <c r="J26" s="582"/>
+      <c r="I26" s="567"/>
+      <c r="J26" s="568"/>
       <c r="K26" s="105"/>
-      <c r="L26" s="586" t="s">
+      <c r="L26" s="575" t="s">
         <v>163</v>
       </c>
-      <c r="M26" s="587"/>
-      <c r="N26" s="587"/>
-      <c r="O26" s="587"/>
-      <c r="P26" s="587"/>
-      <c r="Q26" s="587"/>
-      <c r="R26" s="587"/>
-      <c r="S26" s="587"/>
-      <c r="T26" s="587"/>
-      <c r="U26" s="587"/>
-      <c r="V26" s="587"/>
-      <c r="W26" s="587"/>
-      <c r="X26" s="587"/>
-      <c r="Y26" s="588"/>
+      <c r="M26" s="576"/>
+      <c r="N26" s="576"/>
+      <c r="O26" s="576"/>
+      <c r="P26" s="576"/>
+      <c r="Q26" s="576"/>
+      <c r="R26" s="576"/>
+      <c r="S26" s="576"/>
+      <c r="T26" s="576"/>
+      <c r="U26" s="576"/>
+      <c r="V26" s="576"/>
+      <c r="W26" s="576"/>
+      <c r="X26" s="576"/>
+      <c r="Y26" s="577"/>
       <c r="Z26" s="96"/>
       <c r="AA26" s="119"/>
     </row>
@@ -26849,41 +26841,41 @@
       <c r="E27" s="98"/>
       <c r="F27" s="95"/>
       <c r="G27" s="162"/>
-      <c r="H27" s="577">
+      <c r="H27" s="548">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="578"/>
-      <c r="J27" s="579"/>
+      <c r="I27" s="549"/>
+      <c r="J27" s="550"/>
       <c r="K27" s="105"/>
-      <c r="L27" s="551" t="s">
+      <c r="L27" s="597" t="s">
         <v>147</v>
       </c>
-      <c r="M27" s="499"/>
-      <c r="N27" s="499"/>
-      <c r="O27" s="499" t="s">
+      <c r="M27" s="571"/>
+      <c r="N27" s="571"/>
+      <c r="O27" s="571" t="s">
         <v>164</v>
       </c>
-      <c r="P27" s="499"/>
-      <c r="Q27" s="499" t="s">
+      <c r="P27" s="571"/>
+      <c r="Q27" s="571" t="s">
         <v>165</v>
       </c>
-      <c r="R27" s="499"/>
-      <c r="S27" s="499" t="s">
+      <c r="R27" s="571"/>
+      <c r="S27" s="571" t="s">
         <v>166</v>
       </c>
-      <c r="T27" s="499" t="s">
+      <c r="T27" s="571" t="s">
         <v>167</v>
       </c>
-      <c r="U27" s="499"/>
-      <c r="V27" s="499" t="s">
+      <c r="U27" s="571"/>
+      <c r="V27" s="571" t="s">
         <v>168</v>
       </c>
-      <c r="W27" s="499" t="s">
+      <c r="W27" s="571" t="s">
         <v>169</v>
       </c>
-      <c r="X27" s="499"/>
-      <c r="Y27" s="520" t="s">
+      <c r="X27" s="571"/>
+      <c r="Y27" s="602" t="s">
         <v>155</v>
       </c>
       <c r="Z27" s="96"/>
@@ -26901,20 +26893,20 @@
       <c r="I28" s="98"/>
       <c r="J28" s="193"/>
       <c r="K28" s="105"/>
-      <c r="L28" s="551"/>
-      <c r="M28" s="499"/>
-      <c r="N28" s="499"/>
-      <c r="O28" s="499"/>
-      <c r="P28" s="499"/>
-      <c r="Q28" s="499"/>
-      <c r="R28" s="499"/>
-      <c r="S28" s="499"/>
-      <c r="T28" s="499"/>
-      <c r="U28" s="499"/>
-      <c r="V28" s="499"/>
-      <c r="W28" s="499"/>
-      <c r="X28" s="499"/>
-      <c r="Y28" s="520"/>
+      <c r="L28" s="597"/>
+      <c r="M28" s="571"/>
+      <c r="N28" s="571"/>
+      <c r="O28" s="571"/>
+      <c r="P28" s="571"/>
+      <c r="Q28" s="571"/>
+      <c r="R28" s="571"/>
+      <c r="S28" s="571"/>
+      <c r="T28" s="571"/>
+      <c r="U28" s="571"/>
+      <c r="V28" s="571"/>
+      <c r="W28" s="571"/>
+      <c r="X28" s="571"/>
+      <c r="Y28" s="602"/>
       <c r="Z28" s="96"/>
       <c r="AA28" s="119"/>
     </row>
@@ -26930,19 +26922,19 @@
       <c r="I29" s="194"/>
       <c r="J29" s="164"/>
       <c r="K29" s="105"/>
-      <c r="L29" s="548"/>
-      <c r="M29" s="549"/>
-      <c r="N29" s="549"/>
-      <c r="O29" s="549"/>
-      <c r="P29" s="549"/>
-      <c r="Q29" s="549"/>
-      <c r="R29" s="549"/>
+      <c r="L29" s="583"/>
+      <c r="M29" s="551"/>
+      <c r="N29" s="551"/>
+      <c r="O29" s="551"/>
+      <c r="P29" s="551"/>
+      <c r="Q29" s="551"/>
+      <c r="R29" s="551"/>
       <c r="S29" s="87"/>
-      <c r="T29" s="549"/>
-      <c r="U29" s="549"/>
+      <c r="T29" s="551"/>
+      <c r="U29" s="551"/>
       <c r="V29" s="87"/>
-      <c r="W29" s="549"/>
-      <c r="X29" s="550"/>
+      <c r="W29" s="551"/>
+      <c r="X29" s="552"/>
       <c r="Y29" s="227"/>
       <c r="Z29" s="96"/>
       <c r="AA29" s="119"/>
@@ -26959,19 +26951,19 @@
       <c r="I30" s="125"/>
       <c r="J30" s="125"/>
       <c r="K30" s="95"/>
-      <c r="L30" s="548"/>
-      <c r="M30" s="549"/>
-      <c r="N30" s="549"/>
-      <c r="O30" s="549"/>
-      <c r="P30" s="549"/>
-      <c r="Q30" s="549"/>
-      <c r="R30" s="549"/>
+      <c r="L30" s="583"/>
+      <c r="M30" s="551"/>
+      <c r="N30" s="551"/>
+      <c r="O30" s="551"/>
+      <c r="P30" s="551"/>
+      <c r="Q30" s="551"/>
+      <c r="R30" s="551"/>
       <c r="S30" s="87"/>
-      <c r="T30" s="549"/>
-      <c r="U30" s="549"/>
+      <c r="T30" s="551"/>
+      <c r="U30" s="551"/>
       <c r="V30" s="87"/>
-      <c r="W30" s="549"/>
-      <c r="X30" s="550"/>
+      <c r="W30" s="551"/>
+      <c r="X30" s="552"/>
       <c r="Y30" s="227"/>
       <c r="Z30" s="96"/>
       <c r="AA30" s="95"/>
@@ -26984,25 +26976,25 @@
       <c r="E31" s="98"/>
       <c r="F31" s="95"/>
       <c r="G31" s="161"/>
-      <c r="H31" s="583" t="s">
+      <c r="H31" s="572" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="584"/>
-      <c r="J31" s="585"/>
+      <c r="I31" s="573"/>
+      <c r="J31" s="574"/>
       <c r="K31" s="105"/>
-      <c r="L31" s="548"/>
-      <c r="M31" s="549"/>
-      <c r="N31" s="549"/>
-      <c r="O31" s="549"/>
-      <c r="P31" s="549"/>
-      <c r="Q31" s="549"/>
-      <c r="R31" s="549"/>
+      <c r="L31" s="583"/>
+      <c r="M31" s="551"/>
+      <c r="N31" s="551"/>
+      <c r="O31" s="551"/>
+      <c r="P31" s="551"/>
+      <c r="Q31" s="551"/>
+      <c r="R31" s="551"/>
       <c r="S31" s="87"/>
-      <c r="T31" s="549"/>
-      <c r="U31" s="549"/>
+      <c r="T31" s="551"/>
+      <c r="U31" s="551"/>
       <c r="V31" s="87"/>
-      <c r="W31" s="549"/>
-      <c r="X31" s="550"/>
+      <c r="W31" s="551"/>
+      <c r="X31" s="552"/>
       <c r="Y31" s="227"/>
       <c r="Z31" s="96"/>
       <c r="AA31" s="95"/>
@@ -27019,19 +27011,19 @@
       <c r="I32" s="98"/>
       <c r="J32" s="193"/>
       <c r="K32" s="105"/>
-      <c r="L32" s="548"/>
-      <c r="M32" s="549"/>
-      <c r="N32" s="549"/>
-      <c r="O32" s="549"/>
-      <c r="P32" s="549"/>
-      <c r="Q32" s="549"/>
-      <c r="R32" s="549"/>
+      <c r="L32" s="583"/>
+      <c r="M32" s="551"/>
+      <c r="N32" s="551"/>
+      <c r="O32" s="551"/>
+      <c r="P32" s="551"/>
+      <c r="Q32" s="551"/>
+      <c r="R32" s="551"/>
       <c r="S32" s="87"/>
-      <c r="T32" s="549"/>
-      <c r="U32" s="549"/>
+      <c r="T32" s="551"/>
+      <c r="U32" s="551"/>
       <c r="V32" s="87"/>
-      <c r="W32" s="549"/>
-      <c r="X32" s="550"/>
+      <c r="W32" s="551"/>
+      <c r="X32" s="552"/>
       <c r="Y32" s="227"/>
       <c r="Z32" s="96"/>
       <c r="AA32" s="95"/>
@@ -27044,26 +27036,26 @@
       <c r="E33" s="98"/>
       <c r="F33" s="95"/>
       <c r="G33" s="162"/>
-      <c r="H33" s="577">
+      <c r="H33" s="548">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="578"/>
-      <c r="J33" s="579"/>
+      <c r="I33" s="549"/>
+      <c r="J33" s="550"/>
       <c r="K33" s="105"/>
-      <c r="L33" s="548"/>
-      <c r="M33" s="549"/>
-      <c r="N33" s="549"/>
-      <c r="O33" s="549"/>
-      <c r="P33" s="549"/>
-      <c r="Q33" s="549"/>
-      <c r="R33" s="549"/>
+      <c r="L33" s="583"/>
+      <c r="M33" s="551"/>
+      <c r="N33" s="551"/>
+      <c r="O33" s="551"/>
+      <c r="P33" s="551"/>
+      <c r="Q33" s="551"/>
+      <c r="R33" s="551"/>
       <c r="S33" s="87"/>
-      <c r="T33" s="549"/>
-      <c r="U33" s="549"/>
+      <c r="T33" s="551"/>
+      <c r="U33" s="551"/>
       <c r="V33" s="87"/>
-      <c r="W33" s="549"/>
-      <c r="X33" s="550"/>
+      <c r="W33" s="551"/>
+      <c r="X33" s="552"/>
       <c r="Y33" s="227"/>
       <c r="Z33" s="96"/>
       <c r="AA33" s="225"/>
@@ -27080,19 +27072,19 @@
       <c r="I34" s="98"/>
       <c r="J34" s="193"/>
       <c r="K34" s="105"/>
-      <c r="L34" s="548"/>
-      <c r="M34" s="549"/>
-      <c r="N34" s="549"/>
-      <c r="O34" s="549"/>
-      <c r="P34" s="549"/>
-      <c r="Q34" s="549"/>
-      <c r="R34" s="549"/>
+      <c r="L34" s="583"/>
+      <c r="M34" s="551"/>
+      <c r="N34" s="551"/>
+      <c r="O34" s="551"/>
+      <c r="P34" s="551"/>
+      <c r="Q34" s="551"/>
+      <c r="R34" s="551"/>
       <c r="S34" s="87"/>
-      <c r="T34" s="549"/>
-      <c r="U34" s="549"/>
+      <c r="T34" s="551"/>
+      <c r="U34" s="551"/>
       <c r="V34" s="87"/>
-      <c r="W34" s="549"/>
-      <c r="X34" s="550"/>
+      <c r="W34" s="551"/>
+      <c r="X34" s="552"/>
       <c r="Y34" s="227"/>
       <c r="Z34" s="96"/>
       <c r="AA34" s="95"/>
@@ -27109,19 +27101,19 @@
       <c r="I35" s="194"/>
       <c r="J35" s="164"/>
       <c r="K35" s="105"/>
-      <c r="L35" s="548"/>
-      <c r="M35" s="549"/>
-      <c r="N35" s="549"/>
-      <c r="O35" s="552"/>
-      <c r="P35" s="552"/>
-      <c r="Q35" s="552"/>
-      <c r="R35" s="552"/>
+      <c r="L35" s="583"/>
+      <c r="M35" s="551"/>
+      <c r="N35" s="551"/>
+      <c r="O35" s="578"/>
+      <c r="P35" s="578"/>
+      <c r="Q35" s="578"/>
+      <c r="R35" s="578"/>
       <c r="S35" s="190"/>
-      <c r="T35" s="552"/>
-      <c r="U35" s="552"/>
+      <c r="T35" s="578"/>
+      <c r="U35" s="578"/>
       <c r="V35" s="190"/>
-      <c r="W35" s="552"/>
-      <c r="X35" s="553"/>
+      <c r="W35" s="578"/>
+      <c r="X35" s="598"/>
       <c r="Y35" s="227"/>
       <c r="Z35" s="96"/>
       <c r="AA35" s="119"/>
@@ -27138,19 +27130,19 @@
       <c r="I36" s="125"/>
       <c r="J36" s="125"/>
       <c r="K36" s="95"/>
-      <c r="L36" s="548"/>
-      <c r="M36" s="549"/>
-      <c r="N36" s="550"/>
-      <c r="O36" s="554"/>
-      <c r="P36" s="554"/>
-      <c r="Q36" s="554"/>
-      <c r="R36" s="554"/>
+      <c r="L36" s="583"/>
+      <c r="M36" s="551"/>
+      <c r="N36" s="552"/>
+      <c r="O36" s="555"/>
+      <c r="P36" s="555"/>
+      <c r="Q36" s="555"/>
+      <c r="R36" s="555"/>
       <c r="S36" s="191"/>
-      <c r="T36" s="554"/>
-      <c r="U36" s="554"/>
+      <c r="T36" s="555"/>
+      <c r="U36" s="555"/>
       <c r="V36" s="191"/>
-      <c r="W36" s="554"/>
-      <c r="X36" s="555"/>
+      <c r="W36" s="555"/>
+      <c r="X36" s="579"/>
       <c r="Y36" s="227"/>
       <c r="Z36" s="96"/>
       <c r="AA36" s="95"/>
@@ -27163,25 +27155,25 @@
       <c r="E37" s="98"/>
       <c r="F37" s="95"/>
       <c r="G37" s="161"/>
-      <c r="H37" s="583" t="s">
+      <c r="H37" s="572" t="s">
         <v>159</v>
       </c>
-      <c r="I37" s="584"/>
-      <c r="J37" s="585"/>
+      <c r="I37" s="573"/>
+      <c r="J37" s="574"/>
       <c r="K37" s="105"/>
-      <c r="L37" s="548"/>
-      <c r="M37" s="549"/>
-      <c r="N37" s="550"/>
-      <c r="O37" s="554"/>
-      <c r="P37" s="554"/>
-      <c r="Q37" s="554"/>
-      <c r="R37" s="554"/>
+      <c r="L37" s="583"/>
+      <c r="M37" s="551"/>
+      <c r="N37" s="552"/>
+      <c r="O37" s="555"/>
+      <c r="P37" s="555"/>
+      <c r="Q37" s="555"/>
+      <c r="R37" s="555"/>
       <c r="S37" s="191"/>
-      <c r="T37" s="554"/>
-      <c r="U37" s="554"/>
+      <c r="T37" s="555"/>
+      <c r="U37" s="555"/>
       <c r="V37" s="191"/>
-      <c r="W37" s="554"/>
-      <c r="X37" s="555"/>
+      <c r="W37" s="555"/>
+      <c r="X37" s="579"/>
       <c r="Y37" s="227"/>
       <c r="Z37" s="96"/>
     </row>
@@ -27197,11 +27189,11 @@
       <c r="I38" s="98"/>
       <c r="J38" s="193"/>
       <c r="K38" s="105"/>
-      <c r="L38" s="567" t="s">
+      <c r="L38" s="591" t="s">
         <v>155</v>
       </c>
-      <c r="M38" s="568"/>
-      <c r="N38" s="569"/>
+      <c r="M38" s="592"/>
+      <c r="N38" s="593"/>
       <c r="O38" s="556">
         <f>SUM(O29:P37)</f>
         <v>0</v>
@@ -27245,26 +27237,26 @@
       <c r="E39" s="98"/>
       <c r="F39" s="95"/>
       <c r="G39" s="162"/>
-      <c r="H39" s="577">
+      <c r="H39" s="548">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="578"/>
-      <c r="J39" s="579"/>
+      <c r="I39" s="549"/>
+      <c r="J39" s="550"/>
       <c r="K39" s="105"/>
-      <c r="L39" s="562"/>
-      <c r="M39" s="570"/>
-      <c r="N39" s="571"/>
-      <c r="O39" s="562"/>
-      <c r="P39" s="563"/>
-      <c r="Q39" s="575"/>
-      <c r="R39" s="576"/>
+      <c r="L39" s="586"/>
+      <c r="M39" s="594"/>
+      <c r="N39" s="595"/>
+      <c r="O39" s="586"/>
+      <c r="P39" s="587"/>
+      <c r="Q39" s="569"/>
+      <c r="R39" s="570"/>
       <c r="S39" s="123"/>
-      <c r="T39" s="603"/>
-      <c r="U39" s="603"/>
+      <c r="T39" s="557"/>
+      <c r="U39" s="557"/>
       <c r="V39" s="123"/>
-      <c r="W39" s="603"/>
-      <c r="X39" s="603"/>
+      <c r="W39" s="557"/>
+      <c r="X39" s="557"/>
       <c r="Y39" s="154"/>
       <c r="Z39" s="98"/>
       <c r="AA39" s="95"/>
@@ -27281,19 +27273,19 @@
       <c r="I40" s="98"/>
       <c r="J40" s="193"/>
       <c r="K40" s="105"/>
-      <c r="L40" s="572"/>
-      <c r="M40" s="573"/>
-      <c r="N40" s="574"/>
-      <c r="O40" s="564"/>
-      <c r="P40" s="561"/>
-      <c r="Q40" s="560"/>
-      <c r="R40" s="561"/>
+      <c r="L40" s="559"/>
+      <c r="M40" s="596"/>
+      <c r="N40" s="560"/>
+      <c r="O40" s="588"/>
+      <c r="P40" s="585"/>
+      <c r="Q40" s="584"/>
+      <c r="R40" s="585"/>
       <c r="S40" s="98"/>
-      <c r="T40" s="604"/>
-      <c r="U40" s="604"/>
+      <c r="T40" s="558"/>
+      <c r="U40" s="558"/>
       <c r="V40" s="98"/>
-      <c r="W40" s="604"/>
-      <c r="X40" s="604"/>
+      <c r="W40" s="558"/>
+      <c r="X40" s="558"/>
       <c r="Y40" s="166"/>
       <c r="Z40" s="98"/>
     </row>
@@ -27309,19 +27301,19 @@
       <c r="I41" s="194"/>
       <c r="J41" s="164"/>
       <c r="K41" s="105"/>
-      <c r="L41" s="572"/>
-      <c r="M41" s="573"/>
-      <c r="N41" s="574"/>
-      <c r="O41" s="565"/>
-      <c r="P41" s="566"/>
-      <c r="Q41" s="572"/>
-      <c r="R41" s="574"/>
+      <c r="L41" s="559"/>
+      <c r="M41" s="596"/>
+      <c r="N41" s="560"/>
+      <c r="O41" s="589"/>
+      <c r="P41" s="590"/>
+      <c r="Q41" s="559"/>
+      <c r="R41" s="560"/>
       <c r="S41" s="98"/>
-      <c r="T41" s="572"/>
-      <c r="U41" s="574"/>
+      <c r="T41" s="559"/>
+      <c r="U41" s="560"/>
       <c r="V41" s="98"/>
-      <c r="W41" s="572"/>
-      <c r="X41" s="574"/>
+      <c r="W41" s="559"/>
+      <c r="X41" s="560"/>
       <c r="Y41" s="166"/>
       <c r="Z41" s="98"/>
       <c r="AA41" s="119"/>
@@ -27338,21 +27330,21 @@
       <c r="I42" s="125"/>
       <c r="J42" s="125"/>
       <c r="K42" s="95"/>
-      <c r="L42" s="557"/>
-      <c r="M42" s="558"/>
-      <c r="N42" s="559"/>
-      <c r="O42" s="575"/>
-      <c r="P42" s="576"/>
+      <c r="L42" s="580"/>
+      <c r="M42" s="581"/>
+      <c r="N42" s="582"/>
+      <c r="O42" s="569"/>
+      <c r="P42" s="570"/>
       <c r="Q42" s="98"/>
-      <c r="R42" s="601" t="s">
+      <c r="R42" s="553" t="s">
         <v>217</v>
       </c>
-      <c r="S42" s="602"/>
+      <c r="S42" s="554"/>
       <c r="T42" s="124"/>
-      <c r="U42" s="605"/>
-      <c r="V42" s="606"/>
-      <c r="W42" s="605"/>
-      <c r="X42" s="606"/>
+      <c r="U42" s="561"/>
+      <c r="V42" s="562"/>
+      <c r="W42" s="561"/>
+      <c r="X42" s="562"/>
       <c r="Y42" s="166"/>
       <c r="Z42" s="98"/>
       <c r="AA42" s="95"/>
@@ -27365,19 +27357,19 @@
       <c r="E43" s="98"/>
       <c r="F43" s="95"/>
       <c r="G43" s="161"/>
-      <c r="H43" s="608" t="s">
+      <c r="H43" s="564" t="s">
         <v>171</v>
       </c>
-      <c r="I43" s="608"/>
-      <c r="J43" s="609"/>
+      <c r="I43" s="564"/>
+      <c r="J43" s="565"/>
       <c r="K43" s="105"/>
       <c r="L43" s="161"/>
       <c r="M43" s="192"/>
-      <c r="N43" s="592" t="s">
+      <c r="N43" s="539" t="s">
         <v>161</v>
       </c>
-      <c r="O43" s="593"/>
-      <c r="P43" s="594"/>
+      <c r="O43" s="540"/>
+      <c r="P43" s="541"/>
       <c r="Q43" s="162"/>
       <c r="R43" s="362" t="s">
         <v>218</v>
@@ -27431,21 +27423,21 @@
       <c r="E45" s="98"/>
       <c r="F45" s="95"/>
       <c r="G45" s="162"/>
-      <c r="H45" s="577">
+      <c r="H45" s="548">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="578"/>
-      <c r="J45" s="579"/>
+      <c r="I45" s="549"/>
+      <c r="J45" s="550"/>
       <c r="K45" s="105"/>
       <c r="L45" s="162"/>
       <c r="M45" s="98"/>
       <c r="N45" s="98"/>
-      <c r="O45" s="595">
+      <c r="O45" s="542">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="596"/>
+      <c r="P45" s="543"/>
       <c r="Q45" s="162"/>
       <c r="R45" s="363" t="s">
         <v>219</v>
@@ -27477,8 +27469,8 @@
       <c r="L46" s="162"/>
       <c r="M46" s="98"/>
       <c r="N46" s="98"/>
-      <c r="O46" s="597"/>
-      <c r="P46" s="598"/>
+      <c r="O46" s="544"/>
+      <c r="P46" s="545"/>
       <c r="Q46" s="162"/>
       <c r="R46" s="364"/>
       <c r="S46" s="379"/>
@@ -27589,9 +27581,9 @@
       <c r="E50" s="98"/>
       <c r="F50" s="95"/>
       <c r="G50" s="195"/>
-      <c r="H50" s="599"/>
-      <c r="I50" s="599"/>
-      <c r="J50" s="600"/>
+      <c r="H50" s="546"/>
+      <c r="I50" s="546"/>
+      <c r="J50" s="547"/>
       <c r="K50" s="96"/>
       <c r="L50" s="123"/>
       <c r="M50" s="123"/>
@@ -27646,9 +27638,9 @@
       <c r="E52" s="98"/>
       <c r="F52" s="98"/>
       <c r="G52" s="98"/>
-      <c r="H52" s="607"/>
-      <c r="I52" s="607"/>
-      <c r="J52" s="607"/>
+      <c r="H52" s="563"/>
+      <c r="I52" s="563"/>
+      <c r="J52" s="563"/>
       <c r="K52" s="98"/>
       <c r="L52" s="98"/>
       <c r="M52" s="98"/>
@@ -27749,11 +27741,11 @@
       <c r="U55" s="95"/>
       <c r="V55" s="98"/>
       <c r="W55" s="98"/>
-      <c r="X55" s="589"/>
-      <c r="Y55" s="590"/>
-      <c r="Z55" s="590"/>
-      <c r="AA55" s="590"/>
-      <c r="AB55" s="591"/>
+      <c r="X55" s="536"/>
+      <c r="Y55" s="537"/>
+      <c r="Z55" s="537"/>
+      <c r="AA55" s="537"/>
+      <c r="AB55" s="538"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="98"/>
@@ -27969,11 +27961,11 @@
       <c r="P63" s="98"/>
       <c r="Q63" s="95"/>
       <c r="R63" s="95"/>
-      <c r="U63" s="589"/>
-      <c r="V63" s="590"/>
-      <c r="W63" s="590"/>
-      <c r="X63" s="590"/>
-      <c r="Y63" s="591"/>
+      <c r="U63" s="536"/>
+      <c r="V63" s="537"/>
+      <c r="W63" s="537"/>
+      <c r="X63" s="537"/>
+      <c r="Y63" s="538"/>
       <c r="Z63" s="98"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -28409,6 +28401,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -28433,178 +28597,6 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="5" priority="10">
@@ -28644,22 +28636,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="B2" s="612" t="s">
+      <c r="B2" s="652" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="612"/>
-      <c r="D2" s="612"/>
-      <c r="E2" s="612"/>
-      <c r="F2" s="612"/>
+      <c r="C2" s="652"/>
+      <c r="D2" s="652"/>
+      <c r="E2" s="652"/>
+      <c r="F2" s="652"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="B3" s="613" t="s">
+      <c r="B3" s="653" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="613"/>
-      <c r="D3" s="613"/>
-      <c r="E3" s="613"/>
-      <c r="F3" s="613"/>
+      <c r="C3" s="653"/>
+      <c r="D3" s="653"/>
+      <c r="E3" s="653"/>
+      <c r="F3" s="653"/>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="89" t="s">
@@ -28866,10 +28858,10 @@
       <c r="C26" s="89"/>
       <c r="D26" s="89"/>
       <c r="E26" s="2"/>
-      <c r="G26" s="610" t="s">
+      <c r="G26" s="650" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="611">
+      <c r="H26" s="651">
         <v>5</v>
       </c>
     </row>
@@ -28877,36 +28869,36 @@
       <c r="C27" s="89"/>
       <c r="D27" s="89"/>
       <c r="E27" s="2"/>
-      <c r="G27" s="610"/>
-      <c r="H27" s="611"/>
+      <c r="G27" s="650"/>
+      <c r="H27" s="651"/>
     </row>
     <row r="28" spans="3:8">
       <c r="C28" s="89"/>
       <c r="D28" s="89"/>
       <c r="E28" s="2"/>
-      <c r="G28" s="610"/>
-      <c r="H28" s="611"/>
+      <c r="G28" s="650"/>
+      <c r="H28" s="651"/>
     </row>
     <row r="29" spans="3:8">
       <c r="C29" s="89"/>
       <c r="D29" s="89"/>
       <c r="E29" s="2"/>
-      <c r="G29" s="610"/>
-      <c r="H29" s="611"/>
+      <c r="G29" s="650"/>
+      <c r="H29" s="651"/>
     </row>
     <row r="30" spans="3:8">
       <c r="C30" s="89"/>
       <c r="D30" s="89"/>
       <c r="E30" s="2"/>
-      <c r="G30" s="610"/>
-      <c r="H30" s="611"/>
+      <c r="G30" s="650"/>
+      <c r="H30" s="651"/>
     </row>
     <row r="31" spans="3:8">
       <c r="C31" s="89"/>
       <c r="D31" s="89"/>
       <c r="E31" s="2"/>
-      <c r="G31" s="610"/>
-      <c r="H31" s="611">
+      <c r="G31" s="650"/>
+      <c r="H31" s="651">
         <v>4</v>
       </c>
     </row>
@@ -28914,36 +28906,36 @@
       <c r="C32" s="89"/>
       <c r="D32" s="89"/>
       <c r="E32" s="2"/>
-      <c r="G32" s="610"/>
-      <c r="H32" s="611"/>
+      <c r="G32" s="650"/>
+      <c r="H32" s="651"/>
     </row>
     <row r="33" spans="3:8">
       <c r="C33" s="89"/>
       <c r="D33" s="89"/>
       <c r="E33" s="2"/>
-      <c r="G33" s="610"/>
-      <c r="H33" s="611"/>
+      <c r="G33" s="650"/>
+      <c r="H33" s="651"/>
     </row>
     <row r="34" spans="3:8">
       <c r="C34" s="89"/>
       <c r="D34" s="89"/>
       <c r="E34" s="2"/>
-      <c r="G34" s="610"/>
-      <c r="H34" s="611"/>
+      <c r="G34" s="650"/>
+      <c r="H34" s="651"/>
     </row>
     <row r="35" spans="3:8">
       <c r="C35" s="89"/>
       <c r="D35" s="89"/>
       <c r="E35" s="2"/>
-      <c r="G35" s="610"/>
-      <c r="H35" s="611"/>
+      <c r="G35" s="650"/>
+      <c r="H35" s="651"/>
     </row>
     <row r="36" spans="3:8">
       <c r="C36" s="89"/>
       <c r="D36" s="89"/>
       <c r="E36" s="2"/>
-      <c r="G36" s="610"/>
-      <c r="H36" s="611">
+      <c r="G36" s="650"/>
+      <c r="H36" s="651">
         <v>3</v>
       </c>
     </row>
@@ -28951,252 +28943,252 @@
       <c r="C37" s="89"/>
       <c r="D37" s="89"/>
       <c r="E37" s="2"/>
-      <c r="G37" s="610"/>
-      <c r="H37" s="611"/>
+      <c r="G37" s="650"/>
+      <c r="H37" s="651"/>
     </row>
     <row r="38" spans="3:8">
       <c r="C38" s="89"/>
       <c r="D38" s="89"/>
       <c r="E38" s="2"/>
-      <c r="G38" s="610"/>
-      <c r="H38" s="611"/>
+      <c r="G38" s="650"/>
+      <c r="H38" s="651"/>
     </row>
     <row r="39" spans="3:8">
       <c r="C39" s="89"/>
       <c r="D39" s="89"/>
       <c r="E39" s="2"/>
-      <c r="G39" s="610"/>
-      <c r="H39" s="611"/>
+      <c r="G39" s="650"/>
+      <c r="H39" s="651"/>
     </row>
     <row r="40" spans="3:8">
-      <c r="G40" s="610"/>
-      <c r="H40" s="611"/>
+      <c r="G40" s="650"/>
+      <c r="H40" s="651"/>
     </row>
     <row r="41" spans="3:8">
-      <c r="G41" s="610"/>
-      <c r="H41" s="611">
+      <c r="G41" s="650"/>
+      <c r="H41" s="651">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="3:8">
-      <c r="G42" s="610"/>
-      <c r="H42" s="611"/>
+      <c r="G42" s="650"/>
+      <c r="H42" s="651"/>
     </row>
     <row r="43" spans="3:8">
-      <c r="G43" s="610"/>
-      <c r="H43" s="611"/>
+      <c r="G43" s="650"/>
+      <c r="H43" s="651"/>
     </row>
     <row r="44" spans="3:8">
-      <c r="G44" s="610"/>
-      <c r="H44" s="611"/>
+      <c r="G44" s="650"/>
+      <c r="H44" s="651"/>
     </row>
     <row r="45" spans="3:8">
-      <c r="G45" s="610"/>
-      <c r="H45" s="611"/>
+      <c r="G45" s="650"/>
+      <c r="H45" s="651"/>
     </row>
     <row r="46" spans="3:8">
-      <c r="G46" s="610"/>
-      <c r="H46" s="611">
+      <c r="G46" s="650"/>
+      <c r="H46" s="651">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="3:8">
-      <c r="G47" s="610"/>
-      <c r="H47" s="611"/>
+      <c r="G47" s="650"/>
+      <c r="H47" s="651"/>
     </row>
     <row r="48" spans="3:8">
-      <c r="G48" s="610"/>
-      <c r="H48" s="611"/>
+      <c r="G48" s="650"/>
+      <c r="H48" s="651"/>
     </row>
     <row r="49" spans="7:10">
-      <c r="G49" s="610"/>
-      <c r="H49" s="611"/>
+      <c r="G49" s="650"/>
+      <c r="H49" s="651"/>
     </row>
     <row r="50" spans="7:10">
-      <c r="G50" s="610"/>
-      <c r="H50" s="611"/>
+      <c r="G50" s="650"/>
+      <c r="H50" s="651"/>
     </row>
     <row r="55" spans="7:10">
       <c r="H55" s="200"/>
-      <c r="I55" s="611"/>
-      <c r="J55" s="610"/>
+      <c r="I55" s="651"/>
+      <c r="J55" s="650"/>
     </row>
     <row r="56" spans="7:10">
       <c r="H56" s="200"/>
-      <c r="I56" s="611"/>
-      <c r="J56" s="610"/>
+      <c r="I56" s="651"/>
+      <c r="J56" s="650"/>
     </row>
     <row r="57" spans="7:10">
       <c r="H57" s="200"/>
-      <c r="I57" s="611"/>
-      <c r="J57" s="610"/>
+      <c r="I57" s="651"/>
+      <c r="J57" s="650"/>
     </row>
     <row r="58" spans="7:10">
       <c r="H58" s="200"/>
-      <c r="I58" s="611"/>
-      <c r="J58" s="610"/>
+      <c r="I58" s="651"/>
+      <c r="J58" s="650"/>
     </row>
     <row r="59" spans="7:10">
       <c r="H59" s="200"/>
-      <c r="I59" s="611"/>
-      <c r="J59" s="610"/>
+      <c r="I59" s="651"/>
+      <c r="J59" s="650"/>
     </row>
     <row r="60" spans="7:10">
       <c r="H60" s="200"/>
-      <c r="I60" s="611"/>
-      <c r="J60" s="610"/>
+      <c r="I60" s="651"/>
+      <c r="J60" s="650"/>
     </row>
     <row r="61" spans="7:10">
       <c r="H61" s="200"/>
-      <c r="I61" s="611"/>
-      <c r="J61" s="610"/>
+      <c r="I61" s="651"/>
+      <c r="J61" s="650"/>
     </row>
     <row r="62" spans="7:10">
       <c r="H62" s="200"/>
-      <c r="I62" s="611"/>
-      <c r="J62" s="610"/>
+      <c r="I62" s="651"/>
+      <c r="J62" s="650"/>
     </row>
     <row r="63" spans="7:10">
       <c r="H63" s="200"/>
-      <c r="I63" s="611"/>
-      <c r="J63" s="610"/>
+      <c r="I63" s="651"/>
+      <c r="J63" s="650"/>
     </row>
     <row r="64" spans="7:10">
       <c r="H64" s="200"/>
-      <c r="I64" s="611"/>
-      <c r="J64" s="610"/>
+      <c r="I64" s="651"/>
+      <c r="J64" s="650"/>
     </row>
     <row r="65" spans="8:11">
       <c r="H65" s="200"/>
-      <c r="I65" s="611"/>
-      <c r="J65" s="610"/>
+      <c r="I65" s="651"/>
+      <c r="J65" s="650"/>
     </row>
     <row r="66" spans="8:11">
       <c r="H66" s="200"/>
-      <c r="I66" s="611"/>
-      <c r="J66" s="610"/>
+      <c r="I66" s="651"/>
+      <c r="J66" s="650"/>
     </row>
     <row r="67" spans="8:11">
       <c r="H67" s="200"/>
-      <c r="I67" s="611"/>
-      <c r="J67" s="610"/>
+      <c r="I67" s="651"/>
+      <c r="J67" s="650"/>
     </row>
     <row r="68" spans="8:11">
       <c r="H68" s="200"/>
-      <c r="I68" s="611"/>
-      <c r="J68" s="610"/>
+      <c r="I68" s="651"/>
+      <c r="J68" s="650"/>
     </row>
     <row r="69" spans="8:11">
       <c r="H69" s="200"/>
-      <c r="I69" s="611"/>
-      <c r="J69" s="610"/>
+      <c r="I69" s="651"/>
+      <c r="J69" s="650"/>
     </row>
     <row r="70" spans="8:11">
       <c r="H70" s="200"/>
-      <c r="I70" s="611"/>
-      <c r="J70" s="610"/>
-      <c r="K70" s="610" t="s">
+      <c r="I70" s="651"/>
+      <c r="J70" s="650"/>
+      <c r="K70" s="650" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="71" spans="8:11">
       <c r="H71" s="200"/>
-      <c r="I71" s="611"/>
-      <c r="J71" s="610"/>
-      <c r="K71" s="610"/>
+      <c r="I71" s="651"/>
+      <c r="J71" s="650"/>
+      <c r="K71" s="650"/>
     </row>
     <row r="72" spans="8:11">
       <c r="H72" s="200"/>
-      <c r="I72" s="611"/>
-      <c r="J72" s="610"/>
-      <c r="K72" s="610"/>
+      <c r="I72" s="651"/>
+      <c r="J72" s="650"/>
+      <c r="K72" s="650"/>
     </row>
     <row r="73" spans="8:11">
       <c r="H73" s="200"/>
-      <c r="I73" s="611"/>
-      <c r="J73" s="610"/>
-      <c r="K73" s="610"/>
+      <c r="I73" s="651"/>
+      <c r="J73" s="650"/>
+      <c r="K73" s="650"/>
     </row>
     <row r="74" spans="8:11">
       <c r="H74" s="200"/>
-      <c r="I74" s="611"/>
-      <c r="J74" s="610"/>
-      <c r="K74" s="610"/>
+      <c r="I74" s="651"/>
+      <c r="J74" s="650"/>
+      <c r="K74" s="650"/>
     </row>
     <row r="75" spans="8:11">
       <c r="H75" s="200"/>
-      <c r="I75" s="611"/>
-      <c r="J75" s="610"/>
-      <c r="K75" s="610"/>
+      <c r="I75" s="651"/>
+      <c r="J75" s="650"/>
+      <c r="K75" s="650"/>
     </row>
     <row r="76" spans="8:11">
       <c r="H76" s="200"/>
-      <c r="I76" s="611"/>
-      <c r="J76" s="610"/>
-      <c r="K76" s="610"/>
+      <c r="I76" s="651"/>
+      <c r="J76" s="650"/>
+      <c r="K76" s="650"/>
     </row>
     <row r="77" spans="8:11">
       <c r="H77" s="200"/>
-      <c r="I77" s="611"/>
-      <c r="J77" s="610"/>
-      <c r="K77" s="610"/>
+      <c r="I77" s="651"/>
+      <c r="J77" s="650"/>
+      <c r="K77" s="650"/>
     </row>
     <row r="78" spans="8:11">
       <c r="H78" s="200"/>
-      <c r="I78" s="611"/>
-      <c r="J78" s="610"/>
-      <c r="K78" s="610"/>
+      <c r="I78" s="651"/>
+      <c r="J78" s="650"/>
+      <c r="K78" s="650"/>
     </row>
     <row r="79" spans="8:11">
       <c r="H79" s="200"/>
-      <c r="I79" s="611"/>
-      <c r="J79" s="610"/>
-      <c r="K79" s="610"/>
+      <c r="I79" s="651"/>
+      <c r="J79" s="650"/>
+      <c r="K79" s="650"/>
     </row>
     <row r="80" spans="8:11">
-      <c r="K80" s="610"/>
+      <c r="K80" s="650"/>
     </row>
     <row r="81" spans="11:11">
-      <c r="K81" s="610"/>
+      <c r="K81" s="650"/>
     </row>
     <row r="82" spans="11:11">
-      <c r="K82" s="610"/>
+      <c r="K82" s="650"/>
     </row>
     <row r="83" spans="11:11">
-      <c r="K83" s="610"/>
+      <c r="K83" s="650"/>
     </row>
     <row r="84" spans="11:11">
-      <c r="K84" s="610"/>
+      <c r="K84" s="650"/>
     </row>
     <row r="85" spans="11:11">
-      <c r="K85" s="610"/>
+      <c r="K85" s="650"/>
     </row>
     <row r="86" spans="11:11">
-      <c r="K86" s="610"/>
+      <c r="K86" s="650"/>
     </row>
     <row r="87" spans="11:11">
-      <c r="K87" s="610"/>
+      <c r="K87" s="650"/>
     </row>
     <row r="88" spans="11:11">
-      <c r="K88" s="610"/>
+      <c r="K88" s="650"/>
     </row>
     <row r="89" spans="11:11">
-      <c r="K89" s="610"/>
+      <c r="K89" s="650"/>
     </row>
     <row r="90" spans="11:11">
-      <c r="K90" s="610"/>
+      <c r="K90" s="650"/>
     </row>
     <row r="91" spans="11:11">
-      <c r="K91" s="610"/>
+      <c r="K91" s="650"/>
     </row>
     <row r="92" spans="11:11">
-      <c r="K92" s="610"/>
+      <c r="K92" s="650"/>
     </row>
     <row r="93" spans="11:11">
-      <c r="K93" s="610"/>
+      <c r="K93" s="650"/>
     </row>
     <row r="94" spans="11:11">
-      <c r="K94" s="610"/>
+      <c r="K94" s="650"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -29249,23 +29241,23 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="98"/>
-      <c r="B1" s="614" t="s">
+      <c r="B1" s="689" t="s">
         <v>188</v>
       </c>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
-      <c r="I1" s="615"/>
-      <c r="J1" s="615"/>
-      <c r="K1" s="615"/>
-      <c r="L1" s="615"/>
-      <c r="M1" s="615"/>
-      <c r="N1" s="615"/>
-      <c r="O1" s="615"/>
-      <c r="P1" s="616"/>
+      <c r="C1" s="690"/>
+      <c r="D1" s="690"/>
+      <c r="E1" s="690"/>
+      <c r="F1" s="690"/>
+      <c r="G1" s="690"/>
+      <c r="H1" s="690"/>
+      <c r="I1" s="690"/>
+      <c r="J1" s="690"/>
+      <c r="K1" s="690"/>
+      <c r="L1" s="690"/>
+      <c r="M1" s="690"/>
+      <c r="N1" s="690"/>
+      <c r="O1" s="690"/>
+      <c r="P1" s="691"/>
       <c r="Q1" s="98"/>
       <c r="R1" s="98"/>
       <c r="S1" s="98"/>
@@ -29274,23 +29266,23 @@
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="98"/>
-      <c r="B2" s="617" t="s">
+      <c r="B2" s="692" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="618"/>
-      <c r="D2" s="618"/>
-      <c r="E2" s="618"/>
-      <c r="F2" s="618"/>
-      <c r="G2" s="618"/>
-      <c r="H2" s="618"/>
-      <c r="I2" s="618"/>
-      <c r="J2" s="618"/>
-      <c r="K2" s="618"/>
-      <c r="L2" s="618"/>
-      <c r="M2" s="618"/>
-      <c r="N2" s="618"/>
-      <c r="O2" s="618"/>
-      <c r="P2" s="619"/>
+      <c r="C2" s="693"/>
+      <c r="D2" s="693"/>
+      <c r="E2" s="693"/>
+      <c r="F2" s="693"/>
+      <c r="G2" s="693"/>
+      <c r="H2" s="693"/>
+      <c r="I2" s="693"/>
+      <c r="J2" s="693"/>
+      <c r="K2" s="693"/>
+      <c r="L2" s="693"/>
+      <c r="M2" s="693"/>
+      <c r="N2" s="693"/>
+      <c r="O2" s="693"/>
+      <c r="P2" s="694"/>
       <c r="Q2" s="98"/>
       <c r="R2" s="98"/>
       <c r="S2" s="98"/>
@@ -29331,14 +29323,14 @@
       <c r="H4" s="96"/>
       <c r="I4" s="104"/>
       <c r="J4" s="251"/>
-      <c r="K4" s="632" t="s">
+      <c r="K4" s="682" t="s">
         <v>230</v>
       </c>
-      <c r="L4" s="632"/>
-      <c r="M4" s="632"/>
-      <c r="N4" s="632"/>
-      <c r="O4" s="632"/>
-      <c r="P4" s="632"/>
+      <c r="L4" s="682"/>
+      <c r="M4" s="682"/>
+      <c r="N4" s="682"/>
+      <c r="O4" s="682"/>
+      <c r="P4" s="682"/>
       <c r="Q4" s="98"/>
       <c r="R4" s="98"/>
       <c r="S4" s="98"/>
@@ -29351,18 +29343,18 @@
       <c r="H5" s="95"/>
       <c r="I5" s="98"/>
       <c r="J5" s="252"/>
-      <c r="K5" s="628" t="s">
+      <c r="K5" s="699" t="s">
         <v>191</v>
       </c>
-      <c r="L5" s="628"/>
-      <c r="M5" s="628" t="s">
+      <c r="L5" s="699"/>
+      <c r="M5" s="699" t="s">
         <v>194</v>
       </c>
-      <c r="N5" s="628"/>
-      <c r="O5" s="628" t="s">
+      <c r="N5" s="699"/>
+      <c r="O5" s="699" t="s">
         <v>195</v>
       </c>
-      <c r="P5" s="628"/>
+      <c r="P5" s="699"/>
       <c r="Q5" s="96"/>
       <c r="R5" s="98"/>
       <c r="S5" s="98"/>
@@ -29375,12 +29367,12 @@
       <c r="H6" s="95"/>
       <c r="I6" s="98"/>
       <c r="J6" s="95"/>
-      <c r="K6" s="643"/>
-      <c r="L6" s="624"/>
-      <c r="M6" s="623"/>
-      <c r="N6" s="624"/>
-      <c r="O6" s="623"/>
-      <c r="P6" s="629"/>
+      <c r="K6" s="678"/>
+      <c r="L6" s="679"/>
+      <c r="M6" s="698"/>
+      <c r="N6" s="679"/>
+      <c r="O6" s="698"/>
+      <c r="P6" s="700"/>
       <c r="Q6" s="96"/>
       <c r="R6" s="98"/>
       <c r="S6" s="98"/>
@@ -29391,18 +29383,18 @@
       <c r="A7" s="98"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
-      <c r="E7" s="630"/>
-      <c r="F7" s="631"/>
-      <c r="G7" s="631"/>
-      <c r="H7" s="631"/>
+      <c r="E7" s="680"/>
+      <c r="F7" s="681"/>
+      <c r="G7" s="681"/>
+      <c r="H7" s="681"/>
       <c r="I7" s="98"/>
       <c r="J7" s="119"/>
-      <c r="K7" s="633"/>
-      <c r="L7" s="626"/>
-      <c r="M7" s="625"/>
-      <c r="N7" s="626"/>
-      <c r="O7" s="625"/>
-      <c r="P7" s="627"/>
+      <c r="K7" s="674"/>
+      <c r="L7" s="671"/>
+      <c r="M7" s="670"/>
+      <c r="N7" s="671"/>
+      <c r="O7" s="670"/>
+      <c r="P7" s="677"/>
       <c r="Q7" s="96"/>
       <c r="R7" s="98"/>
       <c r="S7" s="98"/>
@@ -29416,12 +29408,12 @@
       <c r="D8" s="98"/>
       <c r="I8" s="98"/>
       <c r="J8" s="95"/>
-      <c r="K8" s="633"/>
-      <c r="L8" s="626"/>
-      <c r="M8" s="625"/>
-      <c r="N8" s="626"/>
-      <c r="O8" s="625"/>
-      <c r="P8" s="627"/>
+      <c r="K8" s="674"/>
+      <c r="L8" s="671"/>
+      <c r="M8" s="670"/>
+      <c r="N8" s="671"/>
+      <c r="O8" s="670"/>
+      <c r="P8" s="677"/>
       <c r="Q8" s="96"/>
       <c r="R8" s="98"/>
       <c r="S8" s="98"/>
@@ -29435,12 +29427,12 @@
       <c r="D9" s="98"/>
       <c r="I9" s="98"/>
       <c r="J9" s="119"/>
-      <c r="K9" s="633"/>
-      <c r="L9" s="626"/>
-      <c r="M9" s="625"/>
-      <c r="N9" s="626"/>
-      <c r="O9" s="625"/>
-      <c r="P9" s="627"/>
+      <c r="K9" s="674"/>
+      <c r="L9" s="671"/>
+      <c r="M9" s="670"/>
+      <c r="N9" s="671"/>
+      <c r="O9" s="670"/>
+      <c r="P9" s="677"/>
       <c r="Q9" s="96"/>
       <c r="R9" s="98"/>
       <c r="S9" s="98"/>
@@ -29454,12 +29446,12 @@
       <c r="D10" s="98"/>
       <c r="I10" s="98"/>
       <c r="J10" s="95"/>
-      <c r="K10" s="633"/>
-      <c r="L10" s="626"/>
-      <c r="M10" s="625"/>
-      <c r="N10" s="626"/>
-      <c r="O10" s="625"/>
-      <c r="P10" s="627"/>
+      <c r="K10" s="674"/>
+      <c r="L10" s="671"/>
+      <c r="M10" s="670"/>
+      <c r="N10" s="671"/>
+      <c r="O10" s="670"/>
+      <c r="P10" s="677"/>
       <c r="Q10" s="96"/>
       <c r="R10" s="98"/>
       <c r="S10" s="98"/>
@@ -29471,20 +29463,20 @@
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
       <c r="D11" s="95"/>
-      <c r="E11" s="620" t="s">
+      <c r="E11" s="695" t="s">
         <v>193</v>
       </c>
-      <c r="F11" s="621"/>
-      <c r="G11" s="621"/>
-      <c r="H11" s="622"/>
+      <c r="F11" s="696"/>
+      <c r="G11" s="696"/>
+      <c r="H11" s="697"/>
       <c r="I11" s="96"/>
       <c r="J11" s="119"/>
-      <c r="K11" s="633"/>
-      <c r="L11" s="626"/>
-      <c r="M11" s="625"/>
-      <c r="N11" s="626"/>
-      <c r="O11" s="625"/>
-      <c r="P11" s="627"/>
+      <c r="K11" s="674"/>
+      <c r="L11" s="671"/>
+      <c r="M11" s="670"/>
+      <c r="N11" s="671"/>
+      <c r="O11" s="670"/>
+      <c r="P11" s="677"/>
       <c r="Q11" s="96"/>
       <c r="R11" s="98"/>
       <c r="S11" s="98"/>
@@ -29496,22 +29488,22 @@
       <c r="B12" s="98"/>
       <c r="C12" s="98"/>
       <c r="D12" s="95"/>
-      <c r="E12" s="634" t="s">
+      <c r="E12" s="683" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="635"/>
-      <c r="G12" s="636"/>
+      <c r="F12" s="684"/>
+      <c r="G12" s="685"/>
       <c r="H12" s="261" t="s">
         <v>192</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="119"/>
-      <c r="K12" s="633"/>
-      <c r="L12" s="626"/>
-      <c r="M12" s="625"/>
-      <c r="N12" s="626"/>
-      <c r="O12" s="625"/>
-      <c r="P12" s="627"/>
+      <c r="K12" s="674"/>
+      <c r="L12" s="671"/>
+      <c r="M12" s="670"/>
+      <c r="N12" s="671"/>
+      <c r="O12" s="670"/>
+      <c r="P12" s="677"/>
       <c r="Q12" s="96"/>
       <c r="R12" s="98"/>
       <c r="S12" s="98"/>
@@ -29523,22 +29515,22 @@
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
       <c r="D13" s="95"/>
-      <c r="E13" s="637" t="s">
+      <c r="E13" s="686" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="638"/>
-      <c r="G13" s="639"/>
+      <c r="F13" s="687"/>
+      <c r="G13" s="688"/>
       <c r="H13" s="322">
         <v>2</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="95"/>
-      <c r="K13" s="633"/>
-      <c r="L13" s="626"/>
-      <c r="M13" s="625"/>
-      <c r="N13" s="626"/>
-      <c r="O13" s="625"/>
-      <c r="P13" s="627"/>
+      <c r="K13" s="674"/>
+      <c r="L13" s="671"/>
+      <c r="M13" s="670"/>
+      <c r="N13" s="671"/>
+      <c r="O13" s="670"/>
+      <c r="P13" s="677"/>
       <c r="Q13" s="96"/>
       <c r="R13" s="98"/>
       <c r="S13" s="98"/>
@@ -29550,22 +29542,22 @@
       <c r="B14" s="98"/>
       <c r="C14" s="98"/>
       <c r="D14" s="95"/>
-      <c r="E14" s="640" t="s">
+      <c r="E14" s="660" t="s">
         <v>207</v>
       </c>
-      <c r="F14" s="641"/>
-      <c r="G14" s="642"/>
+      <c r="F14" s="661"/>
+      <c r="G14" s="662"/>
       <c r="H14" s="323">
         <v>26</v>
       </c>
       <c r="I14" s="96"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="633"/>
-      <c r="L14" s="626"/>
-      <c r="M14" s="625"/>
-      <c r="N14" s="626"/>
-      <c r="O14" s="625"/>
-      <c r="P14" s="627"/>
+      <c r="K14" s="674"/>
+      <c r="L14" s="671"/>
+      <c r="M14" s="670"/>
+      <c r="N14" s="671"/>
+      <c r="O14" s="670"/>
+      <c r="P14" s="677"/>
       <c r="Q14" s="96"/>
       <c r="R14" s="98"/>
       <c r="S14" s="98"/>
@@ -29577,22 +29569,22 @@
       <c r="B15" s="98"/>
       <c r="C15" s="98"/>
       <c r="D15" s="95"/>
-      <c r="E15" s="640" t="s">
+      <c r="E15" s="660" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="641"/>
-      <c r="G15" s="642"/>
+      <c r="F15" s="661"/>
+      <c r="G15" s="662"/>
       <c r="H15" s="323">
         <v>5</v>
       </c>
       <c r="I15" s="96"/>
       <c r="J15" s="95"/>
-      <c r="K15" s="633"/>
-      <c r="L15" s="626"/>
-      <c r="M15" s="625"/>
-      <c r="N15" s="626"/>
-      <c r="O15" s="625"/>
-      <c r="P15" s="627"/>
+      <c r="K15" s="674"/>
+      <c r="L15" s="671"/>
+      <c r="M15" s="670"/>
+      <c r="N15" s="671"/>
+      <c r="O15" s="670"/>
+      <c r="P15" s="677"/>
       <c r="Q15" s="96"/>
       <c r="R15" s="98"/>
       <c r="S15" s="98"/>
@@ -29604,22 +29596,22 @@
       <c r="B16" s="98"/>
       <c r="C16" s="98"/>
       <c r="D16" s="95"/>
-      <c r="E16" s="640" t="s">
+      <c r="E16" s="660" t="s">
         <v>210</v>
       </c>
-      <c r="F16" s="641"/>
-      <c r="G16" s="642"/>
+      <c r="F16" s="661"/>
+      <c r="G16" s="662"/>
       <c r="H16" s="323">
         <v>29</v>
       </c>
       <c r="I16" s="96"/>
       <c r="J16" s="119"/>
-      <c r="K16" s="633"/>
-      <c r="L16" s="626"/>
-      <c r="M16" s="625"/>
-      <c r="N16" s="626"/>
-      <c r="O16" s="625"/>
-      <c r="P16" s="627"/>
+      <c r="K16" s="674"/>
+      <c r="L16" s="671"/>
+      <c r="M16" s="670"/>
+      <c r="N16" s="671"/>
+      <c r="O16" s="670"/>
+      <c r="P16" s="677"/>
       <c r="Q16" s="96"/>
       <c r="R16" s="98"/>
       <c r="S16" s="98"/>
@@ -29629,22 +29621,22 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="95"/>
       <c r="D17" s="114"/>
-      <c r="E17" s="640" t="s">
+      <c r="E17" s="660" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="641"/>
-      <c r="G17" s="642"/>
+      <c r="F17" s="661"/>
+      <c r="G17" s="662"/>
       <c r="H17" s="323">
         <v>6</v>
       </c>
       <c r="I17" s="96"/>
       <c r="J17" s="119"/>
-      <c r="K17" s="633"/>
-      <c r="L17" s="626"/>
-      <c r="M17" s="625"/>
-      <c r="N17" s="626"/>
-      <c r="O17" s="625"/>
-      <c r="P17" s="627"/>
+      <c r="K17" s="674"/>
+      <c r="L17" s="671"/>
+      <c r="M17" s="670"/>
+      <c r="N17" s="671"/>
+      <c r="O17" s="670"/>
+      <c r="P17" s="677"/>
       <c r="Q17" s="96"/>
       <c r="R17" s="98"/>
       <c r="S17" s="98"/>
@@ -29655,22 +29647,22 @@
       <c r="A18" s="95"/>
       <c r="C18" s="123"/>
       <c r="D18" s="95"/>
-      <c r="E18" s="652" t="s">
+      <c r="E18" s="663" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="653"/>
-      <c r="G18" s="654"/>
+      <c r="F18" s="664"/>
+      <c r="G18" s="665"/>
       <c r="H18" s="324">
         <v>25</v>
       </c>
       <c r="I18" s="96"/>
       <c r="J18" s="95"/>
-      <c r="K18" s="660"/>
-      <c r="L18" s="659"/>
-      <c r="M18" s="644"/>
-      <c r="N18" s="659"/>
-      <c r="O18" s="644"/>
-      <c r="P18" s="645"/>
+      <c r="K18" s="675"/>
+      <c r="L18" s="673"/>
+      <c r="M18" s="672"/>
+      <c r="N18" s="673"/>
+      <c r="O18" s="672"/>
+      <c r="P18" s="676"/>
       <c r="Q18" s="96"/>
       <c r="R18" s="98"/>
       <c r="S18" s="95"/>
@@ -29757,10 +29749,10 @@
         <v>193</v>
       </c>
       <c r="G22" s="298"/>
-      <c r="H22" s="655" t="s">
+      <c r="H22" s="666" t="s">
         <v>196</v>
       </c>
-      <c r="I22" s="656"/>
+      <c r="I22" s="667"/>
       <c r="J22" s="307"/>
       <c r="K22" s="317"/>
       <c r="L22" s="295"/>
@@ -29855,17 +29847,17 @@
       <c r="F26" s="320" t="s">
         <v>197</v>
       </c>
-      <c r="H26" s="657" t="s">
+      <c r="H26" s="668" t="s">
         <v>226</v>
       </c>
-      <c r="I26" s="658"/>
+      <c r="I26" s="669"/>
       <c r="J26" s="402"/>
-      <c r="K26" s="646" t="s">
+      <c r="K26" s="654" t="s">
         <v>229</v>
       </c>
-      <c r="L26" s="647"/>
-      <c r="M26" s="647"/>
-      <c r="N26" s="648"/>
+      <c r="L26" s="655"/>
+      <c r="M26" s="655"/>
+      <c r="N26" s="656"/>
       <c r="O26" s="96"/>
       <c r="P26" s="193"/>
       <c r="Q26" s="96"/>
@@ -29889,12 +29881,12 @@
       </c>
       <c r="I27" s="256"/>
       <c r="J27" s="253"/>
-      <c r="K27" s="649" t="s">
+      <c r="K27" s="657" t="s">
         <v>228</v>
       </c>
-      <c r="L27" s="650"/>
-      <c r="M27" s="650"/>
-      <c r="N27" s="651"/>
+      <c r="L27" s="658"/>
+      <c r="M27" s="658"/>
+      <c r="N27" s="659"/>
       <c r="O27" s="194"/>
       <c r="P27" s="164"/>
       <c r="Q27" s="96"/>
@@ -30341,32 +30333,22 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
     <mergeCell ref="M15:N15"/>
@@ -30383,22 +30365,32 @@
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -30575,14 +30567,14 @@
       <c r="G2" s="330"/>
       <c r="H2" s="330"/>
       <c r="I2" s="330"/>
-      <c r="J2" s="431" t="s">
+      <c r="J2" s="476" t="s">
         <v>216</v>
       </c>
-      <c r="K2" s="431"/>
-      <c r="L2" s="431"/>
-      <c r="M2" s="431"/>
-      <c r="N2" s="431"/>
-      <c r="O2" s="431"/>
+      <c r="K2" s="476"/>
+      <c r="L2" s="476"/>
+      <c r="M2" s="476"/>
+      <c r="N2" s="476"/>
+      <c r="O2" s="476"/>
       <c r="P2" s="330"/>
       <c r="Q2" s="330"/>
       <c r="R2" s="330"/>
@@ -30623,14 +30615,14 @@
       <c r="I4" s="331" t="s">
         <v>214</v>
       </c>
-      <c r="J4" s="430" t="s">
+      <c r="J4" s="475" t="s">
         <v>215</v>
       </c>
-      <c r="K4" s="430"/>
-      <c r="L4" s="430"/>
-      <c r="M4" s="430"/>
-      <c r="N4" s="430"/>
-      <c r="O4" s="430"/>
+      <c r="K4" s="475"/>
+      <c r="L4" s="475"/>
+      <c r="M4" s="475"/>
+      <c r="N4" s="475"/>
+      <c r="O4" s="475"/>
       <c r="P4" s="235"/>
       <c r="Q4" s="235"/>
       <c r="R4" s="236"/>
@@ -30646,17 +30638,17 @@
       <c r="G5" s="332"/>
       <c r="H5" s="332"/>
       <c r="I5" s="334"/>
-      <c r="J5" s="441" t="s">
+      <c r="J5" s="468" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="441"/>
-      <c r="L5" s="441"/>
-      <c r="M5" s="441"/>
-      <c r="N5" s="438" t="s">
+      <c r="K5" s="468"/>
+      <c r="L5" s="468"/>
+      <c r="M5" s="468"/>
+      <c r="N5" s="480" t="s">
         <v>186</v>
       </c>
-      <c r="O5" s="438"/>
-      <c r="P5" s="438"/>
+      <c r="O5" s="480"/>
+      <c r="P5" s="480"/>
       <c r="Q5" s="333"/>
       <c r="R5" s="333"/>
       <c r="S5" s="28"/>
@@ -30687,12 +30679,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="29"/>
-      <c r="C8" s="442" t="str">
+      <c r="C8" s="471" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO OCTUBRE - 2024</v>
       </c>
-      <c r="D8" s="443"/>
-      <c r="E8" s="444"/>
+      <c r="D8" s="472"/>
+      <c r="E8" s="473"/>
       <c r="G8" s="66" t="s">
         <v>1</v>
       </c>
@@ -30735,11 +30727,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="C10" s="445" t="s">
+      <c r="C10" s="474" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="445"/>
-      <c r="E10" s="445"/>
+      <c r="D10" s="474"/>
+      <c r="E10" s="474"/>
       <c r="G10" s="92" t="s">
         <v>8</v>
       </c>
@@ -30764,11 +30756,11 @@
       <c r="C11" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="432">
+      <c r="D11" s="467">
         <f>R13</f>
         <v>0</v>
       </c>
-      <c r="E11" s="432"/>
+      <c r="E11" s="467"/>
       <c r="G11" s="58" t="s">
         <v>9</v>
       </c>
@@ -30793,11 +30785,11 @@
       <c r="C12" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="432">
+      <c r="D12" s="467">
         <f>R12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="432"/>
+      <c r="E12" s="467"/>
       <c r="G12" s="58" t="s">
         <v>7</v>
       </c>
@@ -30822,11 +30814,11 @@
       <c r="C13" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="432">
+      <c r="D13" s="467">
         <f>R10</f>
         <v>0</v>
       </c>
-      <c r="E13" s="432"/>
+      <c r="E13" s="467"/>
       <c r="G13" s="93" t="s">
         <v>6</v>
       </c>
@@ -30851,11 +30843,11 @@
       <c r="C14" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="432">
+      <c r="D14" s="467">
         <f>R11</f>
         <v>0</v>
       </c>
-      <c r="E14" s="432"/>
+      <c r="E14" s="467"/>
       <c r="G14" s="64" t="s">
         <v>10</v>
       </c>
@@ -30889,11 +30881,11 @@
       <c r="C15" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="440">
+      <c r="D15" s="466">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="440"/>
+      <c r="E15" s="466"/>
       <c r="H15" s="45"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -30936,11 +30928,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="29"/>
-      <c r="C24" s="433" t="s">
+      <c r="C24" s="477" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="434"/>
-      <c r="E24" s="435"/>
+      <c r="D24" s="478"/>
+      <c r="E24" s="479"/>
       <c r="S24" s="28"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -30948,11 +30940,11 @@
       <c r="C25" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="436">
+      <c r="D25" s="469">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="437"/>
+      <c r="E25" s="470"/>
       <c r="S25" s="28"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -30960,11 +30952,11 @@
       <c r="C26" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="436">
+      <c r="D26" s="469">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="437"/>
+      <c r="E26" s="470"/>
       <c r="S26" s="28"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -30972,11 +30964,11 @@
       <c r="C27" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="432">
+      <c r="D27" s="467">
         <f>SUM(M10:O10)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="432"/>
+      <c r="E27" s="467"/>
       <c r="S27" s="28"/>
     </row>
     <row r="28" spans="1:19" ht="25.5" customHeight="1">
@@ -30984,11 +30976,11 @@
       <c r="C28" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="432">
+      <c r="D28" s="467">
         <f>SUM(M11:O11)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="432"/>
+      <c r="E28" s="467"/>
       <c r="S28" s="28"/>
     </row>
     <row r="29" spans="1:19" ht="33" customHeight="1">
@@ -30996,11 +30988,11 @@
       <c r="C29" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="439">
+      <c r="D29" s="465">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="439"/>
+      <c r="E29" s="465"/>
       <c r="S29" s="28"/>
     </row>
     <row r="30" spans="1:19">
@@ -31114,6 +31106,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -31125,12 +31123,6 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -31480,37 +31472,37 @@
       <c r="AA1" s="21"/>
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
-      <c r="A2" s="446" t="s">
+      <c r="A2" s="481" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="447"/>
-      <c r="C2" s="447"/>
-      <c r="D2" s="447"/>
-      <c r="E2" s="447"/>
-      <c r="F2" s="447"/>
-      <c r="G2" s="447"/>
-      <c r="H2" s="447"/>
-      <c r="I2" s="447"/>
-      <c r="J2" s="447"/>
-      <c r="K2" s="447"/>
-      <c r="L2" s="447"/>
-      <c r="M2" s="447"/>
-      <c r="N2" s="447"/>
-      <c r="O2" s="447"/>
-      <c r="P2" s="447"/>
-      <c r="Q2" s="447"/>
-      <c r="R2" s="447"/>
-      <c r="S2" s="447"/>
-      <c r="T2" s="448" t="s">
+      <c r="B2" s="482"/>
+      <c r="C2" s="482"/>
+      <c r="D2" s="482"/>
+      <c r="E2" s="482"/>
+      <c r="F2" s="482"/>
+      <c r="G2" s="482"/>
+      <c r="H2" s="482"/>
+      <c r="I2" s="482"/>
+      <c r="J2" s="482"/>
+      <c r="K2" s="482"/>
+      <c r="L2" s="482"/>
+      <c r="M2" s="482"/>
+      <c r="N2" s="482"/>
+      <c r="O2" s="482"/>
+      <c r="P2" s="482"/>
+      <c r="Q2" s="482"/>
+      <c r="R2" s="482"/>
+      <c r="S2" s="482"/>
+      <c r="T2" s="483" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="448"/>
-      <c r="V2" s="448"/>
-      <c r="W2" s="448"/>
-      <c r="X2" s="448"/>
-      <c r="Y2" s="448"/>
-      <c r="Z2" s="448"/>
-      <c r="AA2" s="449"/>
+      <c r="U2" s="483"/>
+      <c r="V2" s="483"/>
+      <c r="W2" s="483"/>
+      <c r="X2" s="483"/>
+      <c r="Y2" s="483"/>
+      <c r="Z2" s="483"/>
+      <c r="AA2" s="484"/>
     </row>
     <row r="3" spans="1:27" ht="2.4500000000000002" customHeight="1">
       <c r="A3" s="22"/>
@@ -33269,754 +33261,753 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75">
-      <c r="A1" s="671" t="s">
+      <c r="A1" s="487" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="672"/>
-      <c r="C1" s="672"/>
-      <c r="D1" s="672"/>
-      <c r="E1" s="672"/>
-      <c r="F1" s="672"/>
-      <c r="G1" s="672"/>
-      <c r="H1" s="672"/>
-      <c r="I1" s="672"/>
-      <c r="J1" s="672"/>
-      <c r="K1" s="672"/>
-      <c r="L1" s="672"/>
-      <c r="M1" s="672"/>
-      <c r="N1" s="672"/>
-      <c r="O1" s="672"/>
-      <c r="P1" s="672"/>
-      <c r="Q1" s="672"/>
-      <c r="R1" s="672"/>
+      <c r="B1" s="488"/>
+      <c r="C1" s="488"/>
+      <c r="D1" s="488"/>
+      <c r="E1" s="488"/>
+      <c r="F1" s="488"/>
+      <c r="G1" s="488"/>
+      <c r="H1" s="488"/>
+      <c r="I1" s="488"/>
+      <c r="J1" s="488"/>
+      <c r="K1" s="488"/>
+      <c r="L1" s="488"/>
+      <c r="M1" s="488"/>
+      <c r="N1" s="488"/>
+      <c r="O1" s="488"/>
+      <c r="P1" s="488"/>
+      <c r="Q1" s="488"/>
+      <c r="R1" s="488"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" thickBot="1">
-      <c r="A2" s="673" t="s">
+      <c r="A2" s="489" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="450"/>
-      <c r="C2" s="450"/>
-      <c r="D2" s="450"/>
-      <c r="E2" s="450"/>
-      <c r="F2" s="450"/>
-      <c r="G2" s="450"/>
-      <c r="H2" s="450"/>
-      <c r="I2" s="450"/>
-      <c r="J2" s="450"/>
-      <c r="K2" s="450"/>
-      <c r="L2" s="450"/>
-      <c r="M2" s="450"/>
-      <c r="N2" s="450"/>
-      <c r="O2" s="450"/>
-      <c r="P2" s="450"/>
-      <c r="Q2" s="450"/>
-      <c r="R2" s="450"/>
+      <c r="B2" s="490"/>
+      <c r="C2" s="490"/>
+      <c r="D2" s="490"/>
+      <c r="E2" s="490"/>
+      <c r="F2" s="490"/>
+      <c r="G2" s="490"/>
+      <c r="H2" s="490"/>
+      <c r="I2" s="490"/>
+      <c r="J2" s="490"/>
+      <c r="K2" s="490"/>
+      <c r="L2" s="490"/>
+      <c r="M2" s="490"/>
+      <c r="N2" s="490"/>
+      <c r="O2" s="490"/>
+      <c r="P2" s="490"/>
+      <c r="Q2" s="490"/>
+      <c r="R2" s="490"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="674"/>
-      <c r="B3" s="668"/>
-      <c r="C3" s="668"/>
-      <c r="D3" s="668"/>
-      <c r="E3" s="668"/>
-      <c r="F3" s="668"/>
-      <c r="G3" s="668"/>
-      <c r="H3" s="668"/>
-      <c r="I3" s="668"/>
-      <c r="J3" s="668"/>
-      <c r="K3" s="668"/>
-      <c r="L3" s="668"/>
-      <c r="M3" s="668"/>
-      <c r="N3" s="668"/>
-      <c r="O3" s="668"/>
-      <c r="P3" s="668"/>
-      <c r="Q3" s="668"/>
-      <c r="R3" s="668"/>
+      <c r="A3" s="433"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A4" s="674"/>
-      <c r="B4" s="675"/>
-      <c r="C4" s="675"/>
-      <c r="D4" s="668"/>
-      <c r="E4" s="668"/>
-      <c r="F4" s="668"/>
-      <c r="G4" s="668"/>
-      <c r="H4" s="668"/>
-      <c r="I4" s="668"/>
-      <c r="J4" s="668"/>
-      <c r="K4" s="668"/>
-      <c r="L4" s="668"/>
-      <c r="M4" s="668"/>
-      <c r="N4" s="668"/>
-      <c r="O4" s="668"/>
-      <c r="P4" s="668"/>
-      <c r="Q4" s="668"/>
-      <c r="R4" s="668"/>
+      <c r="A4" s="433"/>
+      <c r="B4" s="434"/>
+      <c r="C4" s="434"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:21" ht="88.5" customHeight="1" thickBot="1">
-      <c r="A5" s="674"/>
-      <c r="B5" s="692" t="s">
+      <c r="A5" s="433"/>
+      <c r="B5" s="451" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="693" t="s">
+      <c r="C5" s="485" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="693"/>
-      <c r="E5" s="693"/>
-      <c r="F5" s="693" t="s">
+      <c r="D5" s="485"/>
+      <c r="E5" s="485"/>
+      <c r="F5" s="485" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="693"/>
-      <c r="H5" s="693"/>
-      <c r="I5" s="693" t="s">
+      <c r="G5" s="485"/>
+      <c r="H5" s="485"/>
+      <c r="I5" s="485" t="s">
         <v>232</v>
       </c>
-      <c r="J5" s="693"/>
-      <c r="K5" s="693"/>
-      <c r="L5" s="693" t="s">
+      <c r="J5" s="485"/>
+      <c r="K5" s="485"/>
+      <c r="L5" s="485" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="693"/>
-      <c r="N5" s="693"/>
-      <c r="O5" s="693" t="s">
+      <c r="M5" s="485"/>
+      <c r="N5" s="485"/>
+      <c r="O5" s="485" t="s">
         <v>233</v>
       </c>
-      <c r="P5" s="693"/>
-      <c r="Q5" s="694"/>
-      <c r="R5" s="669"/>
-      <c r="S5" s="667"/>
+      <c r="P5" s="485"/>
+      <c r="Q5" s="486"/>
+      <c r="R5" s="431"/>
+      <c r="S5" s="430"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="668"/>
+      <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="21">
-      <c r="A6" s="674"/>
-      <c r="B6" s="695" t="s">
+      <c r="A6" s="433"/>
+      <c r="B6" s="452" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="678"/>
-      <c r="D6" s="679">
+      <c r="C6" s="437"/>
+      <c r="D6" s="438" t="str">
         <f>IF(data_status_reg!$E4="bajo",0,IF(data_status_reg!$E4="medio",0.5,IF(data_status_reg!$E4="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="680"/>
-      <c r="F6" s="680"/>
-      <c r="G6" s="679">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E6" s="439"/>
+      <c r="F6" s="439"/>
+      <c r="G6" s="438" t="str">
         <f>IF(data_status_reg!$E20="bajo",0,IF(data_status_reg!$E20="medio",0.5,IF(data_status_reg!$E20="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="680"/>
-      <c r="I6" s="680"/>
-      <c r="J6" s="679">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H6" s="439"/>
+      <c r="I6" s="439"/>
+      <c r="J6" s="438" t="str">
         <f>IF(data_status_reg!$E36="bajo",0,IF(data_status_reg!$E36="medio",0.5,IF(data_status_reg!$E36="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="680"/>
-      <c r="L6" s="680"/>
-      <c r="M6" s="679">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K6" s="439"/>
+      <c r="L6" s="439"/>
+      <c r="M6" s="438" t="str">
         <f>IF(data_status_reg!$E52="bajo",0,IF(data_status_reg!$E52="medio",0.5,IF(data_status_reg!$E52="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="681"/>
-      <c r="O6" s="697"/>
-      <c r="P6" s="679">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N6" s="440"/>
+      <c r="O6" s="454"/>
+      <c r="P6" s="438" t="str">
         <f>IF(data_status_reg!$E68="bajo",0,IF(data_status_reg!$E68="medio",0.5,IF(data_status_reg!$E68="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q6" s="682"/>
-      <c r="R6" s="670"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q6" s="441"/>
+      <c r="R6" s="432"/>
     </row>
     <row r="7" spans="1:21" ht="21">
-      <c r="A7" s="674"/>
-      <c r="B7" s="695" t="s">
+      <c r="A7" s="433"/>
+      <c r="B7" s="452" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="683"/>
-      <c r="D7" s="663">
+      <c r="C7" s="442"/>
+      <c r="D7" s="427" t="str">
         <f>IF(data_status_reg!$E5="bajo",0,IF(data_status_reg!$E5="medio",0.5,IF(data_status_reg!$E5="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="664"/>
-      <c r="F7" s="664"/>
-      <c r="G7" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E7" s="428"/>
+      <c r="F7" s="428"/>
+      <c r="G7" s="427" t="str">
         <f>IF(data_status_reg!$E21="bajo",0,IF(data_status_reg!$E21="medio",0.5,IF(data_status_reg!$E21="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="664"/>
-      <c r="I7" s="664"/>
-      <c r="J7" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H7" s="428"/>
+      <c r="I7" s="428"/>
+      <c r="J7" s="427" t="str">
         <f>IF(data_status_reg!$E37="bajo",0,IF(data_status_reg!$E37="medio",0.5,IF(data_status_reg!$E37="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="664"/>
-      <c r="L7" s="664"/>
-      <c r="M7" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K7" s="428"/>
+      <c r="L7" s="428"/>
+      <c r="M7" s="427" t="str">
         <f>IF(data_status_reg!$E53="bajo",0,IF(data_status_reg!$E53="medio",0.5,IF(data_status_reg!$E53="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="661"/>
-      <c r="O7" s="698"/>
-      <c r="P7" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N7" s="425"/>
+      <c r="O7" s="455"/>
+      <c r="P7" s="427" t="str">
         <f>IF(data_status_reg!$E69="bajo",0,IF(data_status_reg!$E69="medio",0.5,IF(data_status_reg!$E69="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="684"/>
-      <c r="R7" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q7" s="443"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:21" ht="21">
-      <c r="A8" s="674"/>
-      <c r="B8" s="695" t="s">
+      <c r="A8" s="433"/>
+      <c r="B8" s="452" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="683"/>
-      <c r="D8" s="663">
+      <c r="C8" s="442"/>
+      <c r="D8" s="427" t="str">
         <f>IF(data_status_reg!$E6="bajo",0,IF(data_status_reg!$E6="medio",0.5,IF(data_status_reg!$E6="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="664"/>
-      <c r="F8" s="664"/>
-      <c r="G8" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E8" s="428"/>
+      <c r="F8" s="428"/>
+      <c r="G8" s="427" t="str">
         <f>IF(data_status_reg!$E22="bajo",0,IF(data_status_reg!$E22="medio",0.5,IF(data_status_reg!$E22="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="664"/>
-      <c r="I8" s="664"/>
-      <c r="J8" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H8" s="428"/>
+      <c r="I8" s="428"/>
+      <c r="J8" s="427" t="str">
         <f>IF(data_status_reg!$E38="bajo",0,IF(data_status_reg!$E38="medio",0.5,IF(data_status_reg!$E38="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="664"/>
-      <c r="L8" s="664"/>
-      <c r="M8" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K8" s="428"/>
+      <c r="L8" s="428"/>
+      <c r="M8" s="427" t="str">
         <f>IF(data_status_reg!$E54="bajo",0,IF(data_status_reg!$E54="medio",0.5,IF(data_status_reg!$E54="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="661"/>
-      <c r="O8" s="698"/>
-      <c r="P8" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N8" s="425"/>
+      <c r="O8" s="455"/>
+      <c r="P8" s="427" t="str">
         <f>IF(data_status_reg!$E70="bajo",0,IF(data_status_reg!$E70="medio",0.5,IF(data_status_reg!$E70="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q8" s="684"/>
-      <c r="R8" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q8" s="443"/>
+      <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:21" ht="21">
-      <c r="A9" s="674"/>
-      <c r="B9" s="695" t="s">
+      <c r="A9" s="433"/>
+      <c r="B9" s="452" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="683"/>
-      <c r="D9" s="663">
+      <c r="C9" s="442"/>
+      <c r="D9" s="427" t="str">
         <f>IF(data_status_reg!$E7="bajo",0,IF(data_status_reg!$E7="medio",0.5,IF(data_status_reg!$E7="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="664"/>
-      <c r="F9" s="664"/>
-      <c r="G9" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E9" s="428"/>
+      <c r="F9" s="428"/>
+      <c r="G9" s="427" t="str">
         <f>IF(data_status_reg!$E23="bajo",0,IF(data_status_reg!$E23="medio",0.5,IF(data_status_reg!$E23="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="664"/>
-      <c r="I9" s="664"/>
-      <c r="J9" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H9" s="428"/>
+      <c r="I9" s="428"/>
+      <c r="J9" s="427" t="str">
         <f>IF(data_status_reg!$E39="bajo",0,IF(data_status_reg!$E39="medio",0.5,IF(data_status_reg!$E39="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="664"/>
-      <c r="L9" s="664"/>
-      <c r="M9" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K9" s="428"/>
+      <c r="L9" s="428"/>
+      <c r="M9" s="427" t="str">
         <f>IF(data_status_reg!$E55="bajo",0,IF(data_status_reg!$E55="medio",0.5,IF(data_status_reg!$E55="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="661"/>
-      <c r="O9" s="698"/>
-      <c r="P9" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N9" s="425"/>
+      <c r="O9" s="455"/>
+      <c r="P9" s="427" t="str">
         <f>IF(data_status_reg!$E71="bajo",0,IF(data_status_reg!$E71="medio",0.5,IF(data_status_reg!$E71="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q9" s="684"/>
-      <c r="R9" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q9" s="443"/>
+      <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:21" ht="21">
-      <c r="A10" s="674"/>
-      <c r="B10" s="695" t="s">
+      <c r="A10" s="433"/>
+      <c r="B10" s="452" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="683"/>
-      <c r="D10" s="663">
+      <c r="C10" s="442"/>
+      <c r="D10" s="427" t="str">
         <f>IF(data_status_reg!$E8="bajo",0,IF(data_status_reg!$E8="medio",0.5,IF(data_status_reg!$E8="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="664"/>
-      <c r="F10" s="664"/>
-      <c r="G10" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E10" s="428"/>
+      <c r="F10" s="428"/>
+      <c r="G10" s="427" t="str">
         <f>IF(data_status_reg!$E24="bajo",0,IF(data_status_reg!$E24="medio",0.5,IF(data_status_reg!$E24="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="664"/>
-      <c r="I10" s="664"/>
-      <c r="J10" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H10" s="428"/>
+      <c r="I10" s="428"/>
+      <c r="J10" s="427" t="str">
         <f>IF(data_status_reg!$E40="bajo",0,IF(data_status_reg!$E40="medio",0.5,IF(data_status_reg!$E40="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="664"/>
-      <c r="L10" s="664"/>
-      <c r="M10" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K10" s="428"/>
+      <c r="L10" s="428"/>
+      <c r="M10" s="427" t="str">
         <f>IF(data_status_reg!$E56="bajo",0,IF(data_status_reg!$E56="medio",0.5,IF(data_status_reg!$E56="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="661"/>
-      <c r="O10" s="698"/>
-      <c r="P10" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N10" s="425"/>
+      <c r="O10" s="455"/>
+      <c r="P10" s="427" t="str">
         <f>IF(data_status_reg!$E72="bajo",0,IF(data_status_reg!$E72="medio",0.5,IF(data_status_reg!$E72="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q10" s="684"/>
-      <c r="R10" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q10" s="443"/>
+      <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:21" ht="21">
-      <c r="A11" s="674"/>
-      <c r="B11" s="695" t="s">
+      <c r="A11" s="433"/>
+      <c r="B11" s="452" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="683"/>
-      <c r="D11" s="663">
+      <c r="C11" s="442"/>
+      <c r="D11" s="427" t="str">
         <f>IF(data_status_reg!$E9="bajo",0,IF(data_status_reg!$E9="medio",0.5,IF(data_status_reg!$E9="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="664"/>
-      <c r="F11" s="664"/>
-      <c r="G11" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E11" s="428"/>
+      <c r="F11" s="428"/>
+      <c r="G11" s="427" t="str">
         <f>IF(data_status_reg!$E25="bajo",0,IF(data_status_reg!$E25="medio",0.5,IF(data_status_reg!$E25="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="664"/>
-      <c r="I11" s="664"/>
-      <c r="J11" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H11" s="428"/>
+      <c r="I11" s="428"/>
+      <c r="J11" s="427" t="str">
         <f>IF(data_status_reg!$E41="bajo",0,IF(data_status_reg!$E41="medio",0.5,IF(data_status_reg!$E41="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="664"/>
-      <c r="L11" s="664"/>
-      <c r="M11" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K11" s="428"/>
+      <c r="L11" s="428"/>
+      <c r="M11" s="427" t="str">
         <f>IF(data_status_reg!$E57="bajo",0,IF(data_status_reg!$E57="medio",0.5,IF(data_status_reg!$E57="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="661"/>
-      <c r="O11" s="698"/>
-      <c r="P11" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N11" s="425"/>
+      <c r="O11" s="455"/>
+      <c r="P11" s="427" t="str">
         <f>IF(data_status_reg!$E73="bajo",0,IF(data_status_reg!$E73="medio",0.5,IF(data_status_reg!$E73="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q11" s="684"/>
-      <c r="R11" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q11" s="443"/>
+      <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="21">
-      <c r="A12" s="674"/>
-      <c r="B12" s="695" t="s">
+      <c r="A12" s="433"/>
+      <c r="B12" s="452" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="683"/>
-      <c r="D12" s="663">
+      <c r="C12" s="442"/>
+      <c r="D12" s="427" t="str">
         <f>IF(data_status_reg!$E10="bajo",0,IF(data_status_reg!$E10="medio",0.5,IF(data_status_reg!$E10="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="664"/>
-      <c r="F12" s="664"/>
-      <c r="G12" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E12" s="428"/>
+      <c r="F12" s="428"/>
+      <c r="G12" s="427" t="str">
         <f>IF(data_status_reg!$E26="bajo",0,IF(data_status_reg!$E26="medio",0.5,IF(data_status_reg!$E26="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="664"/>
-      <c r="I12" s="665"/>
-      <c r="J12" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H12" s="428"/>
+      <c r="I12" s="429"/>
+      <c r="J12" s="427" t="str">
         <f>IF(data_status_reg!$E42="bajo",0,IF(data_status_reg!$E42="medio",0.5,IF(data_status_reg!$E42="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="665"/>
-      <c r="L12" s="665"/>
-      <c r="M12" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K12" s="429"/>
+      <c r="L12" s="429"/>
+      <c r="M12" s="427" t="str">
         <f>IF(data_status_reg!$E58="bajo",0,IF(data_status_reg!$E58="medio",0.5,IF(data_status_reg!$E58="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="662"/>
-      <c r="O12" s="699"/>
-      <c r="P12" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N12" s="426"/>
+      <c r="O12" s="456"/>
+      <c r="P12" s="427" t="str">
         <f>IF(data_status_reg!$E74="bajo",0,IF(data_status_reg!$E74="medio",0.5,IF(data_status_reg!$E74="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q12" s="684"/>
-      <c r="R12" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q12" s="443"/>
+      <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:21" ht="21">
-      <c r="A13" s="674"/>
-      <c r="B13" s="695" t="s">
+      <c r="A13" s="433"/>
+      <c r="B13" s="452" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="683"/>
-      <c r="D13" s="663">
+      <c r="C13" s="442"/>
+      <c r="D13" s="427" t="str">
         <f>IF(data_status_reg!$E11="bajo",0,IF(data_status_reg!$E11="medio",0.5,IF(data_status_reg!$E11="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="664"/>
-      <c r="F13" s="664"/>
-      <c r="G13" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E13" s="428"/>
+      <c r="F13" s="428"/>
+      <c r="G13" s="427" t="str">
         <f>IF(data_status_reg!$E27="bajo",0,IF(data_status_reg!$E27="medio",0.5,IF(data_status_reg!$E27="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="664"/>
-      <c r="I13" s="664"/>
-      <c r="J13" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H13" s="428"/>
+      <c r="I13" s="428"/>
+      <c r="J13" s="427" t="str">
         <f>IF(data_status_reg!$E43="bajo",0,IF(data_status_reg!$E43="medio",0.5,IF(data_status_reg!$E43="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="664"/>
-      <c r="L13" s="664"/>
-      <c r="M13" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K13" s="428"/>
+      <c r="L13" s="428"/>
+      <c r="M13" s="427" t="str">
         <f>IF(data_status_reg!$E59="bajo",0,IF(data_status_reg!$E59="medio",0.5,IF(data_status_reg!$E59="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="661"/>
-      <c r="O13" s="698"/>
-      <c r="P13" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N13" s="425"/>
+      <c r="O13" s="455"/>
+      <c r="P13" s="427" t="str">
         <f>IF(data_status_reg!$E75="bajo",0,IF(data_status_reg!$E75="medio",0.5,IF(data_status_reg!$E75="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q13" s="684"/>
-      <c r="R13" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q13" s="443"/>
+      <c r="R13" s="3"/>
       <c r="U13" s="16"/>
     </row>
     <row r="14" spans="1:21" ht="21">
-      <c r="A14" s="674"/>
-      <c r="B14" s="695" t="s">
+      <c r="A14" s="433"/>
+      <c r="B14" s="452" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="683"/>
-      <c r="D14" s="663">
+      <c r="C14" s="442"/>
+      <c r="D14" s="427" t="str">
         <f>IF(data_status_reg!$E12="bajo",0,IF(data_status_reg!$E12="medio",0.5,IF(data_status_reg!$E12="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="664"/>
-      <c r="F14" s="664"/>
-      <c r="G14" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E14" s="428"/>
+      <c r="F14" s="428"/>
+      <c r="G14" s="427" t="str">
         <f>IF(data_status_reg!$E28="bajo",0,IF(data_status_reg!$E28="medio",0.5,IF(data_status_reg!$E28="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="664"/>
-      <c r="I14" s="664"/>
-      <c r="J14" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H14" s="428"/>
+      <c r="I14" s="428"/>
+      <c r="J14" s="427" t="str">
         <f>IF(data_status_reg!$E44="bajo",0,IF(data_status_reg!$E44="medio",0.5,IF(data_status_reg!$E44="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="664"/>
-      <c r="L14" s="664"/>
-      <c r="M14" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K14" s="428"/>
+      <c r="L14" s="428"/>
+      <c r="M14" s="427" t="str">
         <f>IF(data_status_reg!$E60="bajo",0,IF(data_status_reg!$E60="medio",0.5,IF(data_status_reg!$E60="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="661"/>
-      <c r="O14" s="698"/>
-      <c r="P14" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N14" s="425"/>
+      <c r="O14" s="455"/>
+      <c r="P14" s="427" t="str">
         <f>IF(data_status_reg!$E76="bajo",0,IF(data_status_reg!$E76="medio",0.5,IF(data_status_reg!$E76="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q14" s="684"/>
-      <c r="R14" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q14" s="443"/>
+      <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:21" ht="21">
-      <c r="A15" s="674"/>
-      <c r="B15" s="695" t="s">
+      <c r="A15" s="433"/>
+      <c r="B15" s="452" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="683"/>
-      <c r="D15" s="663">
+      <c r="C15" s="442"/>
+      <c r="D15" s="427" t="str">
         <f>IF(data_status_reg!$E13="bajo",0,IF(data_status_reg!$E13="medio",0.5,IF(data_status_reg!$E13="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="664"/>
-      <c r="F15" s="664"/>
-      <c r="G15" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E15" s="428"/>
+      <c r="F15" s="428"/>
+      <c r="G15" s="427" t="str">
         <f>IF(data_status_reg!$E29="bajo",0,IF(data_status_reg!$E29="medio",0.5,IF(data_status_reg!$E29="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="664"/>
-      <c r="I15" s="665"/>
-      <c r="J15" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H15" s="428"/>
+      <c r="I15" s="429"/>
+      <c r="J15" s="427" t="str">
         <f>IF(data_status_reg!$E45="bajo",0,IF(data_status_reg!$E45="medio",0.5,IF(data_status_reg!$E45="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="665"/>
-      <c r="L15" s="665"/>
-      <c r="M15" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K15" s="429"/>
+      <c r="L15" s="429"/>
+      <c r="M15" s="427" t="str">
         <f>IF(data_status_reg!$E61="bajo",0,IF(data_status_reg!$E61="medio",0.5,IF(data_status_reg!$E61="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="662"/>
-      <c r="O15" s="699"/>
-      <c r="P15" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N15" s="426"/>
+      <c r="O15" s="456"/>
+      <c r="P15" s="427" t="str">
         <f>IF(data_status_reg!$E77="bajo",0,IF(data_status_reg!$E77="medio",0.5,IF(data_status_reg!$E77="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q15" s="684"/>
-      <c r="R15" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q15" s="443"/>
+      <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:21" ht="21">
-      <c r="A16" s="674"/>
-      <c r="B16" s="695" t="s">
+      <c r="A16" s="433"/>
+      <c r="B16" s="452" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="683"/>
-      <c r="D16" s="663">
+      <c r="C16" s="442"/>
+      <c r="D16" s="427" t="str">
         <f>IF(data_status_reg!$E14="bajo",0,IF(data_status_reg!$E14="medio",0.5,IF(data_status_reg!$E14="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="664"/>
-      <c r="F16" s="664"/>
-      <c r="G16" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E16" s="428"/>
+      <c r="F16" s="428"/>
+      <c r="G16" s="427" t="str">
         <f>IF(data_status_reg!$E30="bajo",0,IF(data_status_reg!$E30="medio",0.5,IF(data_status_reg!$E30="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="664"/>
-      <c r="I16" s="664"/>
-      <c r="J16" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H16" s="428"/>
+      <c r="I16" s="428"/>
+      <c r="J16" s="427" t="str">
         <f>IF(data_status_reg!$E46="bajo",0,IF(data_status_reg!$E46="medio",0.5,IF(data_status_reg!$E46="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="664"/>
-      <c r="L16" s="664"/>
-      <c r="M16" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K16" s="428"/>
+      <c r="L16" s="428"/>
+      <c r="M16" s="427" t="str">
         <f>IF(data_status_reg!$E62="bajo",0,IF(data_status_reg!$E62="medio",0.5,IF(data_status_reg!$E62="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="661"/>
-      <c r="O16" s="698"/>
-      <c r="P16" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N16" s="425"/>
+      <c r="O16" s="455"/>
+      <c r="P16" s="427" t="str">
         <f>IF(data_status_reg!$E78="bajo",0,IF(data_status_reg!$E78="medio",0.5,IF(data_status_reg!$E78="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q16" s="684"/>
-      <c r="R16" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q16" s="443"/>
+      <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21">
-      <c r="A17" s="674"/>
-      <c r="B17" s="695" t="s">
+      <c r="A17" s="433"/>
+      <c r="B17" s="452" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="683"/>
-      <c r="D17" s="663">
+      <c r="C17" s="442"/>
+      <c r="D17" s="427" t="str">
         <f>IF(data_status_reg!$E15="bajo",0,IF(data_status_reg!$E15="medio",0.5,IF(data_status_reg!$E15="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="664"/>
-      <c r="F17" s="664"/>
-      <c r="G17" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E17" s="428"/>
+      <c r="F17" s="428"/>
+      <c r="G17" s="427" t="str">
         <f>IF(data_status_reg!$E31="bajo",0,IF(data_status_reg!$E31="medio",0.5,IF(data_status_reg!$E31="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="664"/>
-      <c r="I17" s="664"/>
-      <c r="J17" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H17" s="428"/>
+      <c r="I17" s="428"/>
+      <c r="J17" s="427" t="str">
         <f>IF(data_status_reg!$E47="bajo",0,IF(data_status_reg!$E47="medio",0.5,IF(data_status_reg!$E47="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="664"/>
-      <c r="L17" s="664"/>
-      <c r="M17" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K17" s="428"/>
+      <c r="L17" s="428"/>
+      <c r="M17" s="427" t="str">
         <f>IF(data_status_reg!$E63="bajo",0,IF(data_status_reg!$E63="medio",0.5,IF(data_status_reg!$E63="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="661"/>
-      <c r="O17" s="698"/>
-      <c r="P17" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N17" s="425"/>
+      <c r="O17" s="455"/>
+      <c r="P17" s="427" t="str">
         <f>IF(data_status_reg!$E79="bajo",0,IF(data_status_reg!$E79="medio",0.5,IF(data_status_reg!$E79="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q17" s="684"/>
-      <c r="R17" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q17" s="443"/>
+      <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21">
-      <c r="A18" s="674"/>
-      <c r="B18" s="695" t="s">
+      <c r="A18" s="433"/>
+      <c r="B18" s="452" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="683"/>
-      <c r="D18" s="663">
+      <c r="C18" s="442"/>
+      <c r="D18" s="427" t="str">
         <f>IF(data_status_reg!$E16="bajo",0,IF(data_status_reg!$E16="medio",0.5,IF(data_status_reg!$E16="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="664"/>
-      <c r="F18" s="664"/>
-      <c r="G18" s="701" t="s">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E18" s="428"/>
+      <c r="F18" s="428"/>
+      <c r="G18" s="458" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="664"/>
-      <c r="I18" s="664"/>
-      <c r="J18" s="663">
+      <c r="H18" s="428"/>
+      <c r="I18" s="428"/>
+      <c r="J18" s="427" t="str">
         <f>IF(data_status_reg!$E48="bajo",0,IF(data_status_reg!$E48="medio",0.5,IF(data_status_reg!$E48="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="664"/>
-      <c r="L18" s="666"/>
-      <c r="M18" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K18" s="428"/>
+      <c r="M18" s="427" t="str">
         <f>IF(data_status_reg!$E64="bajo",0,IF(data_status_reg!$E64="medio",0.5,IF(data_status_reg!$E64="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="662"/>
-      <c r="O18" s="699"/>
-      <c r="P18" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N18" s="426"/>
+      <c r="O18" s="456"/>
+      <c r="P18" s="427" t="str">
         <f>IF(data_status_reg!$E80="bajo",0,IF(data_status_reg!$E80="medio",0.5,IF(data_status_reg!$E80="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q18" s="684"/>
-      <c r="R18" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q18" s="443"/>
+      <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21">
-      <c r="A19" s="674"/>
-      <c r="B19" s="695" t="s">
+      <c r="A19" s="433"/>
+      <c r="B19" s="452" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="683"/>
-      <c r="D19" s="663">
+      <c r="C19" s="442"/>
+      <c r="D19" s="427" t="str">
         <f>IF(data_status_reg!$E17="bajo",0,IF(data_status_reg!$E17="medio",0.5,IF(data_status_reg!$E17="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="664"/>
-      <c r="F19" s="664"/>
-      <c r="G19" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E19" s="428"/>
+      <c r="F19" s="428"/>
+      <c r="G19" s="427" t="str">
         <f>IF(data_status_reg!$E33="bajo",0,IF(data_status_reg!$E33="medio",0.5,IF(data_status_reg!$E33="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="664"/>
-      <c r="I19" s="664"/>
-      <c r="J19" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H19" s="428"/>
+      <c r="I19" s="428"/>
+      <c r="J19" s="427" t="str">
         <f>IF(data_status_reg!$E49="bajo",0,IF(data_status_reg!$E49="medio",0.5,IF(data_status_reg!$E49="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="664"/>
-      <c r="L19" s="664"/>
-      <c r="M19" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K19" s="428"/>
+      <c r="L19" s="428"/>
+      <c r="M19" s="427" t="str">
         <f>IF(data_status_reg!$E65="bajo",0,IF(data_status_reg!$E65="medio",0.5,IF(data_status_reg!$E65="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="661"/>
-      <c r="O19" s="698"/>
-      <c r="P19" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N19" s="425"/>
+      <c r="O19" s="455"/>
+      <c r="P19" s="427" t="str">
         <f>IF(data_status_reg!$E81="bajo",0,IF(data_status_reg!$E81="medio",0.5,IF(data_status_reg!$E81="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q19" s="684"/>
-      <c r="R19" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q19" s="443"/>
+      <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21">
-      <c r="A20" s="674"/>
-      <c r="B20" s="695" t="s">
+      <c r="A20" s="433"/>
+      <c r="B20" s="452" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="683"/>
-      <c r="D20" s="663">
+      <c r="C20" s="442"/>
+      <c r="D20" s="427" t="str">
         <f>IF(data_status_reg!$E18="bajo",0,IF(data_status_reg!$E18="medio",0.5,IF(data_status_reg!$E18="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="664"/>
-      <c r="F20" s="664"/>
-      <c r="G20" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E20" s="428"/>
+      <c r="F20" s="428"/>
+      <c r="G20" s="427" t="str">
         <f>IF(data_status_reg!$E34="bajo",0,IF(data_status_reg!$E34="medio",0.5,IF(data_status_reg!$E34="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="664"/>
-      <c r="I20" s="664"/>
-      <c r="J20" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="H20" s="428"/>
+      <c r="I20" s="428"/>
+      <c r="J20" s="427" t="str">
         <f>IF(data_status_reg!$E50="bajo",0,IF(data_status_reg!$E50="medio",0.5,IF(data_status_reg!$E50="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="664"/>
-      <c r="L20" s="664"/>
-      <c r="M20" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K20" s="428"/>
+      <c r="L20" s="428"/>
+      <c r="M20" s="427" t="str">
         <f>IF(data_status_reg!$E66="bajo",0,IF(data_status_reg!$E66="medio",0.5,IF(data_status_reg!$E66="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="661"/>
-      <c r="O20" s="698"/>
-      <c r="P20" s="663">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N20" s="425"/>
+      <c r="O20" s="455"/>
+      <c r="P20" s="427" t="str">
         <f>IF(data_status_reg!$E82="bajo",0,IF(data_status_reg!$E82="medio",0.5,IF(data_status_reg!$E82="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q20" s="684"/>
-      <c r="R20" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q20" s="443"/>
+      <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21.75" thickBot="1">
-      <c r="A21" s="674"/>
-      <c r="B21" s="696" t="s">
+      <c r="A21" s="433"/>
+      <c r="B21" s="453" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="685"/>
-      <c r="D21" s="686">
+      <c r="C21" s="444"/>
+      <c r="D21" s="445" t="str">
         <f>IF(data_status_reg!$E19="bajo",0,IF(data_status_reg!$E19="medio",0.5,IF(data_status_reg!$E19="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="687"/>
-      <c r="F21" s="687"/>
-      <c r="G21" s="702" t="s">
+        <v>falta riesgo</v>
+      </c>
+      <c r="E21" s="446"/>
+      <c r="F21" s="446"/>
+      <c r="G21" s="459" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="687"/>
-      <c r="I21" s="687"/>
-      <c r="J21" s="686">
+      <c r="H21" s="446"/>
+      <c r="I21" s="446"/>
+      <c r="J21" s="445" t="str">
         <f>IF(data_status_reg!$E51="bajo",0,IF(data_status_reg!$E51="medio",0.5,IF(data_status_reg!$E51="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="687"/>
-      <c r="L21" s="688"/>
-      <c r="M21" s="689">
+        <v>falta riesgo</v>
+      </c>
+      <c r="K21" s="446"/>
+      <c r="L21" s="447"/>
+      <c r="M21" s="448" t="str">
         <f>IF(data_status_reg!$E67="bajo",0,IF(data_status_reg!$E67="medio",0.5,IF(data_status_reg!$E67="alto",1,"falta riesgo")))</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="690"/>
-      <c r="O21" s="700"/>
-      <c r="P21" s="686">
+        <v>falta riesgo</v>
+      </c>
+      <c r="N21" s="449"/>
+      <c r="O21" s="457"/>
+      <c r="P21" s="445" t="str">
         <f>IF(data_status_reg!$E83="bajo",0,IF(data_status_reg!$E83="medio",0.5,IF(data_status_reg!$E83="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q21" s="691"/>
-      <c r="R21" s="668"/>
+        <v>falta riesgo</v>
+      </c>
+      <c r="Q21" s="450"/>
+      <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="674"/>
-      <c r="B22" s="668"/>
-      <c r="C22" s="668"/>
-      <c r="D22" s="668"/>
-      <c r="E22" s="668"/>
-      <c r="F22" s="668"/>
-      <c r="G22" s="668"/>
-      <c r="H22" s="668"/>
-      <c r="I22" s="668"/>
-      <c r="J22" s="668"/>
-      <c r="K22" s="668"/>
-      <c r="L22" s="668"/>
-      <c r="M22" s="668"/>
-      <c r="N22" s="668"/>
-      <c r="O22" s="668"/>
-      <c r="P22" s="668"/>
-      <c r="Q22" s="668"/>
-      <c r="R22" s="668"/>
+      <c r="A22" s="433"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="676"/>
-      <c r="B23" s="677"/>
-      <c r="C23" s="677"/>
-      <c r="D23" s="677"/>
-      <c r="E23" s="677"/>
-      <c r="F23" s="677"/>
-      <c r="G23" s="677"/>
-      <c r="H23" s="677"/>
-      <c r="I23" s="677"/>
-      <c r="J23" s="677"/>
-      <c r="K23" s="677"/>
-      <c r="L23" s="677"/>
-      <c r="M23" s="677"/>
-      <c r="N23" s="677"/>
-      <c r="O23" s="677"/>
-      <c r="P23" s="677"/>
-      <c r="Q23" s="677"/>
-      <c r="R23" s="677"/>
+      <c r="A23" s="435"/>
+      <c r="B23" s="436"/>
+      <c r="C23" s="436"/>
+      <c r="D23" s="436"/>
+      <c r="E23" s="436"/>
+      <c r="F23" s="436"/>
+      <c r="G23" s="436"/>
+      <c r="H23" s="436"/>
+      <c r="I23" s="436"/>
+      <c r="J23" s="436"/>
+      <c r="K23" s="436"/>
+      <c r="L23" s="436"/>
+      <c r="M23" s="436"/>
+      <c r="N23" s="436"/>
+      <c r="O23" s="436"/>
+      <c r="P23" s="436"/>
+      <c r="Q23" s="436"/>
+      <c r="R23" s="436"/>
     </row>
     <row r="26" spans="1:18" outlineLevel="1"/>
     <row r="27" spans="1:18" outlineLevel="1">
@@ -34230,13 +34221,13 @@
     <row r="96" spans="5:5" outlineLevel="1"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
     <mergeCell ref="L5:N5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -34982,641 +34973,481 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E4" s="89"/>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E5" s="89"/>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E6" s="89"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E7" s="89"/>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E8" s="89"/>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E9" s="89"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E10" s="89"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E11" s="89"/>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E12" s="89"/>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E13" s="89"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E14" s="89"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E15" s="89"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E16" s="89"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E17" s="89"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E18" s="89"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E19" s="89"/>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="90"/>
       <c r="C20" s="90"/>
       <c r="D20" s="90"/>
-      <c r="E20" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E20" s="89"/>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
       <c r="D21" s="90"/>
-      <c r="E21" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E21" s="89"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="90"/>
       <c r="C22" s="90"/>
       <c r="D22" s="90"/>
-      <c r="E22" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E22" s="89"/>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="90"/>
       <c r="C23" s="90"/>
       <c r="D23" s="90"/>
-      <c r="E23" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E23" s="89"/>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="90"/>
       <c r="C24" s="90"/>
       <c r="D24" s="90"/>
-      <c r="E24" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E24" s="89"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="90"/>
       <c r="C25" s="90"/>
       <c r="D25" s="90"/>
-      <c r="E25" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E25" s="89"/>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="90"/>
       <c r="C26" s="90"/>
       <c r="D26" s="90"/>
-      <c r="E26" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E26" s="89"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="90"/>
       <c r="C27" s="90"/>
       <c r="D27" s="90"/>
-      <c r="E27" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E27" s="89"/>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="90"/>
       <c r="C28" s="90"/>
       <c r="D28" s="90"/>
-      <c r="E28" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E28" s="89"/>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="90"/>
       <c r="C29" s="90"/>
       <c r="D29" s="90"/>
-      <c r="E29" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E29" s="89"/>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="90"/>
       <c r="C30" s="90"/>
       <c r="D30" s="90"/>
-      <c r="E30" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E30" s="89"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="90"/>
       <c r="C31" s="90"/>
       <c r="D31" s="90"/>
-      <c r="E31" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E31" s="89"/>
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="90"/>
       <c r="C32" s="90"/>
       <c r="D32" s="90"/>
-      <c r="E32" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E32" s="89"/>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="90"/>
       <c r="C33" s="90"/>
       <c r="D33" s="90"/>
-      <c r="E33" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E33" s="89"/>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="90"/>
       <c r="C34" s="90"/>
       <c r="D34" s="90"/>
-      <c r="E34" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E34" s="89"/>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="90"/>
       <c r="C35" s="90"/>
       <c r="D35" s="90"/>
-      <c r="E35" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E35" s="89"/>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="87"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E36" s="89"/>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="87"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E37" s="89"/>
     </row>
     <row r="38" spans="2:5">
       <c r="B38" s="87"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E38" s="89"/>
     </row>
     <row r="39" spans="2:5">
       <c r="B39" s="87"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E39" s="89"/>
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="87"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E40" s="89"/>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="87"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E41" s="89"/>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="87"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E42" s="89"/>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="87"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E43" s="89"/>
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="87"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E44" s="89"/>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="87"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E45" s="89"/>
     </row>
     <row r="46" spans="2:5">
       <c r="B46" s="87"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E46" s="89"/>
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="87"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E47" s="89"/>
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="87"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E48" s="89"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="87"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E49" s="89"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="87"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E50" s="89"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="87"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E51" s="89"/>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="87"/>
       <c r="C52" s="2"/>
       <c r="D52" s="91"/>
-      <c r="E52" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E52" s="89"/>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="87"/>
       <c r="C53" s="2"/>
       <c r="D53" s="91"/>
-      <c r="E53" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E53" s="89"/>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="87"/>
       <c r="C54" s="2"/>
       <c r="D54" s="91"/>
-      <c r="E54" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E54" s="89"/>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="87"/>
       <c r="C55" s="2"/>
       <c r="D55" s="91"/>
-      <c r="E55" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E55" s="89"/>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="87"/>
       <c r="C56" s="2"/>
       <c r="D56" s="91"/>
-      <c r="E56" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E56" s="89"/>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="87"/>
       <c r="C57" s="2"/>
       <c r="D57" s="91"/>
-      <c r="E57" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E57" s="89"/>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="87"/>
       <c r="C58" s="2"/>
       <c r="D58" s="91"/>
-      <c r="E58" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E58" s="89"/>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="87"/>
       <c r="C59" s="2"/>
       <c r="D59" s="91"/>
-      <c r="E59" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E59" s="89"/>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="87"/>
       <c r="C60" s="2"/>
       <c r="D60" s="91"/>
-      <c r="E60" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E60" s="89"/>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="87"/>
       <c r="C61" s="2"/>
       <c r="D61" s="91"/>
-      <c r="E61" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E61" s="89"/>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="87"/>
       <c r="C62" s="2"/>
       <c r="D62" s="91"/>
-      <c r="E62" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E62" s="89"/>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="87"/>
       <c r="C63" s="2"/>
       <c r="D63" s="91"/>
-      <c r="E63" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E63" s="89"/>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="87"/>
       <c r="C64" s="2"/>
       <c r="D64" s="91"/>
-      <c r="E64" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E64" s="89"/>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="87"/>
       <c r="C65" s="2"/>
       <c r="D65" s="91"/>
-      <c r="E65" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E65" s="89"/>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="87"/>
       <c r="C66" s="2"/>
       <c r="D66" s="91"/>
-      <c r="E66" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E66" s="89"/>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="87"/>
       <c r="C67" s="2"/>
       <c r="D67" s="91"/>
-      <c r="E67" s="89" t="s">
-        <v>234</v>
-      </c>
+      <c r="E67" s="89"/>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="87"/>
       <c r="C68" s="2"/>
       <c r="D68" s="91"/>
-      <c r="E68" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E68" s="89"/>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="87"/>
       <c r="C69" s="2"/>
       <c r="D69" s="91"/>
-      <c r="E69" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E69" s="89"/>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="87"/>
       <c r="C70" s="2"/>
       <c r="D70" s="91"/>
-      <c r="E70" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E70" s="89"/>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="87"/>
       <c r="C71" s="2"/>
       <c r="D71" s="91"/>
-      <c r="E71" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E71" s="89"/>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="87"/>
       <c r="C72" s="2"/>
       <c r="D72" s="91"/>
-      <c r="E72" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E72" s="89"/>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="87"/>
       <c r="C73" s="2"/>
       <c r="D73" s="91"/>
-      <c r="E73" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E73" s="89"/>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="87"/>
       <c r="C74" s="2"/>
       <c r="D74" s="91"/>
-      <c r="E74" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E74" s="89"/>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="87"/>
       <c r="C75" s="2"/>
       <c r="D75" s="91"/>
-      <c r="E75" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E75" s="89"/>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="87"/>
       <c r="C76" s="2"/>
       <c r="D76" s="91"/>
-      <c r="E76" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E76" s="89"/>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="87"/>
       <c r="C77" s="2"/>
       <c r="D77" s="91"/>
-      <c r="E77" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E77" s="89"/>
     </row>
     <row r="78" spans="2:5">
       <c r="B78" s="87"/>
       <c r="C78" s="2"/>
       <c r="D78" s="91"/>
-      <c r="E78" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E78" s="89"/>
     </row>
     <row r="79" spans="2:5">
       <c r="B79" s="87"/>
       <c r="C79" s="2"/>
       <c r="D79" s="91"/>
-      <c r="E79" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E79" s="89"/>
     </row>
     <row r="80" spans="2:5">
       <c r="B80" s="87"/>
       <c r="C80" s="2"/>
       <c r="D80" s="91"/>
-      <c r="E80" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E80" s="89"/>
     </row>
     <row r="81" spans="2:5">
       <c r="B81" s="87"/>
       <c r="C81" s="2"/>
       <c r="D81" s="91"/>
-      <c r="E81" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E81" s="89"/>
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="87"/>
       <c r="C82" s="2"/>
       <c r="D82" s="91"/>
-      <c r="E82" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E82" s="89"/>
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="87"/>
       <c r="C83" s="2"/>
       <c r="D83" s="91"/>
-      <c r="E83" s="89" t="s">
-        <v>235</v>
-      </c>
+      <c r="E83" s="89"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -35673,74 +35504,74 @@
     </row>
     <row r="3" spans="1:16" ht="37.35" customHeight="1">
       <c r="A3" s="37"/>
-      <c r="B3" s="451" t="s">
+      <c r="B3" s="491" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="452"/>
-      <c r="D3" s="452"/>
-      <c r="E3" s="452"/>
-      <c r="F3" s="452"/>
-      <c r="G3" s="452"/>
-      <c r="H3" s="452"/>
-      <c r="I3" s="452"/>
-      <c r="J3" s="452"/>
-      <c r="K3" s="452"/>
-      <c r="L3" s="452"/>
-      <c r="M3" s="452"/>
-      <c r="N3" s="452"/>
-      <c r="O3" s="453"/>
+      <c r="C3" s="492"/>
+      <c r="D3" s="492"/>
+      <c r="E3" s="492"/>
+      <c r="F3" s="492"/>
+      <c r="G3" s="492"/>
+      <c r="H3" s="492"/>
+      <c r="I3" s="492"/>
+      <c r="J3" s="492"/>
+      <c r="K3" s="492"/>
+      <c r="L3" s="492"/>
+      <c r="M3" s="492"/>
+      <c r="N3" s="492"/>
+      <c r="O3" s="493"/>
     </row>
     <row r="4" spans="1:16" ht="7.35" customHeight="1">
       <c r="A4" s="38"/>
-      <c r="B4" s="458" t="s">
+      <c r="B4" s="498" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="459"/>
-      <c r="D4" s="459"/>
-      <c r="E4" s="459"/>
-      <c r="F4" s="459"/>
-      <c r="G4" s="459"/>
-      <c r="H4" s="459"/>
-      <c r="I4" s="459"/>
-      <c r="J4" s="459"/>
-      <c r="K4" s="459"/>
-      <c r="L4" s="459"/>
-      <c r="M4" s="459"/>
-      <c r="N4" s="459"/>
+      <c r="C4" s="499"/>
+      <c r="D4" s="499"/>
+      <c r="E4" s="499"/>
+      <c r="F4" s="499"/>
+      <c r="G4" s="499"/>
+      <c r="H4" s="499"/>
+      <c r="I4" s="499"/>
+      <c r="J4" s="499"/>
+      <c r="K4" s="499"/>
+      <c r="L4" s="499"/>
+      <c r="M4" s="499"/>
+      <c r="N4" s="499"/>
       <c r="O4" s="354"/>
     </row>
     <row r="5" spans="1:16" ht="43.5" customHeight="1">
       <c r="A5" s="38"/>
-      <c r="B5" s="458"/>
-      <c r="C5" s="459"/>
-      <c r="D5" s="459"/>
-      <c r="E5" s="459"/>
-      <c r="F5" s="459"/>
-      <c r="G5" s="459"/>
-      <c r="H5" s="459"/>
-      <c r="I5" s="459"/>
-      <c r="J5" s="459"/>
-      <c r="K5" s="459"/>
-      <c r="L5" s="459"/>
-      <c r="M5" s="459"/>
-      <c r="N5" s="459"/>
+      <c r="B5" s="498"/>
+      <c r="C5" s="499"/>
+      <c r="D5" s="499"/>
+      <c r="E5" s="499"/>
+      <c r="F5" s="499"/>
+      <c r="G5" s="499"/>
+      <c r="H5" s="499"/>
+      <c r="I5" s="499"/>
+      <c r="J5" s="499"/>
+      <c r="K5" s="499"/>
+      <c r="L5" s="499"/>
+      <c r="M5" s="499"/>
+      <c r="N5" s="499"/>
       <c r="O5" s="354"/>
     </row>
     <row r="6" spans="1:16" ht="43.5" customHeight="1">
       <c r="A6" s="38"/>
-      <c r="B6" s="458"/>
-      <c r="C6" s="459"/>
-      <c r="D6" s="459"/>
-      <c r="E6" s="459"/>
-      <c r="F6" s="459"/>
-      <c r="G6" s="459"/>
-      <c r="H6" s="459"/>
-      <c r="I6" s="459"/>
-      <c r="J6" s="459"/>
-      <c r="K6" s="459"/>
-      <c r="L6" s="459"/>
-      <c r="M6" s="459"/>
-      <c r="N6" s="459"/>
+      <c r="B6" s="498"/>
+      <c r="C6" s="499"/>
+      <c r="D6" s="499"/>
+      <c r="E6" s="499"/>
+      <c r="F6" s="499"/>
+      <c r="G6" s="499"/>
+      <c r="H6" s="499"/>
+      <c r="I6" s="499"/>
+      <c r="J6" s="499"/>
+      <c r="K6" s="499"/>
+      <c r="L6" s="499"/>
+      <c r="M6" s="499"/>
+      <c r="N6" s="499"/>
       <c r="O6" s="354"/>
     </row>
     <row r="7" spans="1:16" ht="8.1" customHeight="1">
@@ -35769,19 +35600,19 @@
       <c r="A9" s="338"/>
       <c r="B9" s="345"/>
       <c r="C9" s="336"/>
-      <c r="D9" s="462" t="s">
+      <c r="D9" s="502" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="460"/>
-      <c r="F9" s="460"/>
-      <c r="G9" s="461"/>
+      <c r="E9" s="500"/>
+      <c r="F9" s="500"/>
+      <c r="G9" s="501"/>
       <c r="I9" s="336"/>
-      <c r="J9" s="467" t="s">
+      <c r="J9" s="507" t="s">
         <v>98</v>
       </c>
-      <c r="K9" s="464"/>
-      <c r="L9" s="465"/>
-      <c r="M9" s="466"/>
+      <c r="K9" s="504"/>
+      <c r="L9" s="505"/>
+      <c r="M9" s="506"/>
       <c r="O9" s="354"/>
     </row>
     <row r="10" spans="1:16" ht="37.5" customHeight="1" thickBot="1">
@@ -35790,7 +35621,7 @@
       <c r="C10" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="463"/>
+      <c r="D10" s="503"/>
       <c r="E10" s="76" t="s">
         <v>100</v>
       </c>
@@ -35803,7 +35634,7 @@
       <c r="I10" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="468"/>
+      <c r="J10" s="508"/>
       <c r="K10" s="82" t="s">
         <v>100</v>
       </c>
@@ -36100,58 +35931,58 @@
     <row r="30" spans="1:15" ht="42" customHeight="1" thickBot="1">
       <c r="A30" s="38"/>
       <c r="B30" s="347"/>
-      <c r="C30" s="477" t="s">
+      <c r="C30" s="517" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
-      <c r="G30" s="479"/>
+      <c r="D30" s="518"/>
+      <c r="E30" s="518"/>
+      <c r="F30" s="518"/>
+      <c r="G30" s="519"/>
       <c r="N30" s="355"/>
       <c r="O30" s="346"/>
     </row>
     <row r="31" spans="1:15" ht="49.5" customHeight="1">
       <c r="A31" s="38"/>
       <c r="B31" s="345"/>
-      <c r="C31" s="469" t="s">
+      <c r="C31" s="509" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="470"/>
-      <c r="E31" s="471" t="s">
+      <c r="D31" s="510"/>
+      <c r="E31" s="511" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="471"/>
-      <c r="G31" s="472"/>
+      <c r="F31" s="511"/>
+      <c r="G31" s="512"/>
       <c r="N31" s="355"/>
       <c r="O31" s="346"/>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="38"/>
       <c r="B32" s="345"/>
-      <c r="C32" s="473" t="s">
+      <c r="C32" s="513" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="474"/>
-      <c r="E32" s="475" t="s">
+      <c r="D32" s="514"/>
+      <c r="E32" s="515" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="475"/>
-      <c r="G32" s="476"/>
+      <c r="F32" s="515"/>
+      <c r="G32" s="516"/>
       <c r="N32" s="355"/>
       <c r="O32" s="346"/>
     </row>
     <row r="33" spans="1:15" ht="66.75" customHeight="1" thickBot="1">
       <c r="A33" s="38"/>
       <c r="B33" s="347"/>
-      <c r="C33" s="454" t="s">
+      <c r="C33" s="494" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="455"/>
-      <c r="E33" s="456" t="s">
+      <c r="D33" s="495"/>
+      <c r="E33" s="496" t="s">
         <v>106</v>
       </c>
-      <c r="F33" s="456"/>
-      <c r="G33" s="457"/>
+      <c r="F33" s="496"/>
+      <c r="G33" s="497"/>
       <c r="H33" s="351"/>
       <c r="J33" s="353"/>
       <c r="K33" s="353"/>
@@ -36249,9 +36080,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="114"/>
-      <c r="B1" s="485"/>
-      <c r="C1" s="486"/>
-      <c r="D1" s="487"/>
+      <c r="B1" s="527"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="529"/>
       <c r="E1" s="95"/>
       <c r="F1" s="98"/>
       <c r="G1" s="96"/>
@@ -36273,10 +36104,10 @@
       <c r="E2" s="104"/>
       <c r="G2" s="106"/>
       <c r="H2" s="98"/>
-      <c r="I2" s="494" t="s">
+      <c r="I2" s="523" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="495"/>
+      <c r="J2" s="524"/>
       <c r="K2" s="109"/>
       <c r="L2" s="98"/>
       <c r="M2" s="106"/>
@@ -36329,10 +36160,10 @@
       <c r="B5" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="488" t="s">
+      <c r="C5" s="530" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="489"/>
+      <c r="D5" s="531"/>
       <c r="E5" s="239" t="s">
         <v>110</v>
       </c>
@@ -36362,8 +36193,8 @@
       <c r="B6" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="490"/>
-      <c r="D6" s="491"/>
+      <c r="C6" s="532"/>
+      <c r="D6" s="533"/>
       <c r="E6" s="271"/>
       <c r="F6" s="271"/>
       <c r="G6" s="271"/>
@@ -36383,8 +36214,8 @@
       <c r="B7" s="269" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="492"/>
-      <c r="D7" s="493"/>
+      <c r="C7" s="534"/>
+      <c r="D7" s="535"/>
       <c r="E7" s="273"/>
       <c r="F7" s="273"/>
       <c r="G7" s="273"/>
@@ -36402,8 +36233,8 @@
       <c r="B8" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="492"/>
-      <c r="D8" s="493"/>
+      <c r="C8" s="534"/>
+      <c r="D8" s="535"/>
       <c r="E8" s="273"/>
       <c r="F8" s="273"/>
       <c r="G8" s="273"/>
@@ -36422,8 +36253,8 @@
       <c r="B9" s="269" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="492"/>
-      <c r="D9" s="493"/>
+      <c r="C9" s="534"/>
+      <c r="D9" s="535"/>
       <c r="E9" s="273"/>
       <c r="F9" s="273"/>
       <c r="G9" s="273"/>
@@ -36443,8 +36274,8 @@
       <c r="B10" s="269" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="492"/>
-      <c r="D10" s="493"/>
+      <c r="C10" s="534"/>
+      <c r="D10" s="535"/>
       <c r="E10" s="273"/>
       <c r="F10" s="273"/>
       <c r="G10" s="273"/>
@@ -36463,8 +36294,8 @@
       <c r="B11" s="269" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="492"/>
-      <c r="D11" s="493"/>
+      <c r="C11" s="534"/>
+      <c r="D11" s="535"/>
       <c r="E11" s="273"/>
       <c r="F11" s="273"/>
       <c r="G11" s="273"/>
@@ -36483,8 +36314,8 @@
       <c r="B12" s="270" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="480"/>
-      <c r="D12" s="481"/>
+      <c r="C12" s="525"/>
+      <c r="D12" s="526"/>
       <c r="E12" s="275"/>
       <c r="F12" s="275"/>
       <c r="G12" s="275"/>
@@ -36563,12 +36394,12 @@
       <c r="D16" s="396" t="s">
         <v>130</v>
       </c>
-      <c r="E16" s="482"/>
-      <c r="F16" s="483"/>
-      <c r="G16" s="483"/>
-      <c r="H16" s="483"/>
-      <c r="I16" s="483"/>
-      <c r="J16" s="484"/>
+      <c r="E16" s="520"/>
+      <c r="F16" s="521"/>
+      <c r="G16" s="521"/>
+      <c r="H16" s="521"/>
+      <c r="I16" s="521"/>
+      <c r="J16" s="522"/>
       <c r="K16" s="413"/>
       <c r="L16" s="134"/>
       <c r="M16" s="132"/>
@@ -36584,12 +36415,12 @@
       <c r="D17" s="396" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="482"/>
-      <c r="F17" s="483"/>
-      <c r="G17" s="483"/>
-      <c r="H17" s="483"/>
-      <c r="I17" s="483"/>
-      <c r="J17" s="484"/>
+      <c r="E17" s="520"/>
+      <c r="F17" s="521"/>
+      <c r="G17" s="521"/>
+      <c r="H17" s="521"/>
+      <c r="I17" s="521"/>
+      <c r="J17" s="522"/>
       <c r="K17" s="162"/>
       <c r="L17" s="145"/>
       <c r="M17" s="134"/>
@@ -36606,12 +36437,12 @@
       <c r="D18" s="397" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="482"/>
-      <c r="F18" s="483"/>
-      <c r="G18" s="483"/>
-      <c r="H18" s="483"/>
-      <c r="I18" s="483"/>
-      <c r="J18" s="484"/>
+      <c r="E18" s="520"/>
+      <c r="F18" s="521"/>
+      <c r="G18" s="521"/>
+      <c r="H18" s="521"/>
+      <c r="I18" s="521"/>
+      <c r="J18" s="522"/>
       <c r="L18" s="134"/>
       <c r="M18" s="130"/>
       <c r="N18" s="129"/>
@@ -36625,12 +36456,12 @@
       <c r="D19" s="398" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="482"/>
-      <c r="F19" s="483"/>
-      <c r="G19" s="483"/>
-      <c r="H19" s="483"/>
-      <c r="I19" s="483"/>
-      <c r="J19" s="484"/>
+      <c r="E19" s="520"/>
+      <c r="F19" s="521"/>
+      <c r="G19" s="521"/>
+      <c r="H19" s="521"/>
+      <c r="I19" s="521"/>
+      <c r="J19" s="522"/>
       <c r="K19" s="162"/>
       <c r="L19" s="145"/>
       <c r="M19" s="130"/>
@@ -36644,12 +36475,12 @@
       <c r="D20" s="397" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="482"/>
-      <c r="F20" s="483"/>
-      <c r="G20" s="483"/>
-      <c r="H20" s="483"/>
-      <c r="I20" s="483"/>
-      <c r="J20" s="484"/>
+      <c r="E20" s="520"/>
+      <c r="F20" s="521"/>
+      <c r="G20" s="521"/>
+      <c r="H20" s="521"/>
+      <c r="I20" s="521"/>
+      <c r="J20" s="522"/>
       <c r="K20" s="414"/>
       <c r="L20" s="399"/>
       <c r="M20" s="133"/>
@@ -36662,12 +36493,12 @@
       <c r="D21" s="400" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="482"/>
-      <c r="F21" s="483"/>
-      <c r="G21" s="483"/>
-      <c r="H21" s="483"/>
-      <c r="I21" s="483"/>
-      <c r="J21" s="484"/>
+      <c r="E21" s="520"/>
+      <c r="F21" s="521"/>
+      <c r="G21" s="521"/>
+      <c r="H21" s="521"/>
+      <c r="I21" s="521"/>
+      <c r="J21" s="522"/>
       <c r="K21" s="415"/>
       <c r="L21" s="68"/>
       <c r="M21" s="131"/>
@@ -36681,12 +36512,12 @@
       <c r="D22" s="416" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="482"/>
-      <c r="F22" s="483"/>
-      <c r="G22" s="483"/>
-      <c r="H22" s="483"/>
-      <c r="I22" s="483"/>
-      <c r="J22" s="484"/>
+      <c r="E22" s="520"/>
+      <c r="F22" s="521"/>
+      <c r="G22" s="521"/>
+      <c r="H22" s="521"/>
+      <c r="I22" s="521"/>
+      <c r="J22" s="522"/>
       <c r="L22" s="131"/>
       <c r="M22" s="134"/>
       <c r="N22" s="134"/>
@@ -37104,11 +36935,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E19:J19"/>
@@ -37121,6 +36947,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -37129,15 +36960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
@@ -37146,6 +36968,15 @@
     <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37404,14 +37235,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -37424,6 +37247,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
